--- a/planilha/plano-alimentar-pos-infarto.xlsx
+++ b/planilha/plano-alimentar-pos-infarto.xlsx
@@ -850,7 +850,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:F44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1368,7 +1368,7 @@
     <row r="24" ht="30" customHeight="1">
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>Iogurte natural desnatado</t>
+          <t>Iogurte natural (desnatado, sem açúcar)</t>
         </is>
       </c>
       <c r="C24" s="12" t="inlineStr">
@@ -1388,192 +1388,192 @@
       </c>
       <c r="F24" s="11" t="inlineStr">
         <is>
-          <t>Sem açúcar adicionado</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="9" t="inlineStr">
+          <t>Prefira sempre a versão sem açúcar adicionado</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="30" customHeight="1">
+      <c r="B25" s="11" t="inlineStr">
+        <is>
+          <t>Requeijão</t>
+        </is>
+      </c>
+      <c r="C25" s="12" t="inlineStr">
+        <is>
+          <t>1 colher de sopa (≈15 g)</t>
+        </is>
+      </c>
+      <c r="D25" s="12" t="inlineStr">
+        <is>
+          <t>2x/semana</t>
+        </is>
+      </c>
+      <c r="E25" s="14" t="inlineStr">
+        <is>
+          <t>Moderar</t>
+        </is>
+      </c>
+      <c r="F25" s="11" t="inlineStr">
+        <is>
+          <t>Rico em gordura saturada e sódio; prefira a versão light. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="9" t="inlineStr">
         <is>
           <t>Bebidas</t>
         </is>
       </c>
-      <c r="B25" s="10" t="n"/>
-      <c r="C25" s="10" t="n"/>
-      <c r="D25" s="10" t="n"/>
-      <c r="E25" s="10" t="n"/>
-      <c r="F25" s="10" t="n"/>
-    </row>
-    <row r="26" ht="30" customHeight="1">
-      <c r="B26" s="11" t="inlineStr">
-        <is>
-          <t>Água</t>
-        </is>
-      </c>
-      <c r="C26" s="12" t="inlineStr">
-        <is>
-          <t>à vontade</t>
-        </is>
-      </c>
-      <c r="D26" s="12" t="inlineStr">
-        <is>
-          <t>todos os dias</t>
-        </is>
-      </c>
-      <c r="E26" s="13" t="inlineStr">
-        <is>
-          <t>Liberado</t>
-        </is>
-      </c>
-      <c r="F26" s="11" t="inlineStr"/>
+      <c r="B26" s="10" t="n"/>
+      <c r="C26" s="10" t="n"/>
+      <c r="D26" s="10" t="n"/>
+      <c r="E26" s="10" t="n"/>
+      <c r="F26" s="10" t="n"/>
     </row>
     <row r="27" ht="30" customHeight="1">
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>Refrigerante zero</t>
+          <t>Água</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>200 ml</t>
+          <t>à vontade</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>1x/dia</t>
-        </is>
-      </c>
-      <c r="E27" s="14" t="inlineStr">
-        <is>
-          <t>Moderar</t>
-        </is>
-      </c>
-      <c r="F27" s="11" t="inlineStr">
-        <is>
-          <t>Sugestão gerada por IA — confirmar com nutricionista/cardiologista</t>
-        </is>
-      </c>
+          <t>todos os dias</t>
+        </is>
+      </c>
+      <c r="E27" s="13" t="inlineStr">
+        <is>
+          <t>Liberado</t>
+        </is>
+      </c>
+      <c r="F27" s="11" t="inlineStr"/>
     </row>
     <row r="28" ht="30" customHeight="1">
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>Café sem açúcar</t>
+          <t>Refrigerante zero</t>
         </is>
       </c>
       <c r="C28" s="12" t="inlineStr">
         <is>
-          <t>1 xícara</t>
+          <t>200 ml</t>
         </is>
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
-          <t>2x/dia</t>
-        </is>
-      </c>
-      <c r="E28" s="13" t="inlineStr">
-        <is>
-          <t>Liberado</t>
-        </is>
-      </c>
-      <c r="F28" s="11" t="inlineStr"/>
+          <t>1x/dia</t>
+        </is>
+      </c>
+      <c r="E28" s="14" t="inlineStr">
+        <is>
+          <t>Moderar</t>
+        </is>
+      </c>
+      <c r="F28" s="11" t="inlineStr">
+        <is>
+          <t>Sugestão gerada por IA — confirmar com nutricionista/cardiologista</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="30" customHeight="1">
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>Suco natural sem açúcar</t>
+          <t>Café sem açúcar</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>200 ml</t>
+          <t>1 xícara</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>3x/semana</t>
-        </is>
-      </c>
-      <c r="E29" s="14" t="inlineStr">
-        <is>
-          <t>Moderar</t>
-        </is>
-      </c>
-      <c r="F29" s="11" t="inlineStr">
-        <is>
-          <t>Preferir a fruta inteira, que tem mais fibra</t>
-        </is>
-      </c>
+          <t>2x/dia</t>
+        </is>
+      </c>
+      <c r="E29" s="13" t="inlineStr">
+        <is>
+          <t>Liberado</t>
+        </is>
+      </c>
+      <c r="F29" s="11" t="inlineStr"/>
     </row>
     <row r="30" ht="30" customHeight="1">
       <c r="B30" s="11" t="inlineStr">
         <is>
+          <t>Suco natural sem açúcar</t>
+        </is>
+      </c>
+      <c r="C30" s="12" t="inlineStr">
+        <is>
+          <t>200 ml</t>
+        </is>
+      </c>
+      <c r="D30" s="12" t="inlineStr">
+        <is>
+          <t>3x/semana</t>
+        </is>
+      </c>
+      <c r="E30" s="14" t="inlineStr">
+        <is>
+          <t>Moderar</t>
+        </is>
+      </c>
+      <c r="F30" s="11" t="inlineStr">
+        <is>
+          <t>Preferir a fruta inteira, que tem mais fibra</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="30" customHeight="1">
+      <c r="B31" s="11" t="inlineStr">
+        <is>
           <t>Bebida alcoólica</t>
         </is>
       </c>
-      <c r="C30" s="12" t="inlineStr">
+      <c r="C31" s="12" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D30" s="12" t="inlineStr">
+      <c r="D31" s="12" t="inlineStr">
         <is>
           <t>evitar</t>
         </is>
       </c>
-      <c r="E30" s="15" t="inlineStr">
+      <c r="E31" s="15" t="inlineStr">
         <is>
           <t>Evitar</t>
         </is>
       </c>
-      <c r="F30" s="11" t="inlineStr">
+      <c r="F31" s="11" t="inlineStr">
         <is>
           <t>Piora diretamente os triglicerídeos</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="9" t="inlineStr">
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="9" t="inlineStr">
         <is>
           <t>Doces e Sobremesas</t>
         </is>
       </c>
-      <c r="B31" s="10" t="n"/>
-      <c r="C31" s="10" t="n"/>
-      <c r="D31" s="10" t="n"/>
-      <c r="E31" s="10" t="n"/>
-      <c r="F31" s="10" t="n"/>
-    </row>
-    <row r="32" ht="30" customHeight="1">
-      <c r="B32" s="11" t="inlineStr">
-        <is>
-          <t>Açúcar refinado</t>
-        </is>
-      </c>
-      <c r="C32" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D32" s="12" t="inlineStr">
-        <is>
-          <t>evitar</t>
-        </is>
-      </c>
-      <c r="E32" s="15" t="inlineStr">
-        <is>
-          <t>Evitar</t>
-        </is>
-      </c>
-      <c r="F32" s="11" t="inlineStr">
-        <is>
-          <t>Impacto direto nos triglicerídeos</t>
-        </is>
-      </c>
+      <c r="B32" s="10" t="n"/>
+      <c r="C32" s="10" t="n"/>
+      <c r="D32" s="10" t="n"/>
+      <c r="E32" s="10" t="n"/>
+      <c r="F32" s="10" t="n"/>
     </row>
     <row r="33" ht="30" customHeight="1">
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>Doces industrializados</t>
+          <t>Açúcar refinado</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
@@ -1591,188 +1591,215 @@
           <t>Evitar</t>
         </is>
       </c>
-      <c r="F33" s="11" t="inlineStr"/>
+      <c r="F33" s="11" t="inlineStr">
+        <is>
+          <t>Impacto direto nos triglicerídeos</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="30" customHeight="1">
       <c r="B34" s="11" t="inlineStr">
         <is>
+          <t>Doces industrializados</t>
+        </is>
+      </c>
+      <c r="C34" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D34" s="12" t="inlineStr">
+        <is>
+          <t>evitar</t>
+        </is>
+      </c>
+      <c r="E34" s="15" t="inlineStr">
+        <is>
+          <t>Evitar</t>
+        </is>
+      </c>
+      <c r="F34" s="11" t="inlineStr"/>
+    </row>
+    <row r="35" ht="30" customHeight="1">
+      <c r="B35" s="11" t="inlineStr">
+        <is>
           <t>Chocolate amargo (70%+)</t>
         </is>
       </c>
-      <c r="C34" s="12" t="inlineStr">
+      <c r="C35" s="12" t="inlineStr">
         <is>
           <t>10 g</t>
         </is>
       </c>
-      <c r="D34" s="12" t="inlineStr">
+      <c r="D35" s="12" t="inlineStr">
         <is>
           <t>2x/semana</t>
         </is>
       </c>
-      <c r="E34" s="14" t="inlineStr">
+      <c r="E35" s="14" t="inlineStr">
         <is>
           <t>Moderar</t>
         </is>
       </c>
-      <c r="F34" s="11" t="inlineStr">
+      <c r="F35" s="11" t="inlineStr">
         <is>
           <t>Sugestão gerada por IA — confirmar com nutricionista/cardiologista</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="9" t="inlineStr">
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="9" t="inlineStr">
         <is>
           <t>Gorduras e Temperos</t>
         </is>
       </c>
-      <c r="B35" s="10" t="n"/>
-      <c r="C35" s="10" t="n"/>
-      <c r="D35" s="10" t="n"/>
-      <c r="E35" s="10" t="n"/>
-      <c r="F35" s="10" t="n"/>
-    </row>
-    <row r="36" ht="30" customHeight="1">
-      <c r="B36" s="11" t="inlineStr">
-        <is>
-          <t>Azeite de oliva extra virgem</t>
-        </is>
-      </c>
-      <c r="C36" s="12" t="inlineStr">
-        <is>
-          <t>1-2 colheres de sopa</t>
-        </is>
-      </c>
-      <c r="D36" s="12" t="inlineStr">
-        <is>
-          <t>1x/dia</t>
-        </is>
-      </c>
-      <c r="E36" s="13" t="inlineStr">
-        <is>
-          <t>Liberado</t>
-        </is>
-      </c>
-      <c r="F36" s="11" t="inlineStr"/>
+      <c r="B36" s="10" t="n"/>
+      <c r="C36" s="10" t="n"/>
+      <c r="D36" s="10" t="n"/>
+      <c r="E36" s="10" t="n"/>
+      <c r="F36" s="10" t="n"/>
     </row>
     <row r="37" ht="30" customHeight="1">
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>Manteiga</t>
+          <t>Azeite de oliva extra virgem</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1-2 colheres de sopa</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
-          <t>evitar</t>
-        </is>
-      </c>
-      <c r="E37" s="15" t="inlineStr">
-        <is>
-          <t>Evitar</t>
-        </is>
-      </c>
-      <c r="F37" s="11" t="inlineStr">
-        <is>
-          <t>Preferir azeite</t>
-        </is>
-      </c>
+          <t>1x/dia</t>
+        </is>
+      </c>
+      <c r="E37" s="13" t="inlineStr">
+        <is>
+          <t>Liberado</t>
+        </is>
+      </c>
+      <c r="F37" s="11" t="inlineStr"/>
     </row>
     <row r="38" ht="30" customHeight="1">
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>Sal</t>
+          <t>Manteiga</t>
         </is>
       </c>
       <c r="C38" s="12" t="inlineStr">
         <is>
-          <t>&lt; 5 g no total</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D38" s="12" t="inlineStr">
         <is>
-          <t>todos os dias</t>
-        </is>
-      </c>
-      <c r="E38" s="14" t="inlineStr">
-        <is>
-          <t>Moderar</t>
+          <t>evitar</t>
+        </is>
+      </c>
+      <c r="E38" s="15" t="inlineStr">
+        <is>
+          <t>Evitar</t>
         </is>
       </c>
       <c r="F38" s="11" t="inlineStr">
         <is>
-          <t>Somar sal de cozinha + industrializados</t>
+          <t>Preferir azeite</t>
         </is>
       </c>
     </row>
     <row r="39" ht="30" customHeight="1">
       <c r="B39" s="11" t="inlineStr">
         <is>
+          <t>Sal</t>
+        </is>
+      </c>
+      <c r="C39" s="12" t="inlineStr">
+        <is>
+          <t>&lt; 5 g no total</t>
+        </is>
+      </c>
+      <c r="D39" s="12" t="inlineStr">
+        <is>
+          <t>todos os dias</t>
+        </is>
+      </c>
+      <c r="E39" s="14" t="inlineStr">
+        <is>
+          <t>Moderar</t>
+        </is>
+      </c>
+      <c r="F39" s="11" t="inlineStr">
+        <is>
+          <t>Somar sal de cozinha + industrializados</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="30" customHeight="1">
+      <c r="B40" s="11" t="inlineStr">
+        <is>
           <t>Ervas e temperos naturais</t>
         </is>
       </c>
-      <c r="C39" s="12" t="inlineStr">
+      <c r="C40" s="12" t="inlineStr">
         <is>
           <t>à vontade</t>
         </is>
       </c>
-      <c r="D39" s="12" t="inlineStr">
+      <c r="D40" s="12" t="inlineStr">
         <is>
           <t>todos os dias</t>
         </is>
       </c>
-      <c r="E39" s="13" t="inlineStr">
+      <c r="E40" s="13" t="inlineStr">
         <is>
           <t>Liberado</t>
         </is>
       </c>
-      <c r="F39" s="11" t="inlineStr"/>
-    </row>
-    <row r="40" ht="20" customHeight="1">
-      <c r="A40" s="9" t="inlineStr">
+      <c r="F40" s="11" t="inlineStr"/>
+    </row>
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="9" t="inlineStr">
         <is>
           <t>Vegetais e Verduras</t>
         </is>
       </c>
-      <c r="B40" s="10" t="n"/>
-      <c r="C40" s="10" t="n"/>
-      <c r="D40" s="10" t="n"/>
-      <c r="E40" s="10" t="n"/>
-      <c r="F40" s="10" t="n"/>
-    </row>
-    <row r="41" ht="30" customHeight="1">
-      <c r="B41" s="11" t="inlineStr">
+      <c r="B41" s="10" t="n"/>
+      <c r="C41" s="10" t="n"/>
+      <c r="D41" s="10" t="n"/>
+      <c r="E41" s="10" t="n"/>
+      <c r="F41" s="10" t="n"/>
+    </row>
+    <row r="42" ht="30" customHeight="1">
+      <c r="B42" s="11" t="inlineStr">
         <is>
           <t>Vegetais e verduras em geral</t>
         </is>
       </c>
-      <c r="C41" s="12" t="inlineStr">
+      <c r="C42" s="12" t="inlineStr">
         <is>
           <t>à vontade</t>
         </is>
       </c>
-      <c r="D41" s="12" t="inlineStr">
+      <c r="D42" s="12" t="inlineStr">
         <is>
           <t>todos os dias</t>
         </is>
       </c>
-      <c r="E41" s="13" t="inlineStr">
+      <c r="E42" s="13" t="inlineStr">
         <is>
           <t>Liberado</t>
         </is>
       </c>
-      <c r="F41" s="11" t="inlineStr">
+      <c r="F42" s="11" t="inlineStr">
         <is>
           <t>Se entrar anticoagulante na medicação, revisar consumo de verde-escuros ricos em vitamina K</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="30" customHeight="1">
-      <c r="A43" s="16" t="inlineStr">
+    <row r="44" ht="30" customHeight="1">
+      <c r="A44" s="16" t="inlineStr">
         <is>
           <t>Lista com os alimentos acrescentados até agora — não é uma lista completa. Use a skill 'adicionar-alimento' (ex.: "adicione sucrilhos") para ir acrescentando novos itens aos poucos.</t>
         </is>
@@ -1780,16 +1807,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A41:F41"/>
     <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A36:F36"/>
+    <mergeCell ref="A44:F44"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A31:F31"/>
-    <mergeCell ref="A40:F40"/>
-    <mergeCell ref="A35:F35"/>
+    <mergeCell ref="A32:F32"/>
     <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A26:F26"/>
     <mergeCell ref="A21:F21"/>
     <mergeCell ref="A15:F15"/>
-    <mergeCell ref="A25:F25"/>
-    <mergeCell ref="A43:F43"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/planilha/plano-alimentar-pos-infarto.xlsx
+++ b/planilha/plano-alimentar-pos-infarto.xlsx
@@ -542,7 +542,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -703,22 +703,70 @@
     <row r="14" ht="46" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>Aviso pendente — medicação</t>
+          <t>Medicações em uso (receita 03/09/2026)</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Lista de medicações da alta ainda não preenchida. Existem interações conhecidas entre alimentos e medicações comuns pós-IAM (ex.: anticoagulantes como varfarina e vegetais verde-escuros ricos em vitamina K). Revisar esta planilha assim que a lista de medicações estiver disponível.</t>
+          <t>Aspirina Prevent 100mg (1x/dia, almoço) e Ticagrelor 90mg (12/12h, por 1 ano) — antiagregantes plaquetários; Rosucor (rosuvastatina) 20mg, 2 comprimidos 1x/dia, e Ezetimiba 10mg 1x/dia — colesterol; Maleato de Enalapril 5mg 12/12h — coração/pressão (médico alertou para cuidado com pressão baixa). Todas de uso contínuo — não interromper sem falar com o cardiologista, em especial a dupla Aspirina + Ticagrelor (risco de trombose no stent).</t>
         </is>
       </c>
     </row>
     <row r="15" ht="46" customHeight="1">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Interação medicamentosa — Ticagrelor</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Toranja/grapefruit (fruta ou suco) aumenta o nível de Ticagrelor no sangue e o risco de sangramento — evitar completamente enquanto estiver em uso do medicamento.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="46" customHeight="1">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Interação medicamentosa — Enalapril</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Enalapril pode elevar o potássio do sangue. Evitar sal light/substitutos de sal (ricos em cloreto de potássio) e suplementos de potássio sem orientação médica — atenção redobrada enquanto a função renal ainda está em investigação.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="46" customHeight="1">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Interação medicamentosa — Aspirina + Ticagrelor</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>A dupla antiagregação (esquema padrão por 1 ano pós-stent) já aumenta o risco de sangramento; álcool amplifica esse risco — reforça a orientação de evitar bebida alcoólica.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="46" customHeight="1">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Interação medicamentosa — Rosucor (estatina)</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Evitar suplementos de 'arroz de levedura vermelha' (red yeast rice), que agem como uma estatina natural e podem somar toxicidade com a Rosucor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="46" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>Leitura de rótulos</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>Ao comprar um produto industrializado, olhar sempre: sódio por porção, açúcares totais/adicionados, e a lista de ingredientes procurando 'gordura hidrogenada' ou 'gordura trans'. Prefira produtos com menos ingredientes e sem açúcar adicionado.</t>
         </is>
@@ -850,7 +898,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F44"/>
+  <dimension ref="A1:F47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1056,45 +1104,49 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="9" t="inlineStr">
+    <row r="10" ht="30" customHeight="1">
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>Toranja / grapefruit</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>evitar</t>
+        </is>
+      </c>
+      <c r="E10" s="15" t="inlineStr">
+        <is>
+          <t>Evitar</t>
+        </is>
+      </c>
+      <c r="F10" s="11" t="inlineStr">
+        <is>
+          <t>Interage com o Ticagrelor (aumenta o nível do remédio no sangue e o risco de sangramento) — evitar completamente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>Grãos e Cereais</t>
         </is>
       </c>
-      <c r="B10" s="10" t="n"/>
-      <c r="C10" s="10" t="n"/>
-      <c r="D10" s="10" t="n"/>
-      <c r="E10" s="10" t="n"/>
-      <c r="F10" s="10" t="n"/>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>Arroz integral</t>
-        </is>
-      </c>
-      <c r="C11" s="12" t="inlineStr">
-        <is>
-          <t>200 g (cozido)</t>
-        </is>
-      </c>
-      <c r="D11" s="12" t="inlineStr">
-        <is>
-          <t>quase todo dia</t>
-        </is>
-      </c>
-      <c r="E11" s="13" t="inlineStr">
-        <is>
-          <t>Liberado</t>
-        </is>
-      </c>
-      <c r="F11" s="11" t="inlineStr"/>
+      <c r="B11" s="10" t="n"/>
+      <c r="C11" s="10" t="n"/>
+      <c r="D11" s="10" t="n"/>
+      <c r="E11" s="10" t="n"/>
+      <c r="F11" s="10" t="n"/>
     </row>
     <row r="12" ht="30" customHeight="1">
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Arroz branco</t>
+          <t>Arroz integral</t>
         </is>
       </c>
       <c r="C12" s="12" t="inlineStr">
@@ -1104,113 +1156,109 @@
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>2x/semana</t>
-        </is>
-      </c>
-      <c r="E12" s="14" t="inlineStr">
-        <is>
-          <t>Moderar</t>
-        </is>
-      </c>
-      <c r="F12" s="11" t="inlineStr">
-        <is>
-          <t>Preferir integral no restante da semana</t>
-        </is>
-      </c>
+          <t>quase todo dia</t>
+        </is>
+      </c>
+      <c r="E12" s="13" t="inlineStr">
+        <is>
+          <t>Liberado</t>
+        </is>
+      </c>
+      <c r="F12" s="11" t="inlineStr"/>
     </row>
     <row r="13" ht="30" customHeight="1">
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Aveia</t>
+          <t>Arroz branco</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>2 colheres de sopa</t>
+          <t>200 g (cozido)</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>1x/dia</t>
-        </is>
-      </c>
-      <c r="E13" s="13" t="inlineStr">
-        <is>
-          <t>Liberado</t>
+          <t>2x/semana</t>
+        </is>
+      </c>
+      <c r="E13" s="14" t="inlineStr">
+        <is>
+          <t>Moderar</t>
         </is>
       </c>
       <c r="F13" s="11" t="inlineStr">
         <is>
-          <t>Ajuda a reduzir colesterol</t>
+          <t>Preferir integral no restante da semana</t>
         </is>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1">
       <c r="B14" s="11" t="inlineStr">
         <is>
+          <t>Aveia</t>
+        </is>
+      </c>
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t>2 colheres de sopa</t>
+        </is>
+      </c>
+      <c r="D14" s="12" t="inlineStr">
+        <is>
+          <t>1x/dia</t>
+        </is>
+      </c>
+      <c r="E14" s="13" t="inlineStr">
+        <is>
+          <t>Liberado</t>
+        </is>
+      </c>
+      <c r="F14" s="11" t="inlineStr">
+        <is>
+          <t>Ajuda a reduzir colesterol</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="B15" s="11" t="inlineStr">
+        <is>
           <t>Pão integral</t>
         </is>
       </c>
-      <c r="C14" s="12" t="inlineStr">
+      <c r="C15" s="12" t="inlineStr">
         <is>
           <t>2 fatias</t>
         </is>
       </c>
-      <c r="D14" s="12" t="inlineStr">
+      <c r="D15" s="12" t="inlineStr">
         <is>
           <t>1x/dia</t>
         </is>
       </c>
-      <c r="E14" s="13" t="inlineStr">
+      <c r="E15" s="13" t="inlineStr">
         <is>
           <t>Liberado</t>
         </is>
       </c>
-      <c r="F14" s="11" t="inlineStr"/>
-    </row>
-    <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="9" t="inlineStr">
+      <c r="F15" s="11" t="inlineStr"/>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="9" t="inlineStr">
         <is>
           <t>Proteínas</t>
         </is>
       </c>
-      <c r="B15" s="10" t="n"/>
-      <c r="C15" s="10" t="n"/>
-      <c r="D15" s="10" t="n"/>
-      <c r="E15" s="10" t="n"/>
-      <c r="F15" s="10" t="n"/>
-    </row>
-    <row r="16" ht="30" customHeight="1">
-      <c r="B16" s="11" t="inlineStr">
-        <is>
-          <t>Peixe</t>
-        </is>
-      </c>
-      <c r="C16" s="12" t="inlineStr">
-        <is>
-          <t>150 g</t>
-        </is>
-      </c>
-      <c r="D16" s="12" t="inlineStr">
-        <is>
-          <t>3x/semana</t>
-        </is>
-      </c>
-      <c r="E16" s="13" t="inlineStr">
-        <is>
-          <t>Liberado</t>
-        </is>
-      </c>
-      <c r="F16" s="11" t="inlineStr">
-        <is>
-          <t>Fonte de ômega-3</t>
-        </is>
-      </c>
+      <c r="B16" s="10" t="n"/>
+      <c r="C16" s="10" t="n"/>
+      <c r="D16" s="10" t="n"/>
+      <c r="E16" s="10" t="n"/>
+      <c r="F16" s="10" t="n"/>
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>Frango sem pele</t>
+          <t>Peixe</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
@@ -1220,7 +1268,7 @@
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>quase todo dia</t>
+          <t>3x/semana</t>
         </is>
       </c>
       <c r="E17" s="13" t="inlineStr">
@@ -1228,12 +1276,16 @@
           <t>Liberado</t>
         </is>
       </c>
-      <c r="F17" s="11" t="inlineStr"/>
+      <c r="F17" s="11" t="inlineStr">
+        <is>
+          <t>Fonte de ômega-3</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="30" customHeight="1">
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>Carne vermelha magra</t>
+          <t>Frango sem pele</t>
         </is>
       </c>
       <c r="C18" s="12" t="inlineStr">
@@ -1243,337 +1295,348 @@
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>1x/semana</t>
-        </is>
-      </c>
-      <c r="E18" s="14" t="inlineStr">
-        <is>
-          <t>Moderar</t>
-        </is>
-      </c>
-      <c r="F18" s="11" t="inlineStr">
-        <is>
-          <t>Preferir cortes magros</t>
-        </is>
-      </c>
+          <t>quase todo dia</t>
+        </is>
+      </c>
+      <c r="E18" s="13" t="inlineStr">
+        <is>
+          <t>Liberado</t>
+        </is>
+      </c>
+      <c r="F18" s="11" t="inlineStr"/>
     </row>
     <row r="19" ht="30" customHeight="1">
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>Ovo</t>
+          <t>Carne vermelha magra</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>1 unidade</t>
+          <t>150 g</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>até 5x/semana</t>
-        </is>
-      </c>
-      <c r="E19" s="13" t="inlineStr">
-        <is>
-          <t>Liberado</t>
-        </is>
-      </c>
-      <c r="F19" s="11" t="inlineStr"/>
+          <t>1x/semana</t>
+        </is>
+      </c>
+      <c r="E19" s="14" t="inlineStr">
+        <is>
+          <t>Moderar</t>
+        </is>
+      </c>
+      <c r="F19" s="11" t="inlineStr">
+        <is>
+          <t>Preferir cortes magros</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="30" customHeight="1">
       <c r="B20" s="11" t="inlineStr">
         <is>
+          <t>Ovo</t>
+        </is>
+      </c>
+      <c r="C20" s="12" t="inlineStr">
+        <is>
+          <t>1 unidade</t>
+        </is>
+      </c>
+      <c r="D20" s="12" t="inlineStr">
+        <is>
+          <t>até 5x/semana</t>
+        </is>
+      </c>
+      <c r="E20" s="13" t="inlineStr">
+        <is>
+          <t>Liberado</t>
+        </is>
+      </c>
+      <c r="F20" s="11" t="inlineStr"/>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="B21" s="11" t="inlineStr">
+        <is>
           <t>Feijão / leguminosas</t>
         </is>
       </c>
-      <c r="C20" s="12" t="inlineStr">
+      <c r="C21" s="12" t="inlineStr">
         <is>
           <t>1 concha</t>
         </is>
       </c>
-      <c r="D20" s="12" t="inlineStr">
+      <c r="D21" s="12" t="inlineStr">
         <is>
           <t>1x/dia</t>
         </is>
       </c>
-      <c r="E20" s="13" t="inlineStr">
+      <c r="E21" s="13" t="inlineStr">
         <is>
           <t>Liberado</t>
         </is>
       </c>
-      <c r="F20" s="11" t="inlineStr"/>
-    </row>
-    <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="9" t="inlineStr">
+      <c r="F21" s="11" t="inlineStr"/>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="9" t="inlineStr">
         <is>
           <t>Laticínios</t>
         </is>
       </c>
-      <c r="B21" s="10" t="n"/>
-      <c r="C21" s="10" t="n"/>
-      <c r="D21" s="10" t="n"/>
-      <c r="E21" s="10" t="n"/>
-      <c r="F21" s="10" t="n"/>
-    </row>
-    <row r="22" ht="30" customHeight="1">
-      <c r="B22" s="11" t="inlineStr">
-        <is>
-          <t>Leite desnatado</t>
-        </is>
-      </c>
-      <c r="C22" s="12" t="inlineStr">
-        <is>
-          <t>200 ml</t>
-        </is>
-      </c>
-      <c r="D22" s="12" t="inlineStr">
-        <is>
-          <t>1x/dia</t>
-        </is>
-      </c>
-      <c r="E22" s="13" t="inlineStr">
-        <is>
-          <t>Liberado</t>
-        </is>
-      </c>
-      <c r="F22" s="11" t="inlineStr"/>
+      <c r="B22" s="10" t="n"/>
+      <c r="C22" s="10" t="n"/>
+      <c r="D22" s="10" t="n"/>
+      <c r="E22" s="10" t="n"/>
+      <c r="F22" s="10" t="n"/>
     </row>
     <row r="23" ht="30" customHeight="1">
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>Queijo branco</t>
+          <t>Leite desnatado</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>30 g</t>
+          <t>200 ml</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>3x/semana</t>
-        </is>
-      </c>
-      <c r="E23" s="14" t="inlineStr">
-        <is>
-          <t>Moderar</t>
-        </is>
-      </c>
-      <c r="F23" s="11" t="inlineStr">
-        <is>
-          <t>Atenção ao sódio</t>
-        </is>
-      </c>
+          <t>1x/dia</t>
+        </is>
+      </c>
+      <c r="E23" s="13" t="inlineStr">
+        <is>
+          <t>Liberado</t>
+        </is>
+      </c>
+      <c r="F23" s="11" t="inlineStr"/>
     </row>
     <row r="24" ht="30" customHeight="1">
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>Iogurte natural (desnatado, sem açúcar)</t>
+          <t>Queijo branco</t>
         </is>
       </c>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>1 unidade</t>
+          <t>30 g</t>
         </is>
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
-          <t>1x/dia</t>
-        </is>
-      </c>
-      <c r="E24" s="13" t="inlineStr">
-        <is>
-          <t>Liberado</t>
+          <t>3x/semana</t>
+        </is>
+      </c>
+      <c r="E24" s="14" t="inlineStr">
+        <is>
+          <t>Moderar</t>
         </is>
       </c>
       <c r="F24" s="11" t="inlineStr">
         <is>
-          <t>Prefira sempre a versão sem açúcar adicionado</t>
+          <t>Atenção ao sódio</t>
         </is>
       </c>
     </row>
     <row r="25" ht="30" customHeight="1">
       <c r="B25" s="11" t="inlineStr">
         <is>
+          <t>Iogurte natural (desnatado, sem açúcar)</t>
+        </is>
+      </c>
+      <c r="C25" s="12" t="inlineStr">
+        <is>
+          <t>1 unidade</t>
+        </is>
+      </c>
+      <c r="D25" s="12" t="inlineStr">
+        <is>
+          <t>1x/dia</t>
+        </is>
+      </c>
+      <c r="E25" s="13" t="inlineStr">
+        <is>
+          <t>Liberado</t>
+        </is>
+      </c>
+      <c r="F25" s="11" t="inlineStr">
+        <is>
+          <t>Prefira sempre a versão sem açúcar adicionado</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="B26" s="11" t="inlineStr">
+        <is>
           <t>Requeijão</t>
         </is>
       </c>
-      <c r="C25" s="12" t="inlineStr">
+      <c r="C26" s="12" t="inlineStr">
         <is>
           <t>1 colher de sopa (≈15 g)</t>
         </is>
       </c>
-      <c r="D25" s="12" t="inlineStr">
+      <c r="D26" s="12" t="inlineStr">
         <is>
           <t>2x/semana</t>
         </is>
       </c>
-      <c r="E25" s="14" t="inlineStr">
+      <c r="E26" s="14" t="inlineStr">
         <is>
           <t>Moderar</t>
         </is>
       </c>
-      <c r="F25" s="11" t="inlineStr">
+      <c r="F26" s="11" t="inlineStr">
         <is>
           <t>Rico em gordura saturada e sódio; prefira a versão light. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="9" t="inlineStr">
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="9" t="inlineStr">
         <is>
           <t>Bebidas</t>
         </is>
       </c>
-      <c r="B26" s="10" t="n"/>
-      <c r="C26" s="10" t="n"/>
-      <c r="D26" s="10" t="n"/>
-      <c r="E26" s="10" t="n"/>
-      <c r="F26" s="10" t="n"/>
-    </row>
-    <row r="27" ht="30" customHeight="1">
-      <c r="B27" s="11" t="inlineStr">
-        <is>
-          <t>Água</t>
-        </is>
-      </c>
-      <c r="C27" s="12" t="inlineStr">
-        <is>
-          <t>à vontade</t>
-        </is>
-      </c>
-      <c r="D27" s="12" t="inlineStr">
-        <is>
-          <t>todos os dias</t>
-        </is>
-      </c>
-      <c r="E27" s="13" t="inlineStr">
-        <is>
-          <t>Liberado</t>
-        </is>
-      </c>
-      <c r="F27" s="11" t="inlineStr"/>
+      <c r="B27" s="10" t="n"/>
+      <c r="C27" s="10" t="n"/>
+      <c r="D27" s="10" t="n"/>
+      <c r="E27" s="10" t="n"/>
+      <c r="F27" s="10" t="n"/>
     </row>
     <row r="28" ht="30" customHeight="1">
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>Refrigerante zero</t>
+          <t>Água</t>
         </is>
       </c>
       <c r="C28" s="12" t="inlineStr">
         <is>
-          <t>200 ml</t>
+          <t>à vontade</t>
         </is>
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
-          <t>1x/dia</t>
-        </is>
-      </c>
-      <c r="E28" s="14" t="inlineStr">
-        <is>
-          <t>Moderar</t>
-        </is>
-      </c>
-      <c r="F28" s="11" t="inlineStr">
-        <is>
-          <t>Sugestão gerada por IA — confirmar com nutricionista/cardiologista</t>
-        </is>
-      </c>
+          <t>todos os dias</t>
+        </is>
+      </c>
+      <c r="E28" s="13" t="inlineStr">
+        <is>
+          <t>Liberado</t>
+        </is>
+      </c>
+      <c r="F28" s="11" t="inlineStr"/>
     </row>
     <row r="29" ht="30" customHeight="1">
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>Café sem açúcar</t>
+          <t>Refrigerante zero</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>1 xícara</t>
+          <t>200 ml</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>2x/dia</t>
-        </is>
-      </c>
-      <c r="E29" s="13" t="inlineStr">
-        <is>
-          <t>Liberado</t>
-        </is>
-      </c>
-      <c r="F29" s="11" t="inlineStr"/>
+          <t>1x/dia</t>
+        </is>
+      </c>
+      <c r="E29" s="14" t="inlineStr">
+        <is>
+          <t>Moderar</t>
+        </is>
+      </c>
+      <c r="F29" s="11" t="inlineStr">
+        <is>
+          <t>Sugestão gerada por IA — confirmar com nutricionista/cardiologista</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="30" customHeight="1">
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>Suco natural sem açúcar</t>
+          <t>Café sem açúcar</t>
         </is>
       </c>
       <c r="C30" s="12" t="inlineStr">
         <is>
-          <t>200 ml</t>
+          <t>1 xícara</t>
         </is>
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
-          <t>3x/semana</t>
-        </is>
-      </c>
-      <c r="E30" s="14" t="inlineStr">
-        <is>
-          <t>Moderar</t>
-        </is>
-      </c>
-      <c r="F30" s="11" t="inlineStr">
-        <is>
-          <t>Preferir a fruta inteira, que tem mais fibra</t>
-        </is>
-      </c>
+          <t>2x/dia</t>
+        </is>
+      </c>
+      <c r="E30" s="13" t="inlineStr">
+        <is>
+          <t>Liberado</t>
+        </is>
+      </c>
+      <c r="F30" s="11" t="inlineStr"/>
     </row>
     <row r="31" ht="30" customHeight="1">
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>Bebida alcoólica</t>
+          <t>Suco natural sem açúcar</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
+          <t>200 ml</t>
+        </is>
+      </c>
+      <c r="D31" s="12" t="inlineStr">
+        <is>
+          <t>3x/semana</t>
+        </is>
+      </c>
+      <c r="E31" s="14" t="inlineStr">
+        <is>
+          <t>Moderar</t>
+        </is>
+      </c>
+      <c r="F31" s="11" t="inlineStr">
+        <is>
+          <t>Preferir a fruta inteira, que tem mais fibra</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="30" customHeight="1">
+      <c r="B32" s="11" t="inlineStr">
+        <is>
+          <t>Suco de toranja / grapefruit</t>
+        </is>
+      </c>
+      <c r="C32" s="12" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D31" s="12" t="inlineStr">
+      <c r="D32" s="12" t="inlineStr">
         <is>
           <t>evitar</t>
         </is>
       </c>
-      <c r="E31" s="15" t="inlineStr">
+      <c r="E32" s="15" t="inlineStr">
         <is>
           <t>Evitar</t>
         </is>
       </c>
-      <c r="F31" s="11" t="inlineStr">
-        <is>
-          <t>Piora diretamente os triglicerídeos</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="20" customHeight="1">
-      <c r="A32" s="9" t="inlineStr">
-        <is>
-          <t>Doces e Sobremesas</t>
-        </is>
-      </c>
-      <c r="B32" s="10" t="n"/>
-      <c r="C32" s="10" t="n"/>
-      <c r="D32" s="10" t="n"/>
-      <c r="E32" s="10" t="n"/>
-      <c r="F32" s="10" t="n"/>
+      <c r="F32" s="11" t="inlineStr">
+        <is>
+          <t>Interage com o Ticagrelor (aumenta o nível do remédio no sangue e o risco de sangramento) — evitar completamente.</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="30" customHeight="1">
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>Açúcar refinado</t>
+          <t>Bebida alcoólica</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
@@ -1593,213 +1656,279 @@
       </c>
       <c r="F33" s="11" t="inlineStr">
         <is>
-          <t>Impacto direto nos triglicerídeos</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="30" customHeight="1">
-      <c r="B34" s="11" t="inlineStr">
-        <is>
-          <t>Doces industrializados</t>
-        </is>
-      </c>
-      <c r="C34" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D34" s="12" t="inlineStr">
-        <is>
-          <t>evitar</t>
-        </is>
-      </c>
-      <c r="E34" s="15" t="inlineStr">
-        <is>
-          <t>Evitar</t>
-        </is>
-      </c>
-      <c r="F34" s="11" t="inlineStr"/>
+          <t>Piora diretamente os triglicerídeos; soma-se ao risco de sangramento da Aspirina + Ticagrelor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="9" t="inlineStr">
+        <is>
+          <t>Doces e Sobremesas</t>
+        </is>
+      </c>
+      <c r="B34" s="10" t="n"/>
+      <c r="C34" s="10" t="n"/>
+      <c r="D34" s="10" t="n"/>
+      <c r="E34" s="10" t="n"/>
+      <c r="F34" s="10" t="n"/>
     </row>
     <row r="35" ht="30" customHeight="1">
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>Chocolate amargo (70%+)</t>
+          <t>Açúcar refinado</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>10 g</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
-          <t>2x/semana</t>
-        </is>
-      </c>
-      <c r="E35" s="14" t="inlineStr">
-        <is>
-          <t>Moderar</t>
+          <t>evitar</t>
+        </is>
+      </c>
+      <c r="E35" s="15" t="inlineStr">
+        <is>
+          <t>Evitar</t>
         </is>
       </c>
       <c r="F35" s="11" t="inlineStr">
         <is>
-          <t>Sugestão gerada por IA — confirmar com nutricionista/cardiologista</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="9" t="inlineStr">
-        <is>
-          <t>Gorduras e Temperos</t>
-        </is>
-      </c>
-      <c r="B36" s="10" t="n"/>
-      <c r="C36" s="10" t="n"/>
-      <c r="D36" s="10" t="n"/>
-      <c r="E36" s="10" t="n"/>
-      <c r="F36" s="10" t="n"/>
+          <t>Impacto direto nos triglicerídeos</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="30" customHeight="1">
+      <c r="B36" s="11" t="inlineStr">
+        <is>
+          <t>Doces industrializados</t>
+        </is>
+      </c>
+      <c r="C36" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D36" s="12" t="inlineStr">
+        <is>
+          <t>evitar</t>
+        </is>
+      </c>
+      <c r="E36" s="15" t="inlineStr">
+        <is>
+          <t>Evitar</t>
+        </is>
+      </c>
+      <c r="F36" s="11" t="inlineStr"/>
     </row>
     <row r="37" ht="30" customHeight="1">
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>Azeite de oliva extra virgem</t>
+          <t>Chocolate amargo (70%+)</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>1-2 colheres de sopa</t>
+          <t>10 g</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
-          <t>1x/dia</t>
-        </is>
-      </c>
-      <c r="E37" s="13" t="inlineStr">
-        <is>
-          <t>Liberado</t>
-        </is>
-      </c>
-      <c r="F37" s="11" t="inlineStr"/>
-    </row>
-    <row r="38" ht="30" customHeight="1">
-      <c r="B38" s="11" t="inlineStr">
-        <is>
-          <t>Manteiga</t>
-        </is>
-      </c>
-      <c r="C38" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D38" s="12" t="inlineStr">
-        <is>
-          <t>evitar</t>
-        </is>
-      </c>
-      <c r="E38" s="15" t="inlineStr">
-        <is>
-          <t>Evitar</t>
-        </is>
-      </c>
-      <c r="F38" s="11" t="inlineStr">
-        <is>
-          <t>Preferir azeite</t>
-        </is>
-      </c>
+          <t>2x/semana</t>
+        </is>
+      </c>
+      <c r="E37" s="14" t="inlineStr">
+        <is>
+          <t>Moderar</t>
+        </is>
+      </c>
+      <c r="F37" s="11" t="inlineStr">
+        <is>
+          <t>Sugestão gerada por IA — confirmar com nutricionista/cardiologista</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="9" t="inlineStr">
+        <is>
+          <t>Gorduras e Temperos</t>
+        </is>
+      </c>
+      <c r="B38" s="10" t="n"/>
+      <c r="C38" s="10" t="n"/>
+      <c r="D38" s="10" t="n"/>
+      <c r="E38" s="10" t="n"/>
+      <c r="F38" s="10" t="n"/>
     </row>
     <row r="39" ht="30" customHeight="1">
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>Sal</t>
+          <t>Azeite de oliva extra virgem</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>&lt; 5 g no total</t>
+          <t>1-2 colheres de sopa</t>
         </is>
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
-          <t>todos os dias</t>
-        </is>
-      </c>
-      <c r="E39" s="14" t="inlineStr">
-        <is>
-          <t>Moderar</t>
-        </is>
-      </c>
-      <c r="F39" s="11" t="inlineStr">
-        <is>
-          <t>Somar sal de cozinha + industrializados</t>
-        </is>
-      </c>
+          <t>1x/dia</t>
+        </is>
+      </c>
+      <c r="E39" s="13" t="inlineStr">
+        <is>
+          <t>Liberado</t>
+        </is>
+      </c>
+      <c r="F39" s="11" t="inlineStr"/>
     </row>
     <row r="40" ht="30" customHeight="1">
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>Ervas e temperos naturais</t>
+          <t>Manteiga</t>
         </is>
       </c>
       <c r="C40" s="12" t="inlineStr">
         <is>
-          <t>à vontade</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D40" s="12" t="inlineStr">
         <is>
+          <t>evitar</t>
+        </is>
+      </c>
+      <c r="E40" s="15" t="inlineStr">
+        <is>
+          <t>Evitar</t>
+        </is>
+      </c>
+      <c r="F40" s="11" t="inlineStr">
+        <is>
+          <t>Preferir azeite</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="30" customHeight="1">
+      <c r="B41" s="11" t="inlineStr">
+        <is>
+          <t>Sal</t>
+        </is>
+      </c>
+      <c r="C41" s="12" t="inlineStr">
+        <is>
+          <t>&lt; 5 g no total</t>
+        </is>
+      </c>
+      <c r="D41" s="12" t="inlineStr">
+        <is>
           <t>todos os dias</t>
         </is>
       </c>
-      <c r="E40" s="13" t="inlineStr">
-        <is>
-          <t>Liberado</t>
-        </is>
-      </c>
-      <c r="F40" s="11" t="inlineStr"/>
-    </row>
-    <row r="41" ht="20" customHeight="1">
-      <c r="A41" s="9" t="inlineStr">
-        <is>
-          <t>Vegetais e Verduras</t>
-        </is>
-      </c>
-      <c r="B41" s="10" t="n"/>
-      <c r="C41" s="10" t="n"/>
-      <c r="D41" s="10" t="n"/>
-      <c r="E41" s="10" t="n"/>
-      <c r="F41" s="10" t="n"/>
+      <c r="E41" s="14" t="inlineStr">
+        <is>
+          <t>Moderar</t>
+        </is>
+      </c>
+      <c r="F41" s="11" t="inlineStr">
+        <is>
+          <t>Somar sal de cozinha + industrializados</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="30" customHeight="1">
       <c r="B42" s="11" t="inlineStr">
         <is>
+          <t>Sal light / substituto de sal (cloreto de potássio)</t>
+        </is>
+      </c>
+      <c r="C42" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D42" s="12" t="inlineStr">
+        <is>
+          <t>evitar</t>
+        </is>
+      </c>
+      <c r="E42" s="15" t="inlineStr">
+        <is>
+          <t>Evitar</t>
+        </is>
+      </c>
+      <c r="F42" s="11" t="inlineStr">
+        <is>
+          <t>Enalapril já tende a elevar o potássio; combinado com esse produto o risco de hipercalemia aumenta, ainda mais com a função renal pendente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="30" customHeight="1">
+      <c r="B43" s="11" t="inlineStr">
+        <is>
+          <t>Ervas e temperos naturais</t>
+        </is>
+      </c>
+      <c r="C43" s="12" t="inlineStr">
+        <is>
+          <t>à vontade</t>
+        </is>
+      </c>
+      <c r="D43" s="12" t="inlineStr">
+        <is>
+          <t>todos os dias</t>
+        </is>
+      </c>
+      <c r="E43" s="13" t="inlineStr">
+        <is>
+          <t>Liberado</t>
+        </is>
+      </c>
+      <c r="F43" s="11" t="inlineStr"/>
+    </row>
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="9" t="inlineStr">
+        <is>
+          <t>Vegetais e Verduras</t>
+        </is>
+      </c>
+      <c r="B44" s="10" t="n"/>
+      <c r="C44" s="10" t="n"/>
+      <c r="D44" s="10" t="n"/>
+      <c r="E44" s="10" t="n"/>
+      <c r="F44" s="10" t="n"/>
+    </row>
+    <row r="45" ht="30" customHeight="1">
+      <c r="B45" s="11" t="inlineStr">
+        <is>
           <t>Vegetais e verduras em geral</t>
         </is>
       </c>
-      <c r="C42" s="12" t="inlineStr">
+      <c r="C45" s="12" t="inlineStr">
         <is>
           <t>à vontade</t>
         </is>
       </c>
-      <c r="D42" s="12" t="inlineStr">
+      <c r="D45" s="12" t="inlineStr">
         <is>
           <t>todos os dias</t>
         </is>
       </c>
-      <c r="E42" s="13" t="inlineStr">
+      <c r="E45" s="13" t="inlineStr">
         <is>
           <t>Liberado</t>
         </is>
       </c>
-      <c r="F42" s="11" t="inlineStr">
+      <c r="F45" s="11" t="inlineStr">
         <is>
           <t>Se entrar anticoagulante na medicação, revisar consumo de verde-escuros ricos em vitamina K</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="30" customHeight="1">
-      <c r="A44" s="16" t="inlineStr">
+    <row r="47" ht="30" customHeight="1">
+      <c r="A47" s="16" t="inlineStr">
         <is>
           <t>Lista com os alimentos acrescentados até agora — não é uma lista completa. Use a skill 'adicionar-alimento' (ex.: "adicione sucrilhos") para ir acrescentando novos itens aos poucos.</t>
         </is>
@@ -1807,16 +1936,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="A41:F41"/>
-    <mergeCell ref="A10:F10"/>
-    <mergeCell ref="A36:F36"/>
+    <mergeCell ref="A38:F38"/>
+    <mergeCell ref="A16:F16"/>
+    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="A47:F47"/>
     <mergeCell ref="A44:F44"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A32:F32"/>
+    <mergeCell ref="A27:F27"/>
+    <mergeCell ref="A22:F22"/>
+    <mergeCell ref="A34:F34"/>
     <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A26:F26"/>
-    <mergeCell ref="A21:F21"/>
-    <mergeCell ref="A15:F15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/planilha/plano-alimentar-pos-infarto.xlsx
+++ b/planilha/plano-alimentar-pos-infarto.xlsx
@@ -10,6 +10,8 @@
     <sheet name="Cuidados na Alimentação" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Plano Geral - Restaurante" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Alimentos e Quantidades" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Montar Refeição" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Ref_Alimentos" sheetId="5" state="hidden" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -63,6 +65,41 @@
       <name val="Arial"/>
       <i val="1"/>
       <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00C0392B"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="00666666"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="001F4E5F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="8">
@@ -129,7 +166,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -177,10 +214,91 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="4">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C6E0B4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFE699"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00F4B6B6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <b val="1"/>
+        <color rgb="00C0392B"/>
+        <sz val="10.5"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FCE4D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -1949,4 +2067,3181 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H37"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Montar uma Refeição — escolha os alimentos de cada refeição</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="48" customHeight="1">
+      <c r="A2" s="16" t="inlineStr">
+        <is>
+          <t>Escolha o alimento no menu suspenso da coluna 'Alimento' — a lista já vem filtrada por refeição (por isso não aparece arroz/feijão no café da manhã, por exemplo) e com os alimentos Liberados primeiro. Categoria, Porção sugerida e Classificação preenchem sozinhas. 'Sugestão' mostra um alimento que costuma combinar bem com o item escolhido logo acima (é uma dica, não é obrigatório escolher). Se 'Conflito' mostrar '⚠ Conflito', evite reunir esses itens na mesma refeição.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="17" t="inlineStr">
+        <is>
+          <t>Legenda:</t>
+        </is>
+      </c>
+      <c r="B3" s="18" t="inlineStr">
+        <is>
+          <t>Liberado</t>
+        </is>
+      </c>
+      <c r="C3" s="19" t="inlineStr">
+        <is>
+          <t>Moderar</t>
+        </is>
+      </c>
+      <c r="D3" s="20" t="inlineStr">
+        <is>
+          <t>Evitar</t>
+        </is>
+      </c>
+      <c r="F3" s="21" t="inlineStr">
+        <is>
+          <t>⚠ Conflito</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="22" t="inlineStr">
+        <is>
+          <t>CAFÉ DA MANHÃ</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="n"/>
+      <c r="C5" s="10" t="n"/>
+      <c r="D5" s="10" t="n"/>
+      <c r="E5" s="10" t="n"/>
+      <c r="F5" s="10" t="n"/>
+      <c r="G5" s="10" t="n"/>
+      <c r="H5" s="10" t="n"/>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="23" t="inlineStr">
+        <is>
+          <t>Nº</t>
+        </is>
+      </c>
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>Alimento</t>
+        </is>
+      </c>
+      <c r="C6" s="23" t="inlineStr">
+        <is>
+          <t>Categoria</t>
+        </is>
+      </c>
+      <c r="D6" s="23" t="inlineStr">
+        <is>
+          <t>Porção sugerida</t>
+        </is>
+      </c>
+      <c r="E6" s="23" t="inlineStr">
+        <is>
+          <t>Quantidade a comer</t>
+        </is>
+      </c>
+      <c r="F6" s="23" t="inlineStr">
+        <is>
+          <t>Classificação</t>
+        </is>
+      </c>
+      <c r="G6" s="23" t="inlineStr">
+        <is>
+          <t>Sugestão (com base no item anterior)</t>
+        </is>
+      </c>
+      <c r="H6" s="23" t="inlineStr">
+        <is>
+          <t>Conflito</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="26" customHeight="1">
+      <c r="A7" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="25" t="n"/>
+      <c r="C7" s="26">
+        <f>IFERROR(INDEX(Ref_Alimentos!$B$2:$B$101,MATCH($B7,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D7" s="27">
+        <f>IFERROR(INDEX(Ref_Alimentos!$D$2:$D$101,MATCH($B7,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E7" s="24" t="n"/>
+      <c r="F7" s="28">
+        <f>IFERROR(INDEX(Ref_Alimentos!$C$2:$C$101,MATCH($B7,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G7" s="29" t="inlineStr"/>
+      <c r="H7" s="30">
+        <f>IF($B7="","",IF($F7="Evitar","⚠ Conflito",IF(AND($F7="Moderar",SUMPRODUCT(($B$7:$B$11&lt;&gt;"")*(ROW($B$7:$B$11)&lt;&gt;ROW($B7))*(($F$7:$F$11="Moderar")+($F$7:$F$11="Evitar")))&gt;0),"⚠ Conflito","")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="26" customHeight="1">
+      <c r="A8" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" s="25" t="n"/>
+      <c r="C8" s="26">
+        <f>IFERROR(INDEX(Ref_Alimentos!$B$2:$B$101,MATCH($B8,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D8" s="27">
+        <f>IFERROR(INDEX(Ref_Alimentos!$D$2:$D$101,MATCH($B8,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E8" s="24" t="n"/>
+      <c r="F8" s="28">
+        <f>IFERROR(INDEX(Ref_Alimentos!$C$2:$C$101,MATCH($B8,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G8" s="29">
+        <f>IF($B7="","",IFERROR(INDEX(Ref_Alimentos!$R$2:$R$60,MATCH(IFERROR(INDEX(Ref_Alimentos!$U$2:$U$9,MATCH($C7,Ref_Alimentos!$T$2:$T$9,0)),"")&amp;"|"&amp;"Café da manhã",Ref_Alimentos!$Q$2:$Q$60,0)),""))</f>
+        <v/>
+      </c>
+      <c r="H8" s="30">
+        <f>IF($B8="","",IF($F8="Evitar","⚠ Conflito",IF(AND($F8="Moderar",SUMPRODUCT(($B$7:$B$11&lt;&gt;"")*(ROW($B$7:$B$11)&lt;&gt;ROW($B8))*(($F$7:$F$11="Moderar")+($F$7:$F$11="Evitar")))&gt;0),"⚠ Conflito","")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="26" customHeight="1">
+      <c r="A9" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="B9" s="25" t="n"/>
+      <c r="C9" s="26">
+        <f>IFERROR(INDEX(Ref_Alimentos!$B$2:$B$101,MATCH($B9,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D9" s="27">
+        <f>IFERROR(INDEX(Ref_Alimentos!$D$2:$D$101,MATCH($B9,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E9" s="24" t="n"/>
+      <c r="F9" s="28">
+        <f>IFERROR(INDEX(Ref_Alimentos!$C$2:$C$101,MATCH($B9,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G9" s="29">
+        <f>IF($B8="","",IFERROR(INDEX(Ref_Alimentos!$R$2:$R$60,MATCH(IFERROR(INDEX(Ref_Alimentos!$U$2:$U$9,MATCH($C8,Ref_Alimentos!$T$2:$T$9,0)),"")&amp;"|"&amp;"Café da manhã",Ref_Alimentos!$Q$2:$Q$60,0)),""))</f>
+        <v/>
+      </c>
+      <c r="H9" s="30">
+        <f>IF($B9="","",IF($F9="Evitar","⚠ Conflito",IF(AND($F9="Moderar",SUMPRODUCT(($B$7:$B$11&lt;&gt;"")*(ROW($B$7:$B$11)&lt;&gt;ROW($B9))*(($F$7:$F$11="Moderar")+($F$7:$F$11="Evitar")))&gt;0),"⚠ Conflito","")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="26" customHeight="1">
+      <c r="A10" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="B10" s="25" t="n"/>
+      <c r="C10" s="26">
+        <f>IFERROR(INDEX(Ref_Alimentos!$B$2:$B$101,MATCH($B10,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D10" s="27">
+        <f>IFERROR(INDEX(Ref_Alimentos!$D$2:$D$101,MATCH($B10,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E10" s="24" t="n"/>
+      <c r="F10" s="28">
+        <f>IFERROR(INDEX(Ref_Alimentos!$C$2:$C$101,MATCH($B10,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G10" s="29">
+        <f>IF($B9="","",IFERROR(INDEX(Ref_Alimentos!$R$2:$R$60,MATCH(IFERROR(INDEX(Ref_Alimentos!$U$2:$U$9,MATCH($C9,Ref_Alimentos!$T$2:$T$9,0)),"")&amp;"|"&amp;"Café da manhã",Ref_Alimentos!$Q$2:$Q$60,0)),""))</f>
+        <v/>
+      </c>
+      <c r="H10" s="30">
+        <f>IF($B10="","",IF($F10="Evitar","⚠ Conflito",IF(AND($F10="Moderar",SUMPRODUCT(($B$7:$B$11&lt;&gt;"")*(ROW($B$7:$B$11)&lt;&gt;ROW($B10))*(($F$7:$F$11="Moderar")+($F$7:$F$11="Evitar")))&gt;0),"⚠ Conflito","")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="26" customHeight="1">
+      <c r="A11" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="B11" s="25" t="n"/>
+      <c r="C11" s="26">
+        <f>IFERROR(INDEX(Ref_Alimentos!$B$2:$B$101,MATCH($B11,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D11" s="27">
+        <f>IFERROR(INDEX(Ref_Alimentos!$D$2:$D$101,MATCH($B11,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E11" s="24" t="n"/>
+      <c r="F11" s="28">
+        <f>IFERROR(INDEX(Ref_Alimentos!$C$2:$C$101,MATCH($B11,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G11" s="29">
+        <f>IF($B10="","",IFERROR(INDEX(Ref_Alimentos!$R$2:$R$60,MATCH(IFERROR(INDEX(Ref_Alimentos!$U$2:$U$9,MATCH($C10,Ref_Alimentos!$T$2:$T$9,0)),"")&amp;"|"&amp;"Café da manhã",Ref_Alimentos!$Q$2:$Q$60,0)),""))</f>
+        <v/>
+      </c>
+      <c r="H11" s="30">
+        <f>IF($B11="","",IF($F11="Evitar","⚠ Conflito",IF(AND($F11="Moderar",SUMPRODUCT(($B$7:$B$11&lt;&gt;"")*(ROW($B$7:$B$11)&lt;&gt;ROW($B11))*(($F$7:$F$11="Moderar")+($F$7:$F$11="Evitar")))&gt;0),"⚠ Conflito","")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="22" t="inlineStr">
+        <is>
+          <t>ALMOÇO</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="n"/>
+      <c r="C13" s="10" t="n"/>
+      <c r="D13" s="10" t="n"/>
+      <c r="E13" s="10" t="n"/>
+      <c r="F13" s="10" t="n"/>
+      <c r="G13" s="10" t="n"/>
+      <c r="H13" s="10" t="n"/>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="23" t="inlineStr">
+        <is>
+          <t>Nº</t>
+        </is>
+      </c>
+      <c r="B14" s="23" t="inlineStr">
+        <is>
+          <t>Alimento</t>
+        </is>
+      </c>
+      <c r="C14" s="23" t="inlineStr">
+        <is>
+          <t>Categoria</t>
+        </is>
+      </c>
+      <c r="D14" s="23" t="inlineStr">
+        <is>
+          <t>Porção sugerida</t>
+        </is>
+      </c>
+      <c r="E14" s="23" t="inlineStr">
+        <is>
+          <t>Quantidade a comer</t>
+        </is>
+      </c>
+      <c r="F14" s="23" t="inlineStr">
+        <is>
+          <t>Classificação</t>
+        </is>
+      </c>
+      <c r="G14" s="23" t="inlineStr">
+        <is>
+          <t>Sugestão (com base no item anterior)</t>
+        </is>
+      </c>
+      <c r="H14" s="23" t="inlineStr">
+        <is>
+          <t>Conflito</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="26" customHeight="1">
+      <c r="A15" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="B15" s="25" t="n"/>
+      <c r="C15" s="26">
+        <f>IFERROR(INDEX(Ref_Alimentos!$B$2:$B$101,MATCH($B15,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D15" s="27">
+        <f>IFERROR(INDEX(Ref_Alimentos!$D$2:$D$101,MATCH($B15,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E15" s="24" t="n"/>
+      <c r="F15" s="28">
+        <f>IFERROR(INDEX(Ref_Alimentos!$C$2:$C$101,MATCH($B15,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G15" s="29" t="inlineStr"/>
+      <c r="H15" s="30">
+        <f>IF($B15="","",IF($F15="Evitar","⚠ Conflito",IF(AND($F15="Moderar",SUMPRODUCT(($B$15:$B$19&lt;&gt;"")*(ROW($B$15:$B$19)&lt;&gt;ROW($B15))*(($F$15:$F$19="Moderar")+($F$15:$F$19="Evitar")))&gt;0),"⚠ Conflito","")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="26" customHeight="1">
+      <c r="A16" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="B16" s="25" t="n"/>
+      <c r="C16" s="26">
+        <f>IFERROR(INDEX(Ref_Alimentos!$B$2:$B$101,MATCH($B16,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D16" s="27">
+        <f>IFERROR(INDEX(Ref_Alimentos!$D$2:$D$101,MATCH($B16,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E16" s="24" t="n"/>
+      <c r="F16" s="28">
+        <f>IFERROR(INDEX(Ref_Alimentos!$C$2:$C$101,MATCH($B16,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G16" s="29">
+        <f>IF($B15="","",IFERROR(INDEX(Ref_Alimentos!$R$2:$R$60,MATCH(IFERROR(INDEX(Ref_Alimentos!$U$2:$U$9,MATCH($C15,Ref_Alimentos!$T$2:$T$9,0)),"")&amp;"|"&amp;"Almoço",Ref_Alimentos!$Q$2:$Q$60,0)),""))</f>
+        <v/>
+      </c>
+      <c r="H16" s="30">
+        <f>IF($B16="","",IF($F16="Evitar","⚠ Conflito",IF(AND($F16="Moderar",SUMPRODUCT(($B$15:$B$19&lt;&gt;"")*(ROW($B$15:$B$19)&lt;&gt;ROW($B16))*(($F$15:$F$19="Moderar")+($F$15:$F$19="Evitar")))&gt;0),"⚠ Conflito","")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="26" customHeight="1">
+      <c r="A17" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="B17" s="25" t="n"/>
+      <c r="C17" s="26">
+        <f>IFERROR(INDEX(Ref_Alimentos!$B$2:$B$101,MATCH($B17,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D17" s="27">
+        <f>IFERROR(INDEX(Ref_Alimentos!$D$2:$D$101,MATCH($B17,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E17" s="24" t="n"/>
+      <c r="F17" s="28">
+        <f>IFERROR(INDEX(Ref_Alimentos!$C$2:$C$101,MATCH($B17,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G17" s="29">
+        <f>IF($B16="","",IFERROR(INDEX(Ref_Alimentos!$R$2:$R$60,MATCH(IFERROR(INDEX(Ref_Alimentos!$U$2:$U$9,MATCH($C16,Ref_Alimentos!$T$2:$T$9,0)),"")&amp;"|"&amp;"Almoço",Ref_Alimentos!$Q$2:$Q$60,0)),""))</f>
+        <v/>
+      </c>
+      <c r="H17" s="30">
+        <f>IF($B17="","",IF($F17="Evitar","⚠ Conflito",IF(AND($F17="Moderar",SUMPRODUCT(($B$15:$B$19&lt;&gt;"")*(ROW($B$15:$B$19)&lt;&gt;ROW($B17))*(($F$15:$F$19="Moderar")+($F$15:$F$19="Evitar")))&gt;0),"⚠ Conflito","")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="26" customHeight="1">
+      <c r="A18" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="B18" s="25" t="n"/>
+      <c r="C18" s="26">
+        <f>IFERROR(INDEX(Ref_Alimentos!$B$2:$B$101,MATCH($B18,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D18" s="27">
+        <f>IFERROR(INDEX(Ref_Alimentos!$D$2:$D$101,MATCH($B18,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E18" s="24" t="n"/>
+      <c r="F18" s="28">
+        <f>IFERROR(INDEX(Ref_Alimentos!$C$2:$C$101,MATCH($B18,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G18" s="29">
+        <f>IF($B17="","",IFERROR(INDEX(Ref_Alimentos!$R$2:$R$60,MATCH(IFERROR(INDEX(Ref_Alimentos!$U$2:$U$9,MATCH($C17,Ref_Alimentos!$T$2:$T$9,0)),"")&amp;"|"&amp;"Almoço",Ref_Alimentos!$Q$2:$Q$60,0)),""))</f>
+        <v/>
+      </c>
+      <c r="H18" s="30">
+        <f>IF($B18="","",IF($F18="Evitar","⚠ Conflito",IF(AND($F18="Moderar",SUMPRODUCT(($B$15:$B$19&lt;&gt;"")*(ROW($B$15:$B$19)&lt;&gt;ROW($B18))*(($F$15:$F$19="Moderar")+($F$15:$F$19="Evitar")))&gt;0),"⚠ Conflito","")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="26" customHeight="1">
+      <c r="A19" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="B19" s="25" t="n"/>
+      <c r="C19" s="26">
+        <f>IFERROR(INDEX(Ref_Alimentos!$B$2:$B$101,MATCH($B19,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D19" s="27">
+        <f>IFERROR(INDEX(Ref_Alimentos!$D$2:$D$101,MATCH($B19,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E19" s="24" t="n"/>
+      <c r="F19" s="28">
+        <f>IFERROR(INDEX(Ref_Alimentos!$C$2:$C$101,MATCH($B19,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G19" s="29">
+        <f>IF($B18="","",IFERROR(INDEX(Ref_Alimentos!$R$2:$R$60,MATCH(IFERROR(INDEX(Ref_Alimentos!$U$2:$U$9,MATCH($C18,Ref_Alimentos!$T$2:$T$9,0)),"")&amp;"|"&amp;"Almoço",Ref_Alimentos!$Q$2:$Q$60,0)),""))</f>
+        <v/>
+      </c>
+      <c r="H19" s="30">
+        <f>IF($B19="","",IF($F19="Evitar","⚠ Conflito",IF(AND($F19="Moderar",SUMPRODUCT(($B$15:$B$19&lt;&gt;"")*(ROW($B$15:$B$19)&lt;&gt;ROW($B19))*(($F$15:$F$19="Moderar")+($F$15:$F$19="Evitar")))&gt;0),"⚠ Conflito","")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="22" t="inlineStr">
+        <is>
+          <t>LANCHE</t>
+        </is>
+      </c>
+      <c r="B21" s="10" t="n"/>
+      <c r="C21" s="10" t="n"/>
+      <c r="D21" s="10" t="n"/>
+      <c r="E21" s="10" t="n"/>
+      <c r="F21" s="10" t="n"/>
+      <c r="G21" s="10" t="n"/>
+      <c r="H21" s="10" t="n"/>
+    </row>
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="23" t="inlineStr">
+        <is>
+          <t>Nº</t>
+        </is>
+      </c>
+      <c r="B22" s="23" t="inlineStr">
+        <is>
+          <t>Alimento</t>
+        </is>
+      </c>
+      <c r="C22" s="23" t="inlineStr">
+        <is>
+          <t>Categoria</t>
+        </is>
+      </c>
+      <c r="D22" s="23" t="inlineStr">
+        <is>
+          <t>Porção sugerida</t>
+        </is>
+      </c>
+      <c r="E22" s="23" t="inlineStr">
+        <is>
+          <t>Quantidade a comer</t>
+        </is>
+      </c>
+      <c r="F22" s="23" t="inlineStr">
+        <is>
+          <t>Classificação</t>
+        </is>
+      </c>
+      <c r="G22" s="23" t="inlineStr">
+        <is>
+          <t>Sugestão (com base no item anterior)</t>
+        </is>
+      </c>
+      <c r="H22" s="23" t="inlineStr">
+        <is>
+          <t>Conflito</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="26" customHeight="1">
+      <c r="A23" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="B23" s="25" t="n"/>
+      <c r="C23" s="26">
+        <f>IFERROR(INDEX(Ref_Alimentos!$B$2:$B$101,MATCH($B23,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D23" s="27">
+        <f>IFERROR(INDEX(Ref_Alimentos!$D$2:$D$101,MATCH($B23,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E23" s="24" t="n"/>
+      <c r="F23" s="28">
+        <f>IFERROR(INDEX(Ref_Alimentos!$C$2:$C$101,MATCH($B23,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G23" s="29" t="inlineStr"/>
+      <c r="H23" s="30">
+        <f>IF($B23="","",IF($F23="Evitar","⚠ Conflito",IF(AND($F23="Moderar",SUMPRODUCT(($B$23:$B$27&lt;&gt;"")*(ROW($B$23:$B$27)&lt;&gt;ROW($B23))*(($F$23:$F$27="Moderar")+($F$23:$F$27="Evitar")))&gt;0),"⚠ Conflito","")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="26" customHeight="1">
+      <c r="A24" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="B24" s="25" t="n"/>
+      <c r="C24" s="26">
+        <f>IFERROR(INDEX(Ref_Alimentos!$B$2:$B$101,MATCH($B24,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D24" s="27">
+        <f>IFERROR(INDEX(Ref_Alimentos!$D$2:$D$101,MATCH($B24,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E24" s="24" t="n"/>
+      <c r="F24" s="28">
+        <f>IFERROR(INDEX(Ref_Alimentos!$C$2:$C$101,MATCH($B24,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G24" s="29">
+        <f>IF($B23="","",IFERROR(INDEX(Ref_Alimentos!$R$2:$R$60,MATCH(IFERROR(INDEX(Ref_Alimentos!$U$2:$U$9,MATCH($C23,Ref_Alimentos!$T$2:$T$9,0)),"")&amp;"|"&amp;"Lanche",Ref_Alimentos!$Q$2:$Q$60,0)),""))</f>
+        <v/>
+      </c>
+      <c r="H24" s="30">
+        <f>IF($B24="","",IF($F24="Evitar","⚠ Conflito",IF(AND($F24="Moderar",SUMPRODUCT(($B$23:$B$27&lt;&gt;"")*(ROW($B$23:$B$27)&lt;&gt;ROW($B24))*(($F$23:$F$27="Moderar")+($F$23:$F$27="Evitar")))&gt;0),"⚠ Conflito","")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="26" customHeight="1">
+      <c r="A25" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="B25" s="25" t="n"/>
+      <c r="C25" s="26">
+        <f>IFERROR(INDEX(Ref_Alimentos!$B$2:$B$101,MATCH($B25,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D25" s="27">
+        <f>IFERROR(INDEX(Ref_Alimentos!$D$2:$D$101,MATCH($B25,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E25" s="24" t="n"/>
+      <c r="F25" s="28">
+        <f>IFERROR(INDEX(Ref_Alimentos!$C$2:$C$101,MATCH($B25,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G25" s="29">
+        <f>IF($B24="","",IFERROR(INDEX(Ref_Alimentos!$R$2:$R$60,MATCH(IFERROR(INDEX(Ref_Alimentos!$U$2:$U$9,MATCH($C24,Ref_Alimentos!$T$2:$T$9,0)),"")&amp;"|"&amp;"Lanche",Ref_Alimentos!$Q$2:$Q$60,0)),""))</f>
+        <v/>
+      </c>
+      <c r="H25" s="30">
+        <f>IF($B25="","",IF($F25="Evitar","⚠ Conflito",IF(AND($F25="Moderar",SUMPRODUCT(($B$23:$B$27&lt;&gt;"")*(ROW($B$23:$B$27)&lt;&gt;ROW($B25))*(($F$23:$F$27="Moderar")+($F$23:$F$27="Evitar")))&gt;0),"⚠ Conflito","")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="26" customHeight="1">
+      <c r="A26" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="B26" s="25" t="n"/>
+      <c r="C26" s="26">
+        <f>IFERROR(INDEX(Ref_Alimentos!$B$2:$B$101,MATCH($B26,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D26" s="27">
+        <f>IFERROR(INDEX(Ref_Alimentos!$D$2:$D$101,MATCH($B26,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E26" s="24" t="n"/>
+      <c r="F26" s="28">
+        <f>IFERROR(INDEX(Ref_Alimentos!$C$2:$C$101,MATCH($B26,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G26" s="29">
+        <f>IF($B25="","",IFERROR(INDEX(Ref_Alimentos!$R$2:$R$60,MATCH(IFERROR(INDEX(Ref_Alimentos!$U$2:$U$9,MATCH($C25,Ref_Alimentos!$T$2:$T$9,0)),"")&amp;"|"&amp;"Lanche",Ref_Alimentos!$Q$2:$Q$60,0)),""))</f>
+        <v/>
+      </c>
+      <c r="H26" s="30">
+        <f>IF($B26="","",IF($F26="Evitar","⚠ Conflito",IF(AND($F26="Moderar",SUMPRODUCT(($B$23:$B$27&lt;&gt;"")*(ROW($B$23:$B$27)&lt;&gt;ROW($B26))*(($F$23:$F$27="Moderar")+($F$23:$F$27="Evitar")))&gt;0),"⚠ Conflito","")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="26" customHeight="1">
+      <c r="A27" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="B27" s="25" t="n"/>
+      <c r="C27" s="26">
+        <f>IFERROR(INDEX(Ref_Alimentos!$B$2:$B$101,MATCH($B27,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D27" s="27">
+        <f>IFERROR(INDEX(Ref_Alimentos!$D$2:$D$101,MATCH($B27,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E27" s="24" t="n"/>
+      <c r="F27" s="28">
+        <f>IFERROR(INDEX(Ref_Alimentos!$C$2:$C$101,MATCH($B27,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G27" s="29">
+        <f>IF($B26="","",IFERROR(INDEX(Ref_Alimentos!$R$2:$R$60,MATCH(IFERROR(INDEX(Ref_Alimentos!$U$2:$U$9,MATCH($C26,Ref_Alimentos!$T$2:$T$9,0)),"")&amp;"|"&amp;"Lanche",Ref_Alimentos!$Q$2:$Q$60,0)),""))</f>
+        <v/>
+      </c>
+      <c r="H27" s="30">
+        <f>IF($B27="","",IF($F27="Evitar","⚠ Conflito",IF(AND($F27="Moderar",SUMPRODUCT(($B$23:$B$27&lt;&gt;"")*(ROW($B$23:$B$27)&lt;&gt;ROW($B27))*(($F$23:$F$27="Moderar")+($F$23:$F$27="Evitar")))&gt;0),"⚠ Conflito","")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="22" t="inlineStr">
+        <is>
+          <t>JANTAR</t>
+        </is>
+      </c>
+      <c r="B29" s="10" t="n"/>
+      <c r="C29" s="10" t="n"/>
+      <c r="D29" s="10" t="n"/>
+      <c r="E29" s="10" t="n"/>
+      <c r="F29" s="10" t="n"/>
+      <c r="G29" s="10" t="n"/>
+      <c r="H29" s="10" t="n"/>
+    </row>
+    <row r="30" ht="30" customHeight="1">
+      <c r="A30" s="23" t="inlineStr">
+        <is>
+          <t>Nº</t>
+        </is>
+      </c>
+      <c r="B30" s="23" t="inlineStr">
+        <is>
+          <t>Alimento</t>
+        </is>
+      </c>
+      <c r="C30" s="23" t="inlineStr">
+        <is>
+          <t>Categoria</t>
+        </is>
+      </c>
+      <c r="D30" s="23" t="inlineStr">
+        <is>
+          <t>Porção sugerida</t>
+        </is>
+      </c>
+      <c r="E30" s="23" t="inlineStr">
+        <is>
+          <t>Quantidade a comer</t>
+        </is>
+      </c>
+      <c r="F30" s="23" t="inlineStr">
+        <is>
+          <t>Classificação</t>
+        </is>
+      </c>
+      <c r="G30" s="23" t="inlineStr">
+        <is>
+          <t>Sugestão (com base no item anterior)</t>
+        </is>
+      </c>
+      <c r="H30" s="23" t="inlineStr">
+        <is>
+          <t>Conflito</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="26" customHeight="1">
+      <c r="A31" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="B31" s="25" t="n"/>
+      <c r="C31" s="26">
+        <f>IFERROR(INDEX(Ref_Alimentos!$B$2:$B$101,MATCH($B31,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D31" s="27">
+        <f>IFERROR(INDEX(Ref_Alimentos!$D$2:$D$101,MATCH($B31,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E31" s="24" t="n"/>
+      <c r="F31" s="28">
+        <f>IFERROR(INDEX(Ref_Alimentos!$C$2:$C$101,MATCH($B31,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G31" s="29" t="inlineStr"/>
+      <c r="H31" s="30">
+        <f>IF($B31="","",IF($F31="Evitar","⚠ Conflito",IF(AND($F31="Moderar",SUMPRODUCT(($B$31:$B$35&lt;&gt;"")*(ROW($B$31:$B$35)&lt;&gt;ROW($B31))*(($F$31:$F$35="Moderar")+($F$31:$F$35="Evitar")))&gt;0),"⚠ Conflito","")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" ht="26" customHeight="1">
+      <c r="A32" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="B32" s="25" t="n"/>
+      <c r="C32" s="26">
+        <f>IFERROR(INDEX(Ref_Alimentos!$B$2:$B$101,MATCH($B32,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D32" s="27">
+        <f>IFERROR(INDEX(Ref_Alimentos!$D$2:$D$101,MATCH($B32,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E32" s="24" t="n"/>
+      <c r="F32" s="28">
+        <f>IFERROR(INDEX(Ref_Alimentos!$C$2:$C$101,MATCH($B32,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G32" s="29">
+        <f>IF($B31="","",IFERROR(INDEX(Ref_Alimentos!$R$2:$R$60,MATCH(IFERROR(INDEX(Ref_Alimentos!$U$2:$U$9,MATCH($C31,Ref_Alimentos!$T$2:$T$9,0)),"")&amp;"|"&amp;"Jantar",Ref_Alimentos!$Q$2:$Q$60,0)),""))</f>
+        <v/>
+      </c>
+      <c r="H32" s="30">
+        <f>IF($B32="","",IF($F32="Evitar","⚠ Conflito",IF(AND($F32="Moderar",SUMPRODUCT(($B$31:$B$35&lt;&gt;"")*(ROW($B$31:$B$35)&lt;&gt;ROW($B32))*(($F$31:$F$35="Moderar")+($F$31:$F$35="Evitar")))&gt;0),"⚠ Conflito","")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" ht="26" customHeight="1">
+      <c r="A33" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="B33" s="25" t="n"/>
+      <c r="C33" s="26">
+        <f>IFERROR(INDEX(Ref_Alimentos!$B$2:$B$101,MATCH($B33,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D33" s="27">
+        <f>IFERROR(INDEX(Ref_Alimentos!$D$2:$D$101,MATCH($B33,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E33" s="24" t="n"/>
+      <c r="F33" s="28">
+        <f>IFERROR(INDEX(Ref_Alimentos!$C$2:$C$101,MATCH($B33,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G33" s="29">
+        <f>IF($B32="","",IFERROR(INDEX(Ref_Alimentos!$R$2:$R$60,MATCH(IFERROR(INDEX(Ref_Alimentos!$U$2:$U$9,MATCH($C32,Ref_Alimentos!$T$2:$T$9,0)),"")&amp;"|"&amp;"Jantar",Ref_Alimentos!$Q$2:$Q$60,0)),""))</f>
+        <v/>
+      </c>
+      <c r="H33" s="30">
+        <f>IF($B33="","",IF($F33="Evitar","⚠ Conflito",IF(AND($F33="Moderar",SUMPRODUCT(($B$31:$B$35&lt;&gt;"")*(ROW($B$31:$B$35)&lt;&gt;ROW($B33))*(($F$31:$F$35="Moderar")+($F$31:$F$35="Evitar")))&gt;0),"⚠ Conflito","")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" ht="26" customHeight="1">
+      <c r="A34" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="B34" s="25" t="n"/>
+      <c r="C34" s="26">
+        <f>IFERROR(INDEX(Ref_Alimentos!$B$2:$B$101,MATCH($B34,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D34" s="27">
+        <f>IFERROR(INDEX(Ref_Alimentos!$D$2:$D$101,MATCH($B34,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E34" s="24" t="n"/>
+      <c r="F34" s="28">
+        <f>IFERROR(INDEX(Ref_Alimentos!$C$2:$C$101,MATCH($B34,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G34" s="29">
+        <f>IF($B33="","",IFERROR(INDEX(Ref_Alimentos!$R$2:$R$60,MATCH(IFERROR(INDEX(Ref_Alimentos!$U$2:$U$9,MATCH($C33,Ref_Alimentos!$T$2:$T$9,0)),"")&amp;"|"&amp;"Jantar",Ref_Alimentos!$Q$2:$Q$60,0)),""))</f>
+        <v/>
+      </c>
+      <c r="H34" s="30">
+        <f>IF($B34="","",IF($F34="Evitar","⚠ Conflito",IF(AND($F34="Moderar",SUMPRODUCT(($B$31:$B$35&lt;&gt;"")*(ROW($B$31:$B$35)&lt;&gt;ROW($B34))*(($F$31:$F$35="Moderar")+($F$31:$F$35="Evitar")))&gt;0),"⚠ Conflito","")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35" ht="26" customHeight="1">
+      <c r="A35" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="B35" s="25" t="n"/>
+      <c r="C35" s="26">
+        <f>IFERROR(INDEX(Ref_Alimentos!$B$2:$B$101,MATCH($B35,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D35" s="27">
+        <f>IFERROR(INDEX(Ref_Alimentos!$D$2:$D$101,MATCH($B35,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E35" s="24" t="n"/>
+      <c r="F35" s="28">
+        <f>IFERROR(INDEX(Ref_Alimentos!$C$2:$C$101,MATCH($B35,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G35" s="29">
+        <f>IF($B34="","",IFERROR(INDEX(Ref_Alimentos!$R$2:$R$60,MATCH(IFERROR(INDEX(Ref_Alimentos!$U$2:$U$9,MATCH($C34,Ref_Alimentos!$T$2:$T$9,0)),"")&amp;"|"&amp;"Jantar",Ref_Alimentos!$Q$2:$Q$60,0)),""))</f>
+        <v/>
+      </c>
+      <c r="H35" s="30">
+        <f>IF($B35="","",IF($F35="Evitar","⚠ Conflito",IF(AND($F35="Moderar",SUMPRODUCT(($B$31:$B$35&lt;&gt;"")*(ROW($B$31:$B$35)&lt;&gt;ROW($B35))*(($F$31:$F$35="Moderar")+($F$31:$F$35="Evitar")))&gt;0),"⚠ Conflito","")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37" ht="44" customHeight="1">
+      <c r="A37" s="31" t="inlineStr">
+        <is>
+          <t>Limitações conhecidas: a ordem do menu suspenso é fixa (Liberado &gt; Moderar &gt; Evitar), ela não se reordena sozinha conforme o item anterior — quem indica o que combina melhor é a coluna 'Sugestão'. A coluna 'Conflito' é uma aproximação (marca um item 'Evitar' sozinho, ou dois itens 'Moderar'/'Evitar' juntos na mesma refeição) — não é uma checagem real de interação entre os dois alimentos específicos.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A21:H21"/>
+    <mergeCell ref="A29:H29"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A37:H37"/>
+  </mergeCells>
+  <conditionalFormatting sqref="F7:F11">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+      <formula>"Liberado"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+      <formula>"Moderar"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
+      <formula>"Evitar"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H7:H11">
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="3">
+      <formula>"⚠ Conflito"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F15:F19">
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="0">
+      <formula>"Liberado"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="6" operator="equal" dxfId="1">
+      <formula>"Moderar"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="7" operator="equal" dxfId="2">
+      <formula>"Evitar"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H15:H19">
+    <cfRule type="cellIs" priority="8" operator="equal" dxfId="3">
+      <formula>"⚠ Conflito"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F23:F27">
+    <cfRule type="cellIs" priority="9" operator="equal" dxfId="0">
+      <formula>"Liberado"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="10" operator="equal" dxfId="1">
+      <formula>"Moderar"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="11" operator="equal" dxfId="2">
+      <formula>"Evitar"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H23:H27">
+    <cfRule type="cellIs" priority="12" operator="equal" dxfId="3">
+      <formula>"⚠ Conflito"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F31:F35">
+    <cfRule type="cellIs" priority="13" operator="equal" dxfId="0">
+      <formula>"Liberado"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="14" operator="equal" dxfId="1">
+      <formula>"Moderar"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="15" operator="equal" dxfId="2">
+      <formula>"Evitar"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H31:H35">
+    <cfRule type="cellIs" priority="16" operator="equal" dxfId="3">
+      <formula>"⚠ Conflito"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="4">
+    <dataValidation sqref="B7:B11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Alimento fora da lista" error="Escolha um alimento da lista da coluna (ou deixe em branco)." promptTitle="Alimentos para Café da manhã" prompt="Lista filtrada para esta refeição, com os alimentos Liberados primeiro." type="list" errorStyle="warning">
+      <formula1>=Ref_Alimentos!$L$2:$L$101</formula1>
+    </dataValidation>
+    <dataValidation sqref="B15:B19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Alimento fora da lista" error="Escolha um alimento da lista da coluna (ou deixe em branco)." promptTitle="Alimentos para Almoço" prompt="Lista filtrada para esta refeição, com os alimentos Liberados primeiro." type="list" errorStyle="warning">
+      <formula1>=Ref_Alimentos!$M$2:$M$101</formula1>
+    </dataValidation>
+    <dataValidation sqref="B23:B27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Alimento fora da lista" error="Escolha um alimento da lista da coluna (ou deixe em branco)." promptTitle="Alimentos para Lanche" prompt="Lista filtrada para esta refeição, com os alimentos Liberados primeiro." type="list" errorStyle="warning">
+      <formula1>=Ref_Alimentos!$N$2:$N$101</formula1>
+    </dataValidation>
+    <dataValidation sqref="B31:B35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Alimento fora da lista" error="Escolha um alimento da lista da coluna (ou deixe em branco)." promptTitle="Alimentos para Jantar" prompt="Lista filtrada para esta refeição, com os alimentos Liberados primeiro." type="list" errorStyle="warning">
+      <formula1>=Ref_Alimentos!$O$2:$O$101</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:U35"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Alimento</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Categoria</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Classificação</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Porção</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Frequência</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Observação</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Café da manhã</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Almoço</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Lanche</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Jantar</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Lista — Café da manhã</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Lista — Almoço</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Lista — Lanche</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Lista — Jantar</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>Chave (Categoria|Refeição)</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>Alimento em destaque</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>Categoria escolhida</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>Categoria sugerida</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Maçã com casca</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Frutas</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Liberado</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>1 unidade</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>1x/dia</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Maçã com casca</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Arroz integral</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Maçã com casca</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Arroz integral</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Frutas|Café da manhã</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Maçã com casca</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>Laticínios</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Grãos e Cereais</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Banana</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Frutas</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Liberado</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>1 unidade</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>1x/dia</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Banana</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Peixe</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Banana</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Peixe</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>Grãos e Cereais|Café da manhã</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>Aveia</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Grãos e Cereais</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Laticínios</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Uva</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Frutas</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Moderar</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>200 g</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>1x/semana</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Mais açúcar que outras frutas</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Abacate</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Frango sem pele</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Abacate</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Frango sem pele</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Proteínas|Café da manhã</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Ovo</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Proteínas</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Vegetais e Verduras</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Manga</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Frutas</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Moderar</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>200 g</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>1x/semana</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Mais açúcar que outras frutas</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Aveia</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Ovo</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Pão integral</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Ovo</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>Laticínios|Café da manhã</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>Leite desnatado</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Vegetais e Verduras</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Proteínas</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Abacate</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Frutas</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Liberado</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2 colheres de sopa</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>1x/dia</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Gordura boa, mas calórico</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Pão integral</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Feijão / leguminosas</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Leite desnatado</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Feijão / leguminosas</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>Bebidas|Café da manhã</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>Água</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Bebidas</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Proteínas</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Toranja / grapefruit</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Frutas</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Evitar</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>evitar</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Interage com o Ticagrelor (aumenta o nível do remédio no sangue e o risco de sangramento) — evitar completamente.</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Ovo</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Água</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Iogurte natural (desnatado, sem açúcar)</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Água</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>Doces e Sobremesas|Café da manhã</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>Açúcar refinado</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Frutas</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Laticínios</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Arroz integral</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Grãos e Cereais</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Liberado</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>200 g (cozido)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>quase todo dia</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Leite desnatado</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Azeite de oliva extra virgem</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Água</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Azeite de oliva extra virgem</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>Gorduras e Temperos|Café da manhã</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>Manteiga</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Doces e Sobremesas</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Frutas</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Arroz branco</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Grãos e Cereais</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Moderar</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>200 g (cozido)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2x/semana</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Preferir integral no restante da semana</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Iogurte natural (desnatado, sem açúcar)</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Ervas e temperos naturais</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Café sem açúcar</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Ervas e temperos naturais</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>Vegetais e Verduras|Café da manhã</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>Vegetais e verduras em geral</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gorduras e Temperos</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Vegetais e Verduras</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Aveia</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Grãos e Cereais</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Liberado</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2 colheres de sopa</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>1x/dia</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Ajuda a reduzir colesterol</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Água</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Vegetais e verduras em geral</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Vegetais e verduras em geral</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Vegetais e verduras em geral</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>Grãos e Cereais|Almoço</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>Arroz integral</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Pão integral</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Grãos e Cereais</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Liberado</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2 fatias</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>1x/dia</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Café sem açúcar</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Arroz branco</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Uva</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Arroz branco</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>Proteínas|Almoço</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>Peixe</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Peixe</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Proteínas</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Liberado</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>150 g</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>3x/semana</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Fonte de ômega-3</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Vegetais e verduras em geral</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Carne vermelha magra</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Manga</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Carne vermelha magra</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>Bebidas|Almoço</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>Água</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Frango sem pele</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Proteínas</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Liberado</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>150 g</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>quase todo dia</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Uva</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Refrigerante zero</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Queijo branco</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Refrigerante zero</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>Doces e Sobremesas|Almoço</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>Açúcar refinado</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Carne vermelha magra</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Proteínas</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Moderar</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>150 g</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>1x/semana</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Preferir cortes magros</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Manga</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Sal</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Requeijão</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Sal</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>Gorduras e Temperos|Almoço</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>Azeite de oliva extra virgem</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Ovo</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Proteínas</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Liberado</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>1 unidade</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>até 5x/semana</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Queijo branco</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Bebida alcoólica</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Refrigerante zero</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Bebida alcoólica</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>Vegetais e Verduras|Almoço</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>Vegetais e verduras em geral</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Feijão / leguminosas</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Proteínas</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Liberado</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>1 concha</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>1x/dia</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Requeijão</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Açúcar refinado</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Suco natural sem açúcar</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Açúcar refinado</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>Frutas|Lanche</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>Maçã com casca</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Leite desnatado</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Laticínios</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Liberado</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>200 ml</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>1x/dia</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Suco natural sem açúcar</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Sal light / substituto de sal (cloreto de potássio)</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Chocolate amargo (70%+)</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Sal light / substituto de sal (cloreto de potássio)</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>Grãos e Cereais|Lanche</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>Pão integral</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Queijo branco</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Laticínios</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Moderar</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>30 g</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>3x/semana</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Atenção ao sódio</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Toranja / grapefruit</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Toranja / grapefruit</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>Laticínios|Lanche</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>Leite desnatado</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Iogurte natural (desnatado, sem açúcar)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Laticínios</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Liberado</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>1 unidade</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>1x/dia</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Prefira sempre a versão sem açúcar adicionado</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Suco de toranja / grapefruit</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Suco de toranja / grapefruit</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>Bebidas|Lanche</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>Água</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Requeijão</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Laticínios</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Moderar</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>1 colher de sopa (≈15 g)</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>2x/semana</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Rico em gordura saturada e sódio; prefira a versão light. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Açúcar refinado</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Açúcar refinado</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>Doces e Sobremesas|Lanche</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>Açúcar refinado</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Água</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Bebidas</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Liberado</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>à vontade</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>todos os dias</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Manteiga</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Doces industrializados</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>Vegetais e Verduras|Lanche</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>Vegetais e verduras em geral</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Refrigerante zero</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Bebidas</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Moderar</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>200 ml</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>1x/dia</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Sugestão gerada por IA — confirmar com nutricionista/cardiologista</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>Grãos e Cereais|Jantar</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>Arroz integral</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Café sem açúcar</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Bebidas</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Liberado</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>1 xícara</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>2x/dia</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>Proteínas|Jantar</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>Peixe</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Suco natural sem açúcar</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Bebidas</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Moderar</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>200 ml</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>3x/semana</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Preferir a fruta inteira, que tem mais fibra</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>Bebidas|Jantar</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>Água</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Suco de toranja / grapefruit</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Bebidas</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Evitar</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>evitar</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Interage com o Ticagrelor (aumenta o nível do remédio no sangue e o risco de sangramento) — evitar completamente.</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>Doces e Sobremesas|Jantar</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>Açúcar refinado</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Bebida alcoólica</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Bebidas</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Evitar</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>evitar</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Piora diretamente os triglicerídeos; soma-se ao risco de sangramento da Aspirina + Ticagrelor.</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>Gorduras e Temperos|Jantar</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>Azeite de oliva extra virgem</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Açúcar refinado</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Doces e Sobremesas</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Evitar</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>evitar</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Impacto direto nos triglicerídeos</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>Vegetais e Verduras|Jantar</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>Vegetais e verduras em geral</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Doces industrializados</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Doces e Sobremesas</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Evitar</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>evitar</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Chocolate amargo (70%+)</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Doces e Sobremesas</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Moderar</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>10 g</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>2x/semana</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Sugestão gerada por IA — confirmar com nutricionista/cardiologista</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Azeite de oliva extra virgem</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Gorduras e Temperos</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Liberado</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>1-2 colheres de sopa</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>1x/dia</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Manteiga</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Gorduras e Temperos</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Evitar</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>evitar</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Preferir azeite</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Sal</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Gorduras e Temperos</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Moderar</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>&lt; 5 g no total</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>todos os dias</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Somar sal de cozinha + industrializados</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Sal light / substituto de sal (cloreto de potássio)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Gorduras e Temperos</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Evitar</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>evitar</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Enalapril já tende a elevar o potássio; combinado com esse produto o risco de hipercalemia aumenta, ainda mais com a função renal pendente.</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Ervas e temperos naturais</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Gorduras e Temperos</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Liberado</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>à vontade</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>todos os dias</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Vegetais e verduras em geral</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Vegetais e Verduras</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Liberado</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>à vontade</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>todos os dias</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Se entrar anticoagulante na medicação, revisar consumo de verde-escuros ricos em vitamina K</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/planilha/plano-alimentar-pos-infarto.xlsx
+++ b/planilha/plano-alimentar-pos-infarto.xlsx
@@ -11,9 +11,15 @@
     <sheet name="Plano Geral - Restaurante" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Alimentos e Quantidades" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Montar Refeição" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Ref_Alimentos" sheetId="5" state="hidden" r:id="rId5"/>
+    <sheet name="Fontes e Referências" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Ref_Alimentos" sheetId="6" state="hidden" r:id="rId6"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="Lista_CafeDaManha">Ref_Alimentos!$L$2:$L$101</definedName>
+    <definedName name="Lista_Almoco">Ref_Alimentos!$M$2:$M$101</definedName>
+    <definedName name="Lista_Lanche">Ref_Alimentos!$N$2:$N$101</definedName>
+    <definedName name="Lista_Jantar">Ref_Alimentos!$O$2:$O$101</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -21,7 +27,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="14">
+  <fonts count="17">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -101,6 +107,21 @@
       <i val="1"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="001155CC"/>
+      <sz val="10"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00666666"/>
+      <sz val="9"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -166,7 +187,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -258,6 +279,18 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -802,7 +835,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Meta pós-IAM é LDL &lt;50 mg/dL (bem mais rígida que a meta geral da população). Reforça a importância de manter o cuidado mesmo quando o valor parecer 'razoável' pelos padrões gerais.</t>
+          <t>Meta pós-IAM é bem mais rígida que a da população geral, mas varia por diretriz: &lt;50 mg/dL (diretriz brasileira SBC 2017, usada pelo laboratório), &lt;40 mg/dL (categoria 'risco extremo' da diretriz SBC 2025, se preencher critérios adicionais) ou &lt;55 mg/dL (diretrizes ESC/EAS e ACC/AHA para risco muito alto) — pergunte ao médico qual meta ele está usando (fontes na aba 'Fontes e Referências').</t>
         </is>
       </c>
     </row>
@@ -838,7 +871,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Toranja/grapefruit (fruta ou suco) aumenta o nível de Ticagrelor no sangue e o risco de sangramento — evitar completamente enquanto estiver em uso do medicamento.</t>
+          <t>Toranja/grapefruit (fruta ou suco) inibe uma enzima do fígado (CYP3A4) que ajuda a metabolizar o Ticagrelor. Um estudo publicado mostrou quase o dobro do nível do remédio no sangue com suco em grande quantidade; a própria bula brasileira do Brilinta cita esse estudo e diz que não é esperado ser 'clinicamente relevante para a maioria dos pacientes' — mas recomenda evitar. Como você toma 2 antiagregantes juntos, a orientação mais segura é evitar toranja/grapefruit. Fontes: aba 'Fontes e Referências', linhas 1-2.</t>
         </is>
       </c>
     </row>
@@ -850,7 +883,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Enalapril pode elevar o potássio do sangue. Evitar sal light/substitutos de sal (ricos em cloreto de potássio) e suplementos de potássio sem orientação médica — atenção redobrada enquanto a função renal ainda está em investigação.</t>
+          <t>Enalapril pode elevar o potássio do sangue (reduz a aldosterona). Evitar sal light/substitutos de sal (ricos em cloreto de potássio) e suplementos de potássio sem orientação médica — risco bem documentado de hipercalemia, com atenção redobrada enquanto a função renal ainda está em investigação. Fonte: aba 'Fontes e Referências', linha 3.</t>
         </is>
       </c>
     </row>
@@ -862,7 +895,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>A dupla antiagregação (esquema padrão por 1 ano pós-stent) já aumenta o risco de sangramento; álcool amplifica esse risco — reforça a orientação de evitar bebida alcoólica.</t>
+          <t>A dupla antiagregação (esquema padrão por 1 ano pós-stent, conforme diretriz ACC/AHA) já aumenta o risco de sangramento; estudos mostram que álcool combinado com Aspirina aumenta especificamente o sangramento gastrointestinal alto — reforça a orientação de evitar bebida alcoólica. Fontes: aba 'Fontes e Referências', linhas 4 e 7.</t>
         </is>
       </c>
     </row>
@@ -874,7 +907,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Evitar suplementos de 'arroz de levedura vermelha' (red yeast rice), que agem como uma estatina natural e podem somar toxicidade com a Rosucor.</t>
+          <t>Evitar suplementos de 'arroz de levedura vermelha' (red yeast rice): o NIH americano alerta que contêm uma substância quimicamente idêntica a uma estatina e podem somar efeitos colaterais/toxicidade com a Rosucor. Já a toranja/grapefruit NÃO tem interação relevante conhecida com a Rosucor especificamente (ela usa outra via metabólica, CYP2C9) — o motivo de evitar toranja neste plano é o Ticagrelor, não a Rosucor. Fontes: aba 'Fontes e Referências', linhas 5-6.</t>
         </is>
       </c>
     </row>
@@ -1245,7 +1278,7 @@
       </c>
       <c r="F10" s="11" t="inlineStr">
         <is>
-          <t>Interage com o Ticagrelor (aumenta o nível do remédio no sangue e o risco de sangramento) — evitar completamente.</t>
+          <t>Interage com o Ticagrelor (estudo mostrou quase o dobro do nível do remédio no sangue); a bula diz que não é esperado ser clinicamente relevante p/ a maioria, mas orienta evitar — mais seguro evitar, já que você toma 2 antiagregantes. Ver aba Fontes e Referências.</t>
         </is>
       </c>
     </row>
@@ -1747,7 +1780,7 @@
       </c>
       <c r="F32" s="11" t="inlineStr">
         <is>
-          <t>Interage com o Ticagrelor (aumenta o nível do remédio no sangue e o risco de sangramento) — evitar completamente.</t>
+          <t>Interage com o Ticagrelor (estudo mostrou quase o dobro do nível do remédio no sangue); a bula diz que não é esperado ser clinicamente relevante p/ a maioria, mas orienta evitar — mais seguro evitar, já que você toma 2 antiagregantes. Ver aba Fontes e Referências.</t>
         </is>
       </c>
     </row>
@@ -2963,17 +2996,17 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
-    <dataValidation sqref="B7:B11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Alimento fora da lista" error="Escolha um alimento da lista da coluna (ou deixe em branco)." promptTitle="Alimentos para Café da manhã" prompt="Lista filtrada para esta refeição, com os alimentos Liberados primeiro." type="list" errorStyle="warning">
-      <formula1>=Ref_Alimentos!$L$2:$L$101</formula1>
+    <dataValidation sqref="B7:B11" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Alimento fora da lista" error="Escolha um alimento da lista da coluna (ou deixe em branco)." promptTitle="Alimentos para Café da manhã" prompt="Lista filtrada para esta refeição, com os alimentos Liberados primeiro." type="list" errorStyle="warning">
+      <formula1>=Lista_CafeDaManha</formula1>
     </dataValidation>
-    <dataValidation sqref="B15:B19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Alimento fora da lista" error="Escolha um alimento da lista da coluna (ou deixe em branco)." promptTitle="Alimentos para Almoço" prompt="Lista filtrada para esta refeição, com os alimentos Liberados primeiro." type="list" errorStyle="warning">
-      <formula1>=Ref_Alimentos!$M$2:$M$101</formula1>
+    <dataValidation sqref="B15:B19" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Alimento fora da lista" error="Escolha um alimento da lista da coluna (ou deixe em branco)." promptTitle="Alimentos para Almoço" prompt="Lista filtrada para esta refeição, com os alimentos Liberados primeiro." type="list" errorStyle="warning">
+      <formula1>=Lista_Almoco</formula1>
     </dataValidation>
-    <dataValidation sqref="B23:B27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Alimento fora da lista" error="Escolha um alimento da lista da coluna (ou deixe em branco)." promptTitle="Alimentos para Lanche" prompt="Lista filtrada para esta refeição, com os alimentos Liberados primeiro." type="list" errorStyle="warning">
-      <formula1>=Ref_Alimentos!$N$2:$N$101</formula1>
+    <dataValidation sqref="B23:B27" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Alimento fora da lista" error="Escolha um alimento da lista da coluna (ou deixe em branco)." promptTitle="Alimentos para Lanche" prompt="Lista filtrada para esta refeição, com os alimentos Liberados primeiro." type="list" errorStyle="warning">
+      <formula1>=Lista_Lanche</formula1>
     </dataValidation>
-    <dataValidation sqref="B31:B35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Alimento fora da lista" error="Escolha um alimento da lista da coluna (ou deixe em branco)." promptTitle="Alimentos para Jantar" prompt="Lista filtrada para esta refeição, com os alimentos Liberados primeiro." type="list" errorStyle="warning">
-      <formula1>=Ref_Alimentos!$O$2:$O$101</formula1>
+    <dataValidation sqref="B31:B35" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Alimento fora da lista" error="Escolha um alimento da lista da coluna (ou deixe em branco)." promptTitle="Alimentos para Jantar" prompt="Lista filtrada para esta refeição, com os alimentos Liberados primeiro." type="list" errorStyle="warning">
+      <formula1>=Lista_Jantar</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2986,6 +3019,342 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:E15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Fontes e Referências — de onde vieram as informações médicas</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="46" customHeight="1">
+      <c r="A2" s="16" t="inlineStr">
+        <is>
+          <t>Pesquisa feita em 04/09/2026, priorizando bulas oficiais (Anvisa), estudos revisados por pares (PubMed/PMC), órgãos de saúde do governo (NIH) e diretrizes de sociedades médicas (SBC, AHA, ACC/ESC). Nenhuma destas fontes substitui a avaliação do seu médico — use como ponto de partida para perguntar e confirmar na consulta. Clique no link da coluna 'Fonte' para abrir a página original.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Nº</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Afirmação que a fonte sustenta</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Fonte</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Tipo de fonte</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>URL completa</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="44" customHeight="1">
+      <c r="A4" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="33" t="inlineStr">
+        <is>
+          <t>Suco de toranja em quantidade alta quase dobra o nível de Ticagrelor no sangue e aumenta seu efeito antiagregante</t>
+        </is>
+      </c>
+      <c r="C4" s="34" t="inlineStr">
+        <is>
+          <t>Holmberg et al., 2013, Br J Clin Pharmacol (PubMed)</t>
+        </is>
+      </c>
+      <c r="D4" s="33" t="inlineStr">
+        <is>
+          <t>Estudo clínico revisado por pares</t>
+        </is>
+      </c>
+      <c r="E4" s="35" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/23126367/</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="44" customHeight="1">
+      <c r="A5" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="33" t="inlineStr">
+        <is>
+          <t>Bula brasileira do Brilinta (Ticagrelor) cita esse estudo e orienta evitar suco de toranja em grande quantidade</t>
+        </is>
+      </c>
+      <c r="C5" s="34" t="inlineStr">
+        <is>
+          <t>Bula profissional Brilinta, AstraZeneca do Brasil (aprovada pela Anvisa)</t>
+        </is>
+      </c>
+      <c r="D5" s="33" t="inlineStr">
+        <is>
+          <t>Bula oficial (Anvisa)</t>
+        </is>
+      </c>
+      <c r="E5" s="35" t="inlineStr">
+        <is>
+          <t>https://www.azmed.com.br/content/dam/multibrand/br/pt/azmed-2022/home/bulas-profissionais/bulas/Brilinta_Bula_Profissional.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="44" customHeight="1">
+      <c r="A6" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="33" t="inlineStr">
+        <is>
+          <t>Enalapril (IECA) + sal light/suplemento de potássio aumenta risco de hipercalemia</t>
+        </is>
+      </c>
+      <c r="C6" s="34" t="inlineStr">
+        <is>
+          <t>StatPearls (NCBI Bookshelf), "Enalapril"</t>
+        </is>
+      </c>
+      <c r="D6" s="33" t="inlineStr">
+        <is>
+          <t>Referência clínica revisada por pares</t>
+        </is>
+      </c>
+      <c r="E6" s="35" t="inlineStr">
+        <is>
+          <t>https://www.ncbi.nlm.nih.gov/books/NBK557708/</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="44" customHeight="1">
+      <c r="A7" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="33" t="inlineStr">
+        <is>
+          <t>Álcool combinado com Aspirina aumenta o risco de sangramento gastrointestinal alto</t>
+        </is>
+      </c>
+      <c r="C7" s="34" t="inlineStr">
+        <is>
+          <t>Kaufman et al., 1999, Ann Epidemiol (PubMed)</t>
+        </is>
+      </c>
+      <c r="D7" s="33" t="inlineStr">
+        <is>
+          <t>Estudo epidemiológico revisado por pares</t>
+        </is>
+      </c>
+      <c r="E7" s="35" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/10566713/</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="44" customHeight="1">
+      <c r="A8" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="33" t="inlineStr">
+        <is>
+          <t>Arroz de levedura vermelha (red yeast rice) pode causar os mesmos efeitos colaterais e interações de uma estatina</t>
+        </is>
+      </c>
+      <c r="C8" s="34" t="inlineStr">
+        <is>
+          <t>NIH — National Center for Complementary and Integrative Health</t>
+        </is>
+      </c>
+      <c r="D8" s="33" t="inlineStr">
+        <is>
+          <t>Órgão oficial do governo dos EUA (NIH)</t>
+        </is>
+      </c>
+      <c r="E8" s="35" t="inlineStr">
+        <is>
+          <t>https://www.nccih.nih.gov/health/red-yeast-rice</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="44" customHeight="1">
+      <c r="A9" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="33" t="inlineStr">
+        <is>
+          <t>Rosuvastatina não tem interação relevante com toranja (via CYP2C9, diferente da via CYP3A4 usada pelo Ticagrelor)</t>
+        </is>
+      </c>
+      <c r="C9" s="34" t="inlineStr">
+        <is>
+          <t>Bailey DG et al., 2013, CMAJ, "Grapefruit-medication interactions"</t>
+        </is>
+      </c>
+      <c r="D9" s="33" t="inlineStr">
+        <is>
+          <t>Revisão científica revisada por pares</t>
+        </is>
+      </c>
+      <c r="E9" s="35" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC3589309/</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="44" customHeight="1">
+      <c r="A10" s="32" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="33" t="inlineStr">
+        <is>
+          <t>Duração de 12 meses de dupla antiagregação (Aspirina + Ticagrelor) após stent em síndrome coronariana aguda</t>
+        </is>
+      </c>
+      <c r="C10" s="34" t="inlineStr">
+        <is>
+          <t>2016 ACC/AHA Guideline Focused Update on DAPT; reafirmado na diretriz ACS 2025 (JACC)</t>
+        </is>
+      </c>
+      <c r="D10" s="33" t="inlineStr">
+        <is>
+          <t>Diretriz de sociedades médicas (ACC/AHA)</t>
+        </is>
+      </c>
+      <c r="E10" s="35" t="inlineStr">
+        <is>
+          <t>https://www.acc.org/latest-in-cardiology/ten-points-to-remember/2016/03/25/14/56/2016-acc-aha-guideline-focused-update-on-dapt</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="44" customHeight="1">
+      <c r="A11" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="33" t="inlineStr">
+        <is>
+          <t>Metas de LDL pós-infarto: &lt;50 mg/dL (SBC 2017); &lt;40 mg/dL na categoria "risco extremo" (SBC 2025, com critérios adicionais); &lt;55 mg/dL (ESC/EAS 2019 e ACC/AHA, risco muito alto)</t>
+        </is>
+      </c>
+      <c r="C11" s="34" t="inlineStr">
+        <is>
+          <t>Diretriz Brasileira de Dislipidemias e Prevenção da Aterosclerose 2025 (SBC), Arq Bras Cardiol</t>
+        </is>
+      </c>
+      <c r="D11" s="33" t="inlineStr">
+        <is>
+          <t>Diretriz de sociedade médica (SBC)</t>
+        </is>
+      </c>
+      <c r="E11" s="35" t="inlineStr">
+        <is>
+          <t>https://www.scielo.br/j/abc/a/tRJrwGzKX6C4GvMqdJpZcGk/?lang=pt</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="44" customHeight="1">
+      <c r="A12" s="32" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="33" t="inlineStr">
+        <is>
+          <t>Diretriz alimentar cardioprotetora: sódio controlado, gordura saturada &lt;6% das calorias, padrão Mediterrâneo/DASH</t>
+        </is>
+      </c>
+      <c r="C12" s="34" t="inlineStr">
+        <is>
+          <t>American Heart Association — AHA Diet and Lifestyle Recommendations / 2026 Dietary Guidance to Improve Cardiovascular Health (Circulation)</t>
+        </is>
+      </c>
+      <c r="D12" s="33" t="inlineStr">
+        <is>
+          <t>Diretriz de sociedade médica (AHA)</t>
+        </is>
+      </c>
+      <c r="E12" s="35" t="inlineStr">
+        <is>
+          <t>https://www.heart.org/en/healthy-living/healthy-eating/eat-smart/nutrition-basics/aha-diet-and-lifestyle-recommendations</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="44" customHeight="1">
+      <c r="A13" s="32" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="33" t="inlineStr">
+        <is>
+          <t>No Brasil, a Dieta Cardioprotetora Brasileira (DICA Br) aplica essas mesmas recomendações a alimentos típicos brasileiros</t>
+        </is>
+      </c>
+      <c r="C13" s="34" t="inlineStr">
+        <is>
+          <t>I Diretriz Brasileira de Prevenção Cardiovascular (SBC), Arq Bras Cardiol</t>
+        </is>
+      </c>
+      <c r="D13" s="33" t="inlineStr">
+        <is>
+          <t>Diretriz de sociedade médica (SBC)</t>
+        </is>
+      </c>
+      <c r="E13" s="35" t="inlineStr">
+        <is>
+          <t>https://www.scielo.br/j/abc/a/X94tMKwdnBjkCzVKpXwBqmD/?lang=pt</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="24" customHeight="1">
+      <c r="A15" s="16" t="inlineStr">
+        <is>
+          <t>Lista completa com os mesmos links (mais fácil de clicar em Markdown) também em referencia/dados-consulta-e-alimentacao.md, seção 1b.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A15:E15"/>
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId10"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:U35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -3521,7 +3890,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Interage com o Ticagrelor (aumenta o nível do remédio no sangue e o risco de sangramento) — evitar completamente.</t>
+          <t>Interage com o Ticagrelor (estudo mostrou quase o dobro do nível do remédio no sangue); a bula diz que não é esperado ser clinicamente relevante p/ a maioria, mas orienta evitar — mais seguro evitar, já que você toma 2 antiagregantes. Ver aba Fontes e Referências.</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -4763,7 +5132,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Interage com o Ticagrelor (aumenta o nível do remédio no sangue e o risco de sangramento) — evitar completamente.</t>
+          <t>Interage com o Ticagrelor (estudo mostrou quase o dobro do nível do remédio no sangue); a bula diz que não é esperado ser clinicamente relevante p/ a maioria, mas orienta evitar — mais seguro evitar, já que você toma 2 antiagregantes. Ver aba Fontes e Referências.</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">

--- a/planilha/plano-alimentar-pos-infarto.xlsx
+++ b/planilha/plano-alimentar-pos-infarto.xlsx
@@ -693,7 +693,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -835,7 +835,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Meta pós-IAM é bem mais rígida que a da população geral, mas varia por diretriz: &lt;50 mg/dL (diretriz brasileira SBC 2017, usada pelo laboratório), &lt;40 mg/dL (categoria 'risco extremo' da diretriz SBC 2025, se preencher critérios adicionais) ou &lt;55 mg/dL (diretrizes ESC/EAS e ACC/AHA para risco muito alto) — pergunte ao médico qual meta ele está usando (fontes na aba 'Fontes e Referências').</t>
+          <t>Meta pós-IAM é bem mais rígida que a da população geral, mas varia por diretriz: &lt;50 mg/dL (diretriz brasileira SBC 2017, usada pelo laboratório), &lt;40 mg/dL (categoria 'risco extremo' da diretriz SBC 2025, se preencher critérios adicionais) ou &lt;55 mg/dL (diretrizes ESC/EAS e ACC/AHA para risco muito alto) — pergunte ao médico qual meta ele está usando. A combinação estatina (Rosucor) + Ezetimiba já prescrita é sustentada pelo estudo IMPROVE-IT (LDL médio de 53,7 mg/dL com a combinação, vs. 69,5 mg/dL só com estatina, e menos eventos cardiovasculares). Fontes na aba 'Fontes e Referências'.</t>
         </is>
       </c>
     </row>
@@ -847,7 +847,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Há suspeita ainda não confirmada de proteinúria e duas elevações de creatinina/TFG durante a internação (TFG caiu para 57 na véspera da alta). Enquanto não houver confirmação médica, o plano NÃO aplica restrição renal (sódio/potássio/proteína) — apenas o cuidado cardiovascular abaixo. Revisar esta aba assim que o médico confirmar ou descartar o problema renal.</t>
+          <t>Há suspeita ainda não confirmada de proteinúria (o exame certo a pedir é a relação albumina/creatinina urinária, ACR/RAC, padrão KDIGO) e duas elevações de creatinina/TFG durante a internação (TFG caiu para 57 na véspera da alta) — a última, aplicando o critério objetivo da KDIGO, já preenche Lesão Renal Aguda estágio 1 (não é diagnóstico médico, só a fórmula aplicada aos números). O padrão temporal é compatível com nefropatia por contraste dos 3 cateterismos (ESUR: pico em 3-5 dias, resolução em 7-14 dias). Enquanto não houver confirmação médica de que isso se resolveu, o plano NÃO aplica restrição renal (sódio/potássio/proteína) — apenas o cuidado cardiovascular abaixo. Revisar esta aba assim que o médico confirmar ou descartar o problema renal.</t>
         </is>
       </c>
     </row>
@@ -883,7 +883,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Enalapril pode elevar o potássio do sangue (reduz a aldosterona). Evitar sal light/substitutos de sal (ricos em cloreto de potássio) e suplementos de potássio sem orientação médica — risco bem documentado de hipercalemia, com atenção redobrada enquanto a função renal ainda está em investigação. Fonte: aba 'Fontes e Referências', linha 3.</t>
+          <t>Enalapril pode elevar o potássio do sangue (reduz a aldosterona). Evitar sal light/substitutos de sal (ricos em cloreto de potássio) e suplementos de potássio sem orientação médica — risco bem documentado de hipercalemia. O potássio (4,9) e a creatinina (1,50) da alta ficam dentro da faixa considerada tolerável por uma diretriz de insuficiência cardíaca (ESC 2021) para manter o Enalapril — informação tranquilizadora, mas essa mesma diretriz recomenda reexame de potássio/creatinina em 1-2 semanas, e reforça evitar sal light por precaução até lá. Fontes: aba 'Fontes e Referências', linha 3 (Enalapril) e 15 (limiares ESC).</t>
         </is>
       </c>
     </row>
@@ -914,10 +914,22 @@
     <row r="19" ht="46" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
+          <t>Reabilitação cardíaca</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>A diretriz mais recente de síndrome coronariana aguda (ACC/AHA/ACEP/NAEMSP/SCAI 2025) recomenda encaminhamento para reabilitação cardíaca com o grau mais forte de recomendação (Classe 1), idealmente ainda na alta — reduz mortalidade, reinfarto e reinternações. Não é sobre alimentação diretamente, mas costuma incluir acompanhamento nutricional; vale perguntar ao médico se já foi encaminhado. Fonte: aba 'Fontes e Referências', linha 17.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="46" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
           <t>Leitura de rótulos</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>Ao comprar um produto industrializado, olhar sempre: sódio por porção, açúcares totais/adicionados, e a lista de ingredientes procurando 'gordura hidrogenada' ou 'gordura trans'. Prefira produtos com menos ingredientes e sem açúcar adicionado.</t>
         </is>
@@ -3019,14 +3031,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="50" customWidth="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -3036,10 +3049,10 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="46" customHeight="1">
+    <row r="2" ht="56" customHeight="1">
       <c r="A2" s="16" t="inlineStr">
         <is>
-          <t>Pesquisa feita em 04/09/2026, priorizando bulas oficiais (Anvisa), estudos revisados por pares (PubMed/PMC), órgãos de saúde do governo (NIH) e diretrizes de sociedades médicas (SBC, AHA, ACC/ESC). Nenhuma destas fontes substitui a avaliação do seu médico — use como ponto de partida para perguntar e confirmar na consulta. Clique no link da coluna 'Fonte' para abrir a página original.</t>
+          <t>Pesquisa feita em 04/09/2026, priorizando bulas oficiais (Anvisa), estudos revisados por pares (PubMed/PMC), órgãos de saúde do governo (NIH) e diretrizes de sociedades médicas (SBC, AHA, ACC/ESC, KDIGO, ESUR, ESVS, ADA/SBD). A coluna 'Área' diz se a fonte é sobre alimentação/interação com alimento ou sobre o quadro clínico em geral. Nenhuma destas fontes substitui a avaliação do seu médico — use como ponto de partida para perguntar e confirmar na consulta. Clique no link da coluna 'Fonte' para abrir a página original.</t>
         </is>
       </c>
     </row>
@@ -3065,6 +3078,11 @@
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Área</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>URL completa</t>
         </is>
@@ -3089,7 +3107,12 @@
           <t>Estudo clínico revisado por pares</t>
         </is>
       </c>
-      <c r="E4" s="35" t="inlineStr">
+      <c r="E4" s="32" t="inlineStr">
+        <is>
+          <t>Alimentação</t>
+        </is>
+      </c>
+      <c r="F4" s="35" t="inlineStr">
         <is>
           <t>https://pubmed.ncbi.nlm.nih.gov/23126367/</t>
         </is>
@@ -3114,7 +3137,12 @@
           <t>Bula oficial (Anvisa)</t>
         </is>
       </c>
-      <c r="E5" s="35" t="inlineStr">
+      <c r="E5" s="32" t="inlineStr">
+        <is>
+          <t>Alimentação</t>
+        </is>
+      </c>
+      <c r="F5" s="35" t="inlineStr">
         <is>
           <t>https://www.azmed.com.br/content/dam/multibrand/br/pt/azmed-2022/home/bulas-profissionais/bulas/Brilinta_Bula_Profissional.pdf</t>
         </is>
@@ -3139,7 +3167,12 @@
           <t>Referência clínica revisada por pares</t>
         </is>
       </c>
-      <c r="E6" s="35" t="inlineStr">
+      <c r="E6" s="32" t="inlineStr">
+        <is>
+          <t>Alimentação</t>
+        </is>
+      </c>
+      <c r="F6" s="35" t="inlineStr">
         <is>
           <t>https://www.ncbi.nlm.nih.gov/books/NBK557708/</t>
         </is>
@@ -3164,7 +3197,12 @@
           <t>Estudo epidemiológico revisado por pares</t>
         </is>
       </c>
-      <c r="E7" s="35" t="inlineStr">
+      <c r="E7" s="32" t="inlineStr">
+        <is>
+          <t>Alimentação</t>
+        </is>
+      </c>
+      <c r="F7" s="35" t="inlineStr">
         <is>
           <t>https://pubmed.ncbi.nlm.nih.gov/10566713/</t>
         </is>
@@ -3189,7 +3227,12 @@
           <t>Órgão oficial do governo dos EUA (NIH)</t>
         </is>
       </c>
-      <c r="E8" s="35" t="inlineStr">
+      <c r="E8" s="32" t="inlineStr">
+        <is>
+          <t>Alimentação</t>
+        </is>
+      </c>
+      <c r="F8" s="35" t="inlineStr">
         <is>
           <t>https://www.nccih.nih.gov/health/red-yeast-rice</t>
         </is>
@@ -3214,7 +3257,12 @@
           <t>Revisão científica revisada por pares</t>
         </is>
       </c>
-      <c r="E9" s="35" t="inlineStr">
+      <c r="E9" s="32" t="inlineStr">
+        <is>
+          <t>Alimentação</t>
+        </is>
+      </c>
+      <c r="F9" s="35" t="inlineStr">
         <is>
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC3589309/</t>
         </is>
@@ -3239,7 +3287,12 @@
           <t>Diretriz de sociedades médicas (ACC/AHA)</t>
         </is>
       </c>
-      <c r="E10" s="35" t="inlineStr">
+      <c r="E10" s="32" t="inlineStr">
+        <is>
+          <t>Alimentação</t>
+        </is>
+      </c>
+      <c r="F10" s="35" t="inlineStr">
         <is>
           <t>https://www.acc.org/latest-in-cardiology/ten-points-to-remember/2016/03/25/14/56/2016-acc-aha-guideline-focused-update-on-dapt</t>
         </is>
@@ -3264,7 +3317,12 @@
           <t>Diretriz de sociedade médica (SBC)</t>
         </is>
       </c>
-      <c r="E11" s="35" t="inlineStr">
+      <c r="E11" s="32" t="inlineStr">
+        <is>
+          <t>Alimentação</t>
+        </is>
+      </c>
+      <c r="F11" s="35" t="inlineStr">
         <is>
           <t>https://www.scielo.br/j/abc/a/tRJrwGzKX6C4GvMqdJpZcGk/?lang=pt</t>
         </is>
@@ -3289,7 +3347,12 @@
           <t>Diretriz de sociedade médica (AHA)</t>
         </is>
       </c>
-      <c r="E12" s="35" t="inlineStr">
+      <c r="E12" s="32" t="inlineStr">
+        <is>
+          <t>Alimentação</t>
+        </is>
+      </c>
+      <c r="F12" s="35" t="inlineStr">
         <is>
           <t>https://www.heart.org/en/healthy-living/healthy-eating/eat-smart/nutrition-basics/aha-diet-and-lifestyle-recommendations</t>
         </is>
@@ -3314,24 +3377,389 @@
           <t>Diretriz de sociedade médica (SBC)</t>
         </is>
       </c>
-      <c r="E13" s="35" t="inlineStr">
+      <c r="E13" s="32" t="inlineStr">
+        <is>
+          <t>Alimentação</t>
+        </is>
+      </c>
+      <c r="F13" s="35" t="inlineStr">
         <is>
           <t>https://www.scielo.br/j/abc/a/X94tMKwdnBjkCzVKpXwBqmD/?lang=pt</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="16" t="inlineStr">
-        <is>
-          <t>Lista completa com os mesmos links (mais fácil de clicar em Markdown) também em referencia/dados-consulta-e-alimentacao.md, seção 1b.</t>
+    <row r="14" ht="44" customHeight="1">
+      <c r="A14" s="32" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="33" t="inlineStr">
+        <is>
+          <t>Critério objetivo de Lesão Renal Aguda (LRA) estágio 1: creatinina sobe ≥0,3 mg/dL em 48h</t>
+        </is>
+      </c>
+      <c r="C14" s="34" t="inlineStr">
+        <is>
+          <t>KDIGO — Clinical Practice Guideline for Acute Kidney Injury, 2012</t>
+        </is>
+      </c>
+      <c r="D14" s="33" t="inlineStr">
+        <is>
+          <t>Diretriz de sociedade médica (KDIGO)</t>
+        </is>
+      </c>
+      <c r="E14" s="32" t="inlineStr">
+        <is>
+          <t>Clínico geral</t>
+        </is>
+      </c>
+      <c r="F14" s="35" t="inlineStr">
+        <is>
+          <t>https://kdigo.org/wp-content/uploads/2016/10/KDIGO-2012-AKI-Guideline-English.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="44" customHeight="1">
+      <c r="A15" s="32" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="33" t="inlineStr">
+        <is>
+          <t>Exame padrão para proteinúria é a relação albumina/creatinina urinária (ACR/RAC), categorias A1/A2/A3</t>
+        </is>
+      </c>
+      <c r="C15" s="34" t="inlineStr">
+        <is>
+          <t>KDIGO — Clinical Practice Guideline for CKD, 2012 (categorias mantidas na atualização 2024)</t>
+        </is>
+      </c>
+      <c r="D15" s="33" t="inlineStr">
+        <is>
+          <t>Diretriz de sociedade médica (KDIGO)</t>
+        </is>
+      </c>
+      <c r="E15" s="32" t="inlineStr">
+        <is>
+          <t>Clínico geral</t>
+        </is>
+      </c>
+      <c r="F15" s="35" t="inlineStr">
+        <is>
+          <t>https://kdigo.org/wp-content/uploads/2017/02/KDIGO_2012_CKD_GL.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="44" customHeight="1">
+      <c r="A16" s="32" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="33" t="inlineStr">
+        <is>
+          <t>Múltiplas exposições a contraste em dias próximos são fator de risco para lesão renal por contraste, com pico em 3-5 dias e resolução em 7-14 dias</t>
+        </is>
+      </c>
+      <c r="C16" s="34" t="inlineStr">
+        <is>
+          <t>ESUR — Post-contrast acute kidney injury, Guidelines v10.0, 2018</t>
+        </is>
+      </c>
+      <c r="D16" s="33" t="inlineStr">
+        <is>
+          <t>Diretriz de sociedade médica (ESUR)</t>
+        </is>
+      </c>
+      <c r="E16" s="32" t="inlineStr">
+        <is>
+          <t>Clínico geral</t>
+        </is>
+      </c>
+      <c r="F16" s="35" t="inlineStr">
+        <is>
+          <t>https://www.esur.org/wp-content/uploads/2022/03/ESUR-Guidelines-10_0-Final-Version.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="44" customHeight="1">
+      <c r="A17" s="32" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="33" t="inlineStr">
+        <is>
+          <t>Definição de infarto periprocedimento (tipo 4a): troponina &gt;5x o limite superior + evidência de nova isquemia</t>
+        </is>
+      </c>
+      <c r="C17" s="34" t="inlineStr">
+        <is>
+          <t>Thygesen K, Alpert JS et al. — Fourth Universal Definition of Myocardial Infarction, 2018</t>
+        </is>
+      </c>
+      <c r="D17" s="33" t="inlineStr">
+        <is>
+          <t>Documento conjunto de sociedades médicas (ESC/ACC/AHA/WHF)</t>
+        </is>
+      </c>
+      <c r="E17" s="32" t="inlineStr">
+        <is>
+          <t>Clínico geral</t>
+        </is>
+      </c>
+      <c r="F17" s="35" t="inlineStr">
+        <is>
+          <t>https://www.ahajournals.org/doi/10.1161/CIR.0000000000000617</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="44" customHeight="1">
+      <c r="A18" s="32" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="33" t="inlineStr">
+        <is>
+          <t>Limiares de segurança para manter um IECA (Enalapril): potássio até 5,5 mmol/L e creatinina com alta até 50% (abaixo de 3 mg/dL) são toleráveis; reexame em 1-2 semanas</t>
+        </is>
+      </c>
+      <c r="C18" s="34" t="inlineStr">
+        <is>
+          <t>ESC — Guidelines for the diagnosis and treatment of acute and chronic heart failure, 2021</t>
+        </is>
+      </c>
+      <c r="D18" s="33" t="inlineStr">
+        <is>
+          <t>Diretriz de sociedade médica (ESC)</t>
+        </is>
+      </c>
+      <c r="E18" s="32" t="inlineStr">
+        <is>
+          <t>Clínico geral</t>
+        </is>
+      </c>
+      <c r="F18" s="35" t="inlineStr">
+        <is>
+          <t>https://academic.oup.com/eurheartj/article/42/36/3599/6358045</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="44" customHeight="1">
+      <c r="A19" s="32" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="33" t="inlineStr">
+        <is>
+          <t>Reforço da duração de 12 meses de dupla antiagregação após síndrome coronariana aguda</t>
+        </is>
+      </c>
+      <c r="C19" s="34" t="inlineStr">
+        <is>
+          <t>ESC — Guidelines for the management of acute coronary syndromes, 2023</t>
+        </is>
+      </c>
+      <c r="D19" s="33" t="inlineStr">
+        <is>
+          <t>Diretriz de sociedade médica (ESC)</t>
+        </is>
+      </c>
+      <c r="E19" s="32" t="inlineStr">
+        <is>
+          <t>Clínico geral</t>
+        </is>
+      </c>
+      <c r="F19" s="35" t="inlineStr">
+        <is>
+          <t>https://academic.oup.com/eurheartj/article/45/14/1193/7516285</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="44" customHeight="1">
+      <c r="A20" s="32" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" s="33" t="inlineStr">
+        <is>
+          <t>Encaminhamento para reabilitação cardíaca antes da alta é recomendação Classe 1 (a mais forte) após síndrome coronariana aguda</t>
+        </is>
+      </c>
+      <c r="C20" s="34" t="inlineStr">
+        <is>
+          <t>ACC/AHA/ACEP/NAEMSP/SCAI — Guideline for the Management of Patients With Acute Coronary Syndromes, 2025</t>
+        </is>
+      </c>
+      <c r="D20" s="33" t="inlineStr">
+        <is>
+          <t>Diretriz de sociedades médicas (ACC/AHA e outras)</t>
+        </is>
+      </c>
+      <c r="E20" s="32" t="inlineStr">
+        <is>
+          <t>Clínico geral</t>
+        </is>
+      </c>
+      <c r="F20" s="35" t="inlineStr">
+        <is>
+          <t>https://www.ahajournals.org/doi/10.1161/CIR.0000000000001309</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="44" customHeight="1">
+      <c r="A21" s="32" t="n">
+        <v>18</v>
+      </c>
+      <c r="B21" s="33" t="inlineStr">
+        <is>
+          <t>Estudo que sustenta a combinação estatina + ezetimiba para reduzir LDL após síndrome coronariana aguda (IMPROVE-IT)</t>
+        </is>
+      </c>
+      <c r="C21" s="34" t="inlineStr">
+        <is>
+          <t>Cannon CP et al. — Ezetimibe Added to Statin Therapy after Acute Coronary Syndromes, N Engl J Med 2015</t>
+        </is>
+      </c>
+      <c r="D21" s="33" t="inlineStr">
+        <is>
+          <t>Estudo clínico revisado por pares</t>
+        </is>
+      </c>
+      <c r="E21" s="32" t="inlineStr">
+        <is>
+          <t>Alimentação</t>
+        </is>
+      </c>
+      <c r="F21" s="35" t="inlineStr">
+        <is>
+          <t>https://www.nejm.org/doi/full/10.1056/NEJMoa1410489</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="44" customHeight="1">
+      <c r="A22" s="32" t="n">
+        <v>19</v>
+      </c>
+      <c r="B22" s="33" t="inlineStr">
+        <is>
+          <t>HbA1c ≥6,5% sugere diabetes prévio; abaixo de 5,7% (caso do paciente) é consistente com hiperglicemia de estresse, não diabetes</t>
+        </is>
+      </c>
+      <c r="C22" s="34" t="inlineStr">
+        <is>
+          <t>American Diabetes Association — Standards of Care in Diabetes, edições 2024-2026</t>
+        </is>
+      </c>
+      <c r="D22" s="33" t="inlineStr">
+        <is>
+          <t>Diretriz de sociedade médica (ADA)</t>
+        </is>
+      </c>
+      <c r="E22" s="32" t="inlineStr">
+        <is>
+          <t>Clínico geral</t>
+        </is>
+      </c>
+      <c r="F22" s="35" t="inlineStr">
+        <is>
+          <t>https://diabetesjournals.org/care/article/49/Supplement_1/S339/163925/16-Diabetes-Care-in-the-Hospital-Standards-of-Care</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="44" customHeight="1">
+      <c r="A23" s="32" t="n">
+        <v>20</v>
+      </c>
+      <c r="B23" s="33" t="inlineStr">
+        <is>
+          <t>Até 60% dos pacientes com hiperglicemia de estresse na internação desenvolvem diabetes em 6-12 meses</t>
+        </is>
+      </c>
+      <c r="C23" s="34" t="inlineStr">
+        <is>
+          <t>Sociedade Brasileira de Diabetes — Hiperglicemia Hospitalar no Paciente Não-Crítico</t>
+        </is>
+      </c>
+      <c r="D23" s="33" t="inlineStr">
+        <is>
+          <t>Diretriz de sociedade médica (SBD)</t>
+        </is>
+      </c>
+      <c r="E23" s="32" t="inlineStr">
+        <is>
+          <t>Clínico geral</t>
+        </is>
+      </c>
+      <c r="F23" s="35" t="inlineStr">
+        <is>
+          <t>https://diretriz.diabetes.org.br/hiperglicemia-hospitalar-em-paciente-nao-critico/</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="44" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>21</v>
+      </c>
+      <c r="B24" s="33" t="inlineStr">
+        <is>
+          <t>Placa carotídea com estenose abaixo de 50% é tratada de forma conservadora (antiagregante, estatina, controle de pressão), sem indicação de cirurgia</t>
+        </is>
+      </c>
+      <c r="C24" s="34" t="inlineStr">
+        <is>
+          <t>ESC/ESVS — Guidelines on Peripheral Arterial Diseases (2017/2018) e atualização sobre doença carotídea/vertebral (2023)</t>
+        </is>
+      </c>
+      <c r="D24" s="33" t="inlineStr">
+        <is>
+          <t>Diretriz de sociedade médica (ESC/ESVS)</t>
+        </is>
+      </c>
+      <c r="E24" s="32" t="inlineStr">
+        <is>
+          <t>Clínico geral</t>
+        </is>
+      </c>
+      <c r="F24" s="35" t="inlineStr">
+        <is>
+          <t>https://academic.oup.com/eurheartj/article/39/9/763/4095038</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="44" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>22</v>
+      </c>
+      <c r="B25" s="33" t="inlineStr">
+        <is>
+          <t>Mesma conduta conservadora para placa carotídea leve, do lado da prevenção de AVC</t>
+        </is>
+      </c>
+      <c r="C25" s="34" t="inlineStr">
+        <is>
+          <t>AHA/ASA — Guideline for the Prevention of Stroke in Patients With Stroke and TIA, 2021</t>
+        </is>
+      </c>
+      <c r="D25" s="33" t="inlineStr">
+        <is>
+          <t>Diretriz de sociedade médica (AHA/ASA)</t>
+        </is>
+      </c>
+      <c r="E25" s="32" t="inlineStr">
+        <is>
+          <t>Clínico geral</t>
+        </is>
+      </c>
+      <c r="F25" s="35" t="inlineStr">
+        <is>
+          <t>https://www.ahajournals.org/doi/10.1161/STR.0000000000000375</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="24" customHeight="1">
+      <c r="A27" s="16" t="inlineStr">
+        <is>
+          <t>Lista completa com os mesmos links (mais fácil de clicar em Markdown) também em referencia/historico-tratamento.md, seção 'Referências médicas'.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A15:E15"/>
-    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A27:F27"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId1"/>
@@ -3344,6 +3772,18 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C23" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C24" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C25" r:id="rId22"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/planilha/plano-alimentar-pos-infarto.xlsx
+++ b/planilha/plano-alimentar-pos-infarto.xlsx
@@ -1061,7 +1061,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F47"/>
+  <dimension ref="A1:F48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1606,266 +1606,266 @@
     <row r="25" ht="30" customHeight="1">
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>Iogurte natural (desnatado, sem açúcar)</t>
+          <t>Mussarela</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>1 unidade</t>
+          <t>30 g</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>1x/dia</t>
-        </is>
-      </c>
-      <c r="E25" s="13" t="inlineStr">
-        <is>
-          <t>Liberado</t>
+          <t>2x/semana</t>
+        </is>
+      </c>
+      <c r="E25" s="14" t="inlineStr">
+        <is>
+          <t>Moderar</t>
         </is>
       </c>
       <c r="F25" s="11" t="inlineStr">
         <is>
-          <t>Prefira sempre a versão sem açúcar adicionado</t>
+          <t>Mais gordura saturada e sódio que o queijo branco; prefira o queijo branco no dia a dia. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="30" customHeight="1">
       <c r="B26" s="11" t="inlineStr">
         <is>
+          <t>Iogurte natural (desnatado, sem açúcar)</t>
+        </is>
+      </c>
+      <c r="C26" s="12" t="inlineStr">
+        <is>
+          <t>1 unidade</t>
+        </is>
+      </c>
+      <c r="D26" s="12" t="inlineStr">
+        <is>
+          <t>1x/dia</t>
+        </is>
+      </c>
+      <c r="E26" s="13" t="inlineStr">
+        <is>
+          <t>Liberado</t>
+        </is>
+      </c>
+      <c r="F26" s="11" t="inlineStr">
+        <is>
+          <t>Prefira sempre a versão sem açúcar adicionado</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="30" customHeight="1">
+      <c r="B27" s="11" t="inlineStr">
+        <is>
           <t>Requeijão</t>
         </is>
       </c>
-      <c r="C26" s="12" t="inlineStr">
+      <c r="C27" s="12" t="inlineStr">
         <is>
           <t>1 colher de sopa (≈15 g)</t>
         </is>
       </c>
-      <c r="D26" s="12" t="inlineStr">
+      <c r="D27" s="12" t="inlineStr">
         <is>
           <t>2x/semana</t>
         </is>
       </c>
-      <c r="E26" s="14" t="inlineStr">
+      <c r="E27" s="14" t="inlineStr">
         <is>
           <t>Moderar</t>
         </is>
       </c>
-      <c r="F26" s="11" t="inlineStr">
+      <c r="F27" s="11" t="inlineStr">
         <is>
           <t>Rico em gordura saturada e sódio; prefira a versão light. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="9" t="inlineStr">
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="9" t="inlineStr">
         <is>
           <t>Bebidas</t>
         </is>
       </c>
-      <c r="B27" s="10" t="n"/>
-      <c r="C27" s="10" t="n"/>
-      <c r="D27" s="10" t="n"/>
-      <c r="E27" s="10" t="n"/>
-      <c r="F27" s="10" t="n"/>
-    </row>
-    <row r="28" ht="30" customHeight="1">
-      <c r="B28" s="11" t="inlineStr">
-        <is>
-          <t>Água</t>
-        </is>
-      </c>
-      <c r="C28" s="12" t="inlineStr">
-        <is>
-          <t>à vontade</t>
-        </is>
-      </c>
-      <c r="D28" s="12" t="inlineStr">
-        <is>
-          <t>todos os dias</t>
-        </is>
-      </c>
-      <c r="E28" s="13" t="inlineStr">
-        <is>
-          <t>Liberado</t>
-        </is>
-      </c>
-      <c r="F28" s="11" t="inlineStr"/>
+      <c r="B28" s="10" t="n"/>
+      <c r="C28" s="10" t="n"/>
+      <c r="D28" s="10" t="n"/>
+      <c r="E28" s="10" t="n"/>
+      <c r="F28" s="10" t="n"/>
     </row>
     <row r="29" ht="30" customHeight="1">
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>Refrigerante zero</t>
+          <t>Água</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>200 ml</t>
+          <t>à vontade</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>1x/dia</t>
-        </is>
-      </c>
-      <c r="E29" s="14" t="inlineStr">
-        <is>
-          <t>Moderar</t>
-        </is>
-      </c>
-      <c r="F29" s="11" t="inlineStr">
-        <is>
-          <t>Sugestão gerada por IA — confirmar com nutricionista/cardiologista</t>
-        </is>
-      </c>
+          <t>todos os dias</t>
+        </is>
+      </c>
+      <c r="E29" s="13" t="inlineStr">
+        <is>
+          <t>Liberado</t>
+        </is>
+      </c>
+      <c r="F29" s="11" t="inlineStr"/>
     </row>
     <row r="30" ht="30" customHeight="1">
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>Café sem açúcar</t>
+          <t>Refrigerante zero</t>
         </is>
       </c>
       <c r="C30" s="12" t="inlineStr">
         <is>
-          <t>1 xícara</t>
+          <t>200 ml</t>
         </is>
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
-          <t>2x/dia</t>
-        </is>
-      </c>
-      <c r="E30" s="13" t="inlineStr">
-        <is>
-          <t>Liberado</t>
-        </is>
-      </c>
-      <c r="F30" s="11" t="inlineStr"/>
+          <t>1x/dia</t>
+        </is>
+      </c>
+      <c r="E30" s="14" t="inlineStr">
+        <is>
+          <t>Moderar</t>
+        </is>
+      </c>
+      <c r="F30" s="11" t="inlineStr">
+        <is>
+          <t>Sugestão gerada por IA — confirmar com nutricionista/cardiologista</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="30" customHeight="1">
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>Suco natural sem açúcar</t>
+          <t>Café sem açúcar</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>200 ml</t>
+          <t>1 xícara</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>3x/semana</t>
-        </is>
-      </c>
-      <c r="E31" s="14" t="inlineStr">
-        <is>
-          <t>Moderar</t>
-        </is>
-      </c>
-      <c r="F31" s="11" t="inlineStr">
-        <is>
-          <t>Preferir a fruta inteira, que tem mais fibra</t>
-        </is>
-      </c>
+          <t>2x/dia</t>
+        </is>
+      </c>
+      <c r="E31" s="13" t="inlineStr">
+        <is>
+          <t>Liberado</t>
+        </is>
+      </c>
+      <c r="F31" s="11" t="inlineStr"/>
     </row>
     <row r="32" ht="30" customHeight="1">
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>Suco de toranja / grapefruit</t>
+          <t>Suco natural sem açúcar</t>
         </is>
       </c>
       <c r="C32" s="12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>200 ml</t>
         </is>
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
-          <t>evitar</t>
-        </is>
-      </c>
-      <c r="E32" s="15" t="inlineStr">
-        <is>
-          <t>Evitar</t>
+          <t>3x/semana</t>
+        </is>
+      </c>
+      <c r="E32" s="14" t="inlineStr">
+        <is>
+          <t>Moderar</t>
         </is>
       </c>
       <c r="F32" s="11" t="inlineStr">
         <is>
-          <t>Interage com o Ticagrelor (estudo mostrou quase o dobro do nível do remédio no sangue); a bula diz que não é esperado ser clinicamente relevante p/ a maioria, mas orienta evitar — mais seguro evitar, já que você toma 2 antiagregantes. Ver aba Fontes e Referências.</t>
+          <t>Preferir a fruta inteira, que tem mais fibra</t>
         </is>
       </c>
     </row>
     <row r="33" ht="30" customHeight="1">
       <c r="B33" s="11" t="inlineStr">
         <is>
+          <t>Suco de toranja / grapefruit</t>
+        </is>
+      </c>
+      <c r="C33" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D33" s="12" t="inlineStr">
+        <is>
+          <t>evitar</t>
+        </is>
+      </c>
+      <c r="E33" s="15" t="inlineStr">
+        <is>
+          <t>Evitar</t>
+        </is>
+      </c>
+      <c r="F33" s="11" t="inlineStr">
+        <is>
+          <t>Interage com o Ticagrelor (estudo mostrou quase o dobro do nível do remédio no sangue); a bula diz que não é esperado ser clinicamente relevante p/ a maioria, mas orienta evitar — mais seguro evitar, já que você toma 2 antiagregantes. Ver aba Fontes e Referências.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="30" customHeight="1">
+      <c r="B34" s="11" t="inlineStr">
+        <is>
           <t>Bebida alcoólica</t>
         </is>
       </c>
-      <c r="C33" s="12" t="inlineStr">
+      <c r="C34" s="12" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D33" s="12" t="inlineStr">
+      <c r="D34" s="12" t="inlineStr">
         <is>
           <t>evitar</t>
         </is>
       </c>
-      <c r="E33" s="15" t="inlineStr">
+      <c r="E34" s="15" t="inlineStr">
         <is>
           <t>Evitar</t>
         </is>
       </c>
-      <c r="F33" s="11" t="inlineStr">
+      <c r="F34" s="11" t="inlineStr">
         <is>
           <t>Piora diretamente os triglicerídeos; soma-se ao risco de sangramento da Aspirina + Ticagrelor.</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="20" customHeight="1">
-      <c r="A34" s="9" t="inlineStr">
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="9" t="inlineStr">
         <is>
           <t>Doces e Sobremesas</t>
         </is>
       </c>
-      <c r="B34" s="10" t="n"/>
-      <c r="C34" s="10" t="n"/>
-      <c r="D34" s="10" t="n"/>
-      <c r="E34" s="10" t="n"/>
-      <c r="F34" s="10" t="n"/>
-    </row>
-    <row r="35" ht="30" customHeight="1">
-      <c r="B35" s="11" t="inlineStr">
-        <is>
-          <t>Açúcar refinado</t>
-        </is>
-      </c>
-      <c r="C35" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D35" s="12" t="inlineStr">
-        <is>
-          <t>evitar</t>
-        </is>
-      </c>
-      <c r="E35" s="15" t="inlineStr">
-        <is>
-          <t>Evitar</t>
-        </is>
-      </c>
-      <c r="F35" s="11" t="inlineStr">
-        <is>
-          <t>Impacto direto nos triglicerídeos</t>
-        </is>
-      </c>
+      <c r="B35" s="10" t="n"/>
+      <c r="C35" s="10" t="n"/>
+      <c r="D35" s="10" t="n"/>
+      <c r="E35" s="10" t="n"/>
+      <c r="F35" s="10" t="n"/>
     </row>
     <row r="36" ht="30" customHeight="1">
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>Doces industrializados</t>
+          <t>Açúcar refinado</t>
         </is>
       </c>
       <c r="C36" s="12" t="inlineStr">
@@ -1883,215 +1883,242 @@
           <t>Evitar</t>
         </is>
       </c>
-      <c r="F36" s="11" t="inlineStr"/>
+      <c r="F36" s="11" t="inlineStr">
+        <is>
+          <t>Impacto direto nos triglicerídeos</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="30" customHeight="1">
       <c r="B37" s="11" t="inlineStr">
         <is>
+          <t>Doces industrializados</t>
+        </is>
+      </c>
+      <c r="C37" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D37" s="12" t="inlineStr">
+        <is>
+          <t>evitar</t>
+        </is>
+      </c>
+      <c r="E37" s="15" t="inlineStr">
+        <is>
+          <t>Evitar</t>
+        </is>
+      </c>
+      <c r="F37" s="11" t="inlineStr"/>
+    </row>
+    <row r="38" ht="30" customHeight="1">
+      <c r="B38" s="11" t="inlineStr">
+        <is>
           <t>Chocolate amargo (70%+)</t>
         </is>
       </c>
-      <c r="C37" s="12" t="inlineStr">
+      <c r="C38" s="12" t="inlineStr">
         <is>
           <t>10 g</t>
         </is>
       </c>
-      <c r="D37" s="12" t="inlineStr">
+      <c r="D38" s="12" t="inlineStr">
         <is>
           <t>2x/semana</t>
         </is>
       </c>
-      <c r="E37" s="14" t="inlineStr">
+      <c r="E38" s="14" t="inlineStr">
         <is>
           <t>Moderar</t>
         </is>
       </c>
-      <c r="F37" s="11" t="inlineStr">
+      <c r="F38" s="11" t="inlineStr">
         <is>
           <t>Sugestão gerada por IA — confirmar com nutricionista/cardiologista</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="20" customHeight="1">
-      <c r="A38" s="9" t="inlineStr">
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="9" t="inlineStr">
         <is>
           <t>Gorduras e Temperos</t>
         </is>
       </c>
-      <c r="B38" s="10" t="n"/>
-      <c r="C38" s="10" t="n"/>
-      <c r="D38" s="10" t="n"/>
-      <c r="E38" s="10" t="n"/>
-      <c r="F38" s="10" t="n"/>
-    </row>
-    <row r="39" ht="30" customHeight="1">
-      <c r="B39" s="11" t="inlineStr">
-        <is>
-          <t>Azeite de oliva extra virgem</t>
-        </is>
-      </c>
-      <c r="C39" s="12" t="inlineStr">
-        <is>
-          <t>1-2 colheres de sopa</t>
-        </is>
-      </c>
-      <c r="D39" s="12" t="inlineStr">
-        <is>
-          <t>1x/dia</t>
-        </is>
-      </c>
-      <c r="E39" s="13" t="inlineStr">
-        <is>
-          <t>Liberado</t>
-        </is>
-      </c>
-      <c r="F39" s="11" t="inlineStr"/>
+      <c r="B39" s="10" t="n"/>
+      <c r="C39" s="10" t="n"/>
+      <c r="D39" s="10" t="n"/>
+      <c r="E39" s="10" t="n"/>
+      <c r="F39" s="10" t="n"/>
     </row>
     <row r="40" ht="30" customHeight="1">
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>Manteiga</t>
+          <t>Azeite de oliva extra virgem</t>
         </is>
       </c>
       <c r="C40" s="12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1-2 colheres de sopa</t>
         </is>
       </c>
       <c r="D40" s="12" t="inlineStr">
         <is>
-          <t>evitar</t>
-        </is>
-      </c>
-      <c r="E40" s="15" t="inlineStr">
-        <is>
-          <t>Evitar</t>
-        </is>
-      </c>
-      <c r="F40" s="11" t="inlineStr">
-        <is>
-          <t>Preferir azeite</t>
-        </is>
-      </c>
+          <t>1x/dia</t>
+        </is>
+      </c>
+      <c r="E40" s="13" t="inlineStr">
+        <is>
+          <t>Liberado</t>
+        </is>
+      </c>
+      <c r="F40" s="11" t="inlineStr"/>
     </row>
     <row r="41" ht="30" customHeight="1">
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>Sal</t>
+          <t>Manteiga</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>&lt; 5 g no total</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
-          <t>todos os dias</t>
-        </is>
-      </c>
-      <c r="E41" s="14" t="inlineStr">
-        <is>
-          <t>Moderar</t>
+          <t>evitar</t>
+        </is>
+      </c>
+      <c r="E41" s="15" t="inlineStr">
+        <is>
+          <t>Evitar</t>
         </is>
       </c>
       <c r="F41" s="11" t="inlineStr">
         <is>
-          <t>Somar sal de cozinha + industrializados</t>
+          <t>Preferir azeite</t>
         </is>
       </c>
     </row>
     <row r="42" ht="30" customHeight="1">
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>Sal light / substituto de sal (cloreto de potássio)</t>
+          <t>Sal</t>
         </is>
       </c>
       <c r="C42" s="12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>&lt; 5 g no total</t>
         </is>
       </c>
       <c r="D42" s="12" t="inlineStr">
         <is>
-          <t>evitar</t>
-        </is>
-      </c>
-      <c r="E42" s="15" t="inlineStr">
-        <is>
-          <t>Evitar</t>
+          <t>todos os dias</t>
+        </is>
+      </c>
+      <c r="E42" s="14" t="inlineStr">
+        <is>
+          <t>Moderar</t>
         </is>
       </c>
       <c r="F42" s="11" t="inlineStr">
         <is>
-          <t>Enalapril já tende a elevar o potássio; combinado com esse produto o risco de hipercalemia aumenta, ainda mais com a função renal pendente.</t>
+          <t>Somar sal de cozinha + industrializados</t>
         </is>
       </c>
     </row>
     <row r="43" ht="30" customHeight="1">
       <c r="B43" s="11" t="inlineStr">
         <is>
+          <t>Sal light / substituto de sal (cloreto de potássio)</t>
+        </is>
+      </c>
+      <c r="C43" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D43" s="12" t="inlineStr">
+        <is>
+          <t>evitar</t>
+        </is>
+      </c>
+      <c r="E43" s="15" t="inlineStr">
+        <is>
+          <t>Evitar</t>
+        </is>
+      </c>
+      <c r="F43" s="11" t="inlineStr">
+        <is>
+          <t>Enalapril já tende a elevar o potássio; combinado com esse produto o risco de hipercalemia aumenta, ainda mais com a função renal pendente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="30" customHeight="1">
+      <c r="B44" s="11" t="inlineStr">
+        <is>
           <t>Ervas e temperos naturais</t>
         </is>
       </c>
-      <c r="C43" s="12" t="inlineStr">
+      <c r="C44" s="12" t="inlineStr">
         <is>
           <t>à vontade</t>
         </is>
       </c>
-      <c r="D43" s="12" t="inlineStr">
+      <c r="D44" s="12" t="inlineStr">
         <is>
           <t>todos os dias</t>
         </is>
       </c>
-      <c r="E43" s="13" t="inlineStr">
+      <c r="E44" s="13" t="inlineStr">
         <is>
           <t>Liberado</t>
         </is>
       </c>
-      <c r="F43" s="11" t="inlineStr"/>
-    </row>
-    <row r="44" ht="20" customHeight="1">
-      <c r="A44" s="9" t="inlineStr">
+      <c r="F44" s="11" t="inlineStr"/>
+    </row>
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="9" t="inlineStr">
         <is>
           <t>Vegetais e Verduras</t>
         </is>
       </c>
-      <c r="B44" s="10" t="n"/>
-      <c r="C44" s="10" t="n"/>
-      <c r="D44" s="10" t="n"/>
-      <c r="E44" s="10" t="n"/>
-      <c r="F44" s="10" t="n"/>
-    </row>
-    <row r="45" ht="30" customHeight="1">
-      <c r="B45" s="11" t="inlineStr">
+      <c r="B45" s="10" t="n"/>
+      <c r="C45" s="10" t="n"/>
+      <c r="D45" s="10" t="n"/>
+      <c r="E45" s="10" t="n"/>
+      <c r="F45" s="10" t="n"/>
+    </row>
+    <row r="46" ht="30" customHeight="1">
+      <c r="B46" s="11" t="inlineStr">
         <is>
           <t>Vegetais e verduras em geral</t>
         </is>
       </c>
-      <c r="C45" s="12" t="inlineStr">
+      <c r="C46" s="12" t="inlineStr">
         <is>
           <t>à vontade</t>
         </is>
       </c>
-      <c r="D45" s="12" t="inlineStr">
+      <c r="D46" s="12" t="inlineStr">
         <is>
           <t>todos os dias</t>
         </is>
       </c>
-      <c r="E45" s="13" t="inlineStr">
+      <c r="E46" s="13" t="inlineStr">
         <is>
           <t>Liberado</t>
         </is>
       </c>
-      <c r="F45" s="11" t="inlineStr">
+      <c r="F46" s="11" t="inlineStr">
         <is>
           <t>Se entrar anticoagulante na medicação, revisar consumo de verde-escuros ricos em vitamina K</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="30" customHeight="1">
-      <c r="A47" s="16" t="inlineStr">
+    <row r="48" ht="30" customHeight="1">
+      <c r="A48" s="16" t="inlineStr">
         <is>
           <t>Lista com os alimentos acrescentados até agora — não é uma lista completa. Use a skill 'adicionar-alimento' (ex.: "adicione sucrilhos") para ir acrescentando novos itens aos poucos.</t>
         </is>
@@ -2099,16 +2126,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="A38:F38"/>
     <mergeCell ref="A16:F16"/>
     <mergeCell ref="A11:F11"/>
-    <mergeCell ref="A47:F47"/>
-    <mergeCell ref="A44:F44"/>
+    <mergeCell ref="A28:F28"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A27:F27"/>
+    <mergeCell ref="A45:F45"/>
     <mergeCell ref="A22:F22"/>
-    <mergeCell ref="A34:F34"/>
+    <mergeCell ref="A35:F35"/>
     <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A48:F48"/>
+    <mergeCell ref="A39:F39"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3795,7 +3822,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U35"/>
+  <dimension ref="A1:U36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4889,7 +4916,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Requeijão</t>
+          <t>Mussarela</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -4963,7 +4990,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Refrigerante zero</t>
+          <t>Requeijão</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -5023,7 +5050,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Requeijão</t>
+          <t>Mussarela</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -5033,7 +5060,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Suco natural sem açúcar</t>
+          <t>Refrigerante zero</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -5093,17 +5120,17 @@
       <c r="J17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
+          <t>Requeijão</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Sal light / substituto de sal (cloreto de potássio)</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
           <t>Suco natural sem açúcar</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>Sal light / substituto de sal (cloreto de potássio)</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>Chocolate amargo (70%+)</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -5167,12 +5194,12 @@
       <c r="J18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Toranja / grapefruit</t>
+          <t>Suco natural sem açúcar</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Toranja / grapefruit</t>
+          <t>Chocolate amargo (70%+)</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -5189,7 +5216,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Iogurte natural (desnatado, sem açúcar)</t>
+          <t>Mussarela</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5199,22 +5226,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Liberado</t>
+          <t>Moderar</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1 unidade</t>
+          <t>30 g</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1x/dia</t>
+          <t>2x/semana</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Prefira sempre a versão sem açúcar adicionado</t>
+          <t>Mais gordura saturada e sódio que o queijo branco; prefira o queijo branco no dia a dia. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -5231,12 +5258,12 @@
       <c r="J19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Suco de toranja / grapefruit</t>
+          <t>Toranja / grapefruit</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Suco de toranja / grapefruit</t>
+          <t>Toranja / grapefruit</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -5253,7 +5280,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Requeijão</t>
+          <t>Iogurte natural (desnatado, sem açúcar)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5263,22 +5290,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Moderar</t>
+          <t>Liberado</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1 colher de sopa (≈15 g)</t>
+          <t>1 unidade</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2x/semana</t>
+          <t>1x/dia</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rico em gordura saturada e sódio; prefira a versão light. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
+          <t>Prefira sempre a versão sem açúcar adicionado</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -5295,12 +5322,12 @@
       <c r="J20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Açúcar refinado</t>
+          <t>Suco de toranja / grapefruit</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Açúcar refinado</t>
+          <t>Suco de toranja / grapefruit</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
@@ -5317,58 +5344,54 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Água</t>
+          <t>Requeijão</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Bebidas</t>
+          <t>Laticínios</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Liberado</t>
+          <t>Moderar</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>à vontade</t>
+          <t>1 colher de sopa (≈15 g)</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>todos os dias</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr"/>
+          <t>2x/semana</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Rico em gordura saturada e sódio; prefira a versão light. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
+        </is>
+      </c>
       <c r="G21" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="J21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Manteiga</t>
+          <t>Açúcar refinado</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Doces industrializados</t>
+          <t>Açúcar refinado</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
@@ -5385,7 +5408,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Refrigerante zero</t>
+          <t>Água</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5395,25 +5418,25 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Moderar</t>
+          <t>Liberado</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>200 ml</t>
+          <t>à vontade</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1x/dia</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Sugestão gerada por IA — confirmar com nutricionista/cardiologista</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr"/>
+          <t>todos os dias</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="H22" t="inlineStr">
         <is>
           <t>X</t>
@@ -5427,6 +5450,16 @@
       <c r="J22" t="inlineStr">
         <is>
           <t>X</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Manteiga</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Doces industrializados</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
@@ -5443,7 +5476,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Café sem açúcar</t>
+          <t>Refrigerante zero</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -5453,32 +5486,40 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Liberado</t>
+          <t>Moderar</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1 xícara</t>
+          <t>200 ml</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2x/dia</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr"/>
+          <t>1x/dia</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Sugestão gerada por IA — confirmar com nutricionista/cardiologista</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="Q23" t="inlineStr">
         <is>
           <t>Proteínas|Jantar</t>
@@ -5493,7 +5534,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Suco natural sem açúcar</t>
+          <t>Café sem açúcar</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5503,24 +5544,20 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Moderar</t>
+          <t>Liberado</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>200 ml</t>
+          <t>1 xícara</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>3x/semana</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Preferir a fruta inteira, que tem mais fibra</t>
-        </is>
-      </c>
+          <t>2x/dia</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
           <t>X</t>
@@ -5547,7 +5584,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Suco de toranja / grapefruit</t>
+          <t>Suco natural sem açúcar</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5557,22 +5594,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Evitar</t>
+          <t>Moderar</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>200 ml</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>evitar</t>
+          <t>3x/semana</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Interage com o Ticagrelor (estudo mostrou quase o dobro do nível do remédio no sangue); a bula diz que não é esperado ser clinicamente relevante p/ a maioria, mas orienta evitar — mais seguro evitar, já que você toma 2 antiagregantes. Ver aba Fontes e Referências.</t>
+          <t>Preferir a fruta inteira, que tem mais fibra</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -5601,7 +5638,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Bebida alcoólica</t>
+          <t>Suco de toranja / grapefruit</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5626,21 +5663,21 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Piora diretamente os triglicerídeos; soma-se ao risco de sangramento da Aspirina + Ticagrelor.</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+          <t>Interage com o Ticagrelor (estudo mostrou quase o dobro do nível do remédio no sangue); a bula diz que não é esperado ser clinicamente relevante p/ a maioria, mas orienta evitar — mais seguro evitar, já que você toma 2 antiagregantes. Ver aba Fontes e Referências.</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
       <c r="Q26" t="inlineStr">
         <is>
           <t>Gorduras e Temperos|Jantar</t>
@@ -5655,12 +5692,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Açúcar refinado</t>
+          <t>Bebida alcoólica</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Doces e Sobremesas</t>
+          <t>Bebidas</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -5680,24 +5717,16 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Impacto direto nos triglicerídeos</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+          <t>Piora diretamente os triglicerídeos; soma-se ao risco de sangramento da Aspirina + Ticagrelor.</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
           <t>X</t>
@@ -5717,7 +5746,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Doces industrializados</t>
+          <t>Açúcar refinado</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5740,20 +5769,36 @@
           <t>evitar</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Impacto direto nos triglicerídeos</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="I28" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Chocolate amargo (70%+)</t>
+          <t>Doces industrializados</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5763,24 +5808,20 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Moderar</t>
+          <t>Evitar</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>10 g</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2x/semana</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Sugestão gerada por IA — confirmar com nutricionista/cardiologista</t>
-        </is>
-      </c>
+          <t>evitar</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
@@ -5793,47 +5834,47 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Azeite de oliva extra virgem</t>
+          <t>Chocolate amargo (70%+)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Gorduras e Temperos</t>
+          <t>Doces e Sobremesas</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Liberado</t>
+          <t>Moderar</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1-2 colheres de sopa</t>
+          <t>10 g</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1x/dia</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr"/>
+          <t>2x/semana</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Sugestão gerada por IA — confirmar com nutricionista/cardiologista</t>
+        </is>
+      </c>
       <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Manteiga</t>
+          <t>Azeite de oliva extra virgem</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -5843,37 +5884,37 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Evitar</t>
+          <t>Liberado</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1-2 colheres de sopa</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>evitar</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Preferir azeite</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
+          <t>1x/dia</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Sal</t>
+          <t>Manteiga</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -5883,41 +5924,37 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Moderar</t>
+          <t>Evitar</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>&lt; 5 g no total</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>todos os dias</t>
+          <t>evitar</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Somar sal de cozinha + industrializados</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+          <t>Preferir azeite</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="J32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Sal light / substituto de sal (cloreto de potássio)</t>
+          <t>Sal</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -5927,22 +5964,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Evitar</t>
+          <t>Moderar</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>&lt; 5 g no total</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>evitar</t>
+          <t>todos os dias</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Enalapril já tende a elevar o potássio; combinado com esse produto o risco de hipercalemia aumenta, ainda mais com a função renal pendente.</t>
+          <t>Somar sal de cozinha + industrializados</t>
         </is>
       </c>
       <c r="G33" t="inlineStr"/>
@@ -5961,7 +5998,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Ervas e temperos naturais</t>
+          <t>Sal light / substituto de sal (cloreto de potássio)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -5971,20 +6008,24 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Liberado</t>
+          <t>Evitar</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>à vontade</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>todos os dias</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr"/>
+          <t>evitar</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Enalapril já tende a elevar o potássio; combinado com esse produto o risco de hipercalemia aumenta, ainda mais com a função renal pendente.</t>
+        </is>
+      </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
@@ -6001,50 +6042,90 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>Ervas e temperos naturais</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Gorduras e Temperos</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Liberado</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>à vontade</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>todos os dias</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
           <t>Vegetais e verduras em geral</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>Vegetais e Verduras</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>Liberado</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>à vontade</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>todos os dias</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>Se entrar anticoagulante na medicação, revisar consumo de verde-escuros ricos em vitamina K</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
         <is>
           <t>X</t>
         </is>

--- a/planilha/plano-alimentar-pos-infarto.xlsx
+++ b/planilha/plano-alimentar-pos-infarto.xlsx
@@ -983,7 +983,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>1/2 do prato: vegetais e salada (à vontade, tempero simples com azeite/limão). 1/4 do prato: proteína magra grelhada/assada (peixe, frango sem pele, ovo, leguminosas). 1/4 do prato: carboidrato integral (arroz integral, batata-doce, mandioca, pão integral) em porção moderada.</t>
+          <t>1/2 do prato: vegetais e salada (à vontade, tempero simples com azeite/limão). 1/4 do prato: proteína magra grelhada/assada (peixe, frango sem pele, ovo, leguminosas). 1/4 do prato: carboidrato integral (arroz integral, batata-doce, mandioca, pão de forma integral) em porção moderada.</t>
         </is>
       </c>
     </row>
@@ -1386,7 +1386,7 @@
     <row r="15" ht="30" customHeight="1">
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>Pão integral</t>
+          <t>Pão de forma integral</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
@@ -1579,7 +1579,7 @@
     <row r="24" ht="30" customHeight="1">
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>Queijo branco</t>
+          <t>Queijo branco frescal</t>
         </is>
       </c>
       <c r="C24" s="12" t="inlineStr">
@@ -1592,14 +1592,14 @@
           <t>3x/semana</t>
         </is>
       </c>
-      <c r="E24" s="14" t="inlineStr">
-        <is>
-          <t>Moderar</t>
+      <c r="E24" s="13" t="inlineStr">
+        <is>
+          <t>Liberado</t>
         </is>
       </c>
       <c r="F24" s="11" t="inlineStr">
         <is>
-          <t>Atenção ao sódio</t>
+          <t>Tipo fresco (ex.: Minas frescal), sem cura/salga pesada — bem menos sódio e gordura que queijos curados. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
         </is>
       </c>
     </row>
@@ -1626,7 +1626,7 @@
       </c>
       <c r="F25" s="11" t="inlineStr">
         <is>
-          <t>Mais gordura saturada e sódio que o queijo branco; prefira o queijo branco no dia a dia. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
+          <t>Mais gordura saturada e sódio que o queijo branco frescal; prefira o frescal no dia a dia. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
         </is>
       </c>
     </row>
@@ -4216,7 +4216,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Pão integral</t>
+          <t>Pão de forma integral</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -4290,7 +4290,7 @@
       <c r="J6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Pão integral</t>
+          <t>Pão de forma integral</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -4384,7 +4384,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Iogurte natural (desnatado, sem açúcar)</t>
+          <t>Queijo branco frescal</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -4464,7 +4464,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Água</t>
+          <t>Iogurte natural (desnatado, sem açúcar)</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -4538,7 +4538,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Iogurte natural (desnatado, sem açúcar)</t>
+          <t>Queijo branco frescal</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -4548,7 +4548,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Café sem açúcar</t>
+          <t>Água</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -4618,7 +4618,7 @@
       <c r="J10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Água</t>
+          <t>Iogurte natural (desnatado, sem açúcar)</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4628,7 +4628,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Vegetais e verduras em geral</t>
+          <t>Café sem açúcar</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -4650,7 +4650,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Pão integral</t>
+          <t>Pão de forma integral</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4688,7 +4688,7 @@
       <c r="J11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Café sem açúcar</t>
+          <t>Água</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4698,7 +4698,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Uva</t>
+          <t>Vegetais e verduras em geral</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -4762,7 +4762,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Vegetais e verduras em geral</t>
+          <t>Café sem açúcar</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Manga</t>
+          <t>Uva</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -4832,7 +4832,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Uva</t>
+          <t>Vegetais e verduras em geral</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -4842,7 +4842,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Queijo branco</t>
+          <t>Manga</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Manga</t>
+          <t>Uva</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -4980,7 +4980,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Queijo branco</t>
+          <t>Manga</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -5145,14 +5145,14 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>Pão integral</t>
+          <t>Pão de forma integral</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Queijo branco</t>
+          <t>Queijo branco frescal</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -5162,7 +5162,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Moderar</t>
+          <t>Liberado</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -5177,7 +5177,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Atenção ao sódio</t>
+          <t>Tipo fresco (ex.: Minas frescal), sem cura/salga pesada — bem menos sódio e gordura que queijos curados. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -5241,7 +5241,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mais gordura saturada e sódio que o queijo branco; prefira o queijo branco no dia a dia. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
+          <t>Mais gordura saturada e sódio que o queijo branco frescal; prefira o frescal no dia a dia. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">

--- a/planilha/plano-alimentar-pos-infarto.xlsx
+++ b/planilha/plano-alimentar-pos-infarto.xlsx
@@ -63,6 +63,11 @@
     </font>
     <font>
       <name val="Arial"/>
+      <i val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="10.5"/>
@@ -101,11 +106,6 @@
       <i val="1"/>
       <color rgb="001F4E5F"/>
       <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <i val="1"/>
-      <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -213,7 +213,10 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -232,28 +235,28 @@
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -262,23 +265,20 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1061,15 +1061,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F48"/>
+  <dimension ref="A1:H49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="46" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -1095,6 +1097,11 @@
           <t>Evitar</t>
         </is>
       </c>
+      <c r="G2" s="9" t="inlineStr">
+        <is>
+          <t>Gostoso: preencha você mesmo (menu suspenso na coluna)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1109,1034 +1116,1169 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
           <t>Porção</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Frequência</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>Classificação</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Gostoso</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Observação</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>Frutas</t>
         </is>
       </c>
-      <c r="B4" s="10" t="n"/>
-      <c r="C4" s="10" t="n"/>
-      <c r="D4" s="10" t="n"/>
-      <c r="E4" s="10" t="n"/>
-      <c r="F4" s="10" t="n"/>
+      <c r="B4" s="11" t="n"/>
+      <c r="C4" s="11" t="n"/>
+      <c r="D4" s="11" t="n"/>
+      <c r="E4" s="11" t="n"/>
+      <c r="F4" s="11" t="n"/>
+      <c r="G4" s="11" t="n"/>
+      <c r="H4" s="11" t="n"/>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="12" t="inlineStr">
         <is>
           <t>Maçã com casca</t>
         </is>
       </c>
-      <c r="C5" s="12" t="inlineStr">
+      <c r="C5" s="13" t="inlineStr"/>
+      <c r="D5" s="13" t="inlineStr">
         <is>
           <t>1 unidade</t>
         </is>
       </c>
-      <c r="D5" s="12" t="inlineStr">
+      <c r="E5" s="13" t="inlineStr">
         <is>
           <t>1x/dia</t>
         </is>
       </c>
-      <c r="E5" s="13" t="inlineStr">
+      <c r="F5" s="14" t="inlineStr">
         <is>
           <t>Liberado</t>
         </is>
       </c>
-      <c r="F5" s="11" t="inlineStr"/>
+      <c r="G5" s="13" t="inlineStr"/>
+      <c r="H5" s="12" t="inlineStr"/>
     </row>
     <row r="6" ht="30" customHeight="1">
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>Banana</t>
         </is>
       </c>
-      <c r="C6" s="12" t="inlineStr">
+      <c r="C6" s="13" t="inlineStr"/>
+      <c r="D6" s="13" t="inlineStr">
         <is>
           <t>1 unidade</t>
         </is>
       </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="E6" s="13" t="inlineStr">
         <is>
           <t>1x/dia</t>
         </is>
       </c>
-      <c r="E6" s="13" t="inlineStr">
+      <c r="F6" s="14" t="inlineStr">
         <is>
           <t>Liberado</t>
         </is>
       </c>
-      <c r="F6" s="11" t="inlineStr"/>
+      <c r="G6" s="13" t="inlineStr"/>
+      <c r="H6" s="12" t="inlineStr"/>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="12" t="inlineStr">
         <is>
           <t>Uva</t>
         </is>
       </c>
-      <c r="C7" s="12" t="inlineStr">
+      <c r="C7" s="13" t="inlineStr"/>
+      <c r="D7" s="13" t="inlineStr">
         <is>
           <t>200 g</t>
         </is>
       </c>
-      <c r="D7" s="12" t="inlineStr">
+      <c r="E7" s="13" t="inlineStr">
         <is>
           <t>1x/semana</t>
         </is>
       </c>
-      <c r="E7" s="14" t="inlineStr">
+      <c r="F7" s="15" t="inlineStr">
         <is>
           <t>Moderar</t>
         </is>
       </c>
-      <c r="F7" s="11" t="inlineStr">
+      <c r="G7" s="13" t="inlineStr"/>
+      <c r="H7" s="12" t="inlineStr">
         <is>
           <t>Mais açúcar que outras frutas</t>
         </is>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
-      <c r="B8" s="11" t="inlineStr">
+      <c r="B8" s="12" t="inlineStr">
         <is>
           <t>Manga</t>
         </is>
       </c>
-      <c r="C8" s="12" t="inlineStr">
+      <c r="C8" s="13" t="inlineStr"/>
+      <c r="D8" s="13" t="inlineStr">
         <is>
           <t>200 g</t>
         </is>
       </c>
-      <c r="D8" s="12" t="inlineStr">
+      <c r="E8" s="13" t="inlineStr">
         <is>
           <t>1x/semana</t>
         </is>
       </c>
-      <c r="E8" s="14" t="inlineStr">
+      <c r="F8" s="15" t="inlineStr">
         <is>
           <t>Moderar</t>
         </is>
       </c>
-      <c r="F8" s="11" t="inlineStr">
+      <c r="G8" s="13" t="inlineStr"/>
+      <c r="H8" s="12" t="inlineStr">
         <is>
           <t>Mais açúcar que outras frutas</t>
         </is>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
-      <c r="B9" s="11" t="inlineStr">
+      <c r="B9" s="12" t="inlineStr">
         <is>
           <t>Abacate</t>
         </is>
       </c>
-      <c r="C9" s="12" t="inlineStr">
+      <c r="C9" s="13" t="inlineStr"/>
+      <c r="D9" s="13" t="inlineStr">
         <is>
           <t>2 colheres de sopa</t>
         </is>
       </c>
-      <c r="D9" s="12" t="inlineStr">
+      <c r="E9" s="13" t="inlineStr">
         <is>
           <t>1x/dia</t>
         </is>
       </c>
-      <c r="E9" s="13" t="inlineStr">
+      <c r="F9" s="14" t="inlineStr">
         <is>
           <t>Liberado</t>
         </is>
       </c>
-      <c r="F9" s="11" t="inlineStr">
+      <c r="G9" s="13" t="inlineStr"/>
+      <c r="H9" s="12" t="inlineStr">
         <is>
           <t>Gordura boa, mas calórico</t>
         </is>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
-      <c r="B10" s="11" t="inlineStr">
+      <c r="B10" s="12" t="inlineStr">
         <is>
           <t>Toranja / grapefruit</t>
         </is>
       </c>
-      <c r="C10" s="12" t="inlineStr">
+      <c r="C10" s="13" t="inlineStr"/>
+      <c r="D10" s="13" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D10" s="12" t="inlineStr">
+      <c r="E10" s="13" t="inlineStr">
         <is>
           <t>evitar</t>
         </is>
       </c>
-      <c r="E10" s="15" t="inlineStr">
+      <c r="F10" s="16" t="inlineStr">
         <is>
           <t>Evitar</t>
         </is>
       </c>
-      <c r="F10" s="11" t="inlineStr">
+      <c r="G10" s="13" t="inlineStr"/>
+      <c r="H10" s="12" t="inlineStr">
         <is>
           <t>Interage com o Ticagrelor (estudo mostrou quase o dobro do nível do remédio no sangue); a bula diz que não é esperado ser clinicamente relevante p/ a maioria, mas orienta evitar — mais seguro evitar, já que você toma 2 antiagregantes. Ver aba Fontes e Referências.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="9" t="inlineStr">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>Grãos e Cereais</t>
         </is>
       </c>
-      <c r="B11" s="10" t="n"/>
-      <c r="C11" s="10" t="n"/>
-      <c r="D11" s="10" t="n"/>
-      <c r="E11" s="10" t="n"/>
-      <c r="F11" s="10" t="n"/>
+      <c r="B11" s="11" t="n"/>
+      <c r="C11" s="11" t="n"/>
+      <c r="D11" s="11" t="n"/>
+      <c r="E11" s="11" t="n"/>
+      <c r="F11" s="11" t="n"/>
+      <c r="G11" s="11" t="n"/>
+      <c r="H11" s="11" t="n"/>
     </row>
     <row r="12" ht="30" customHeight="1">
-      <c r="B12" s="11" t="inlineStr">
+      <c r="B12" s="12" t="inlineStr">
         <is>
           <t>Arroz integral</t>
         </is>
       </c>
-      <c r="C12" s="12" t="inlineStr">
+      <c r="C12" s="13" t="inlineStr"/>
+      <c r="D12" s="13" t="inlineStr">
         <is>
           <t>200 g (cozido)</t>
         </is>
       </c>
-      <c r="D12" s="12" t="inlineStr">
+      <c r="E12" s="13" t="inlineStr">
         <is>
           <t>quase todo dia</t>
         </is>
       </c>
-      <c r="E12" s="13" t="inlineStr">
+      <c r="F12" s="14" t="inlineStr">
         <is>
           <t>Liberado</t>
         </is>
       </c>
-      <c r="F12" s="11" t="inlineStr"/>
+      <c r="G12" s="13" t="inlineStr"/>
+      <c r="H12" s="12" t="inlineStr"/>
     </row>
     <row r="13" ht="30" customHeight="1">
-      <c r="B13" s="11" t="inlineStr">
+      <c r="B13" s="12" t="inlineStr">
         <is>
           <t>Arroz branco</t>
         </is>
       </c>
-      <c r="C13" s="12" t="inlineStr">
+      <c r="C13" s="13" t="inlineStr"/>
+      <c r="D13" s="13" t="inlineStr">
         <is>
           <t>200 g (cozido)</t>
         </is>
       </c>
-      <c r="D13" s="12" t="inlineStr">
+      <c r="E13" s="13" t="inlineStr">
         <is>
           <t>2x/semana</t>
         </is>
       </c>
-      <c r="E13" s="14" t="inlineStr">
+      <c r="F13" s="15" t="inlineStr">
         <is>
           <t>Moderar</t>
         </is>
       </c>
-      <c r="F13" s="11" t="inlineStr">
+      <c r="G13" s="13" t="inlineStr"/>
+      <c r="H13" s="12" t="inlineStr">
         <is>
           <t>Preferir integral no restante da semana</t>
         </is>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1">
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B14" s="12" t="inlineStr">
         <is>
           <t>Aveia</t>
         </is>
       </c>
-      <c r="C14" s="12" t="inlineStr">
+      <c r="C14" s="13" t="inlineStr"/>
+      <c r="D14" s="13" t="inlineStr">
         <is>
           <t>2 colheres de sopa</t>
         </is>
       </c>
-      <c r="D14" s="12" t="inlineStr">
+      <c r="E14" s="13" t="inlineStr">
         <is>
           <t>1x/dia</t>
         </is>
       </c>
-      <c r="E14" s="13" t="inlineStr">
+      <c r="F14" s="14" t="inlineStr">
         <is>
           <t>Liberado</t>
         </is>
       </c>
-      <c r="F14" s="11" t="inlineStr">
+      <c r="G14" s="13" t="inlineStr"/>
+      <c r="H14" s="12" t="inlineStr">
         <is>
           <t>Ajuda a reduzir colesterol</t>
         </is>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1">
-      <c r="B15" s="11" t="inlineStr">
+      <c r="B15" s="12" t="inlineStr">
         <is>
           <t>Pão de forma integral</t>
         </is>
       </c>
-      <c r="C15" s="12" t="inlineStr">
+      <c r="C15" s="13" t="inlineStr"/>
+      <c r="D15" s="13" t="inlineStr">
         <is>
           <t>2 fatias</t>
         </is>
       </c>
-      <c r="D15" s="12" t="inlineStr">
+      <c r="E15" s="13" t="inlineStr">
         <is>
           <t>1x/dia</t>
         </is>
       </c>
-      <c r="E15" s="13" t="inlineStr">
+      <c r="F15" s="14" t="inlineStr">
         <is>
           <t>Liberado</t>
         </is>
       </c>
-      <c r="F15" s="11" t="inlineStr"/>
+      <c r="G15" s="13" t="inlineStr"/>
+      <c r="H15" s="12" t="inlineStr"/>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="9" t="inlineStr">
+      <c r="A16" s="10" t="inlineStr">
         <is>
           <t>Proteínas</t>
         </is>
       </c>
-      <c r="B16" s="10" t="n"/>
-      <c r="C16" s="10" t="n"/>
-      <c r="D16" s="10" t="n"/>
-      <c r="E16" s="10" t="n"/>
-      <c r="F16" s="10" t="n"/>
+      <c r="B16" s="11" t="n"/>
+      <c r="C16" s="11" t="n"/>
+      <c r="D16" s="11" t="n"/>
+      <c r="E16" s="11" t="n"/>
+      <c r="F16" s="11" t="n"/>
+      <c r="G16" s="11" t="n"/>
+      <c r="H16" s="11" t="n"/>
     </row>
     <row r="17" ht="30" customHeight="1">
-      <c r="B17" s="11" t="inlineStr">
+      <c r="B17" s="12" t="inlineStr">
         <is>
           <t>Peixe</t>
         </is>
       </c>
-      <c r="C17" s="12" t="inlineStr">
+      <c r="C17" s="13" t="inlineStr"/>
+      <c r="D17" s="13" t="inlineStr">
         <is>
           <t>150 g</t>
         </is>
       </c>
-      <c r="D17" s="12" t="inlineStr">
+      <c r="E17" s="13" t="inlineStr">
         <is>
           <t>3x/semana</t>
         </is>
       </c>
-      <c r="E17" s="13" t="inlineStr">
+      <c r="F17" s="14" t="inlineStr">
         <is>
           <t>Liberado</t>
         </is>
       </c>
-      <c r="F17" s="11" t="inlineStr">
+      <c r="G17" s="13" t="inlineStr"/>
+      <c r="H17" s="12" t="inlineStr">
         <is>
           <t>Fonte de ômega-3</t>
         </is>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1">
-      <c r="B18" s="11" t="inlineStr">
+      <c r="B18" s="12" t="inlineStr">
         <is>
           <t>Frango sem pele</t>
         </is>
       </c>
-      <c r="C18" s="12" t="inlineStr">
+      <c r="C18" s="13" t="inlineStr"/>
+      <c r="D18" s="13" t="inlineStr">
         <is>
           <t>150 g</t>
         </is>
       </c>
-      <c r="D18" s="12" t="inlineStr">
+      <c r="E18" s="13" t="inlineStr">
         <is>
           <t>quase todo dia</t>
         </is>
       </c>
-      <c r="E18" s="13" t="inlineStr">
+      <c r="F18" s="14" t="inlineStr">
         <is>
           <t>Liberado</t>
         </is>
       </c>
-      <c r="F18" s="11" t="inlineStr"/>
+      <c r="G18" s="13" t="inlineStr"/>
+      <c r="H18" s="12" t="inlineStr"/>
     </row>
     <row r="19" ht="30" customHeight="1">
-      <c r="B19" s="11" t="inlineStr">
+      <c r="B19" s="12" t="inlineStr">
         <is>
           <t>Carne vermelha magra</t>
         </is>
       </c>
-      <c r="C19" s="12" t="inlineStr">
+      <c r="C19" s="13" t="inlineStr"/>
+      <c r="D19" s="13" t="inlineStr">
         <is>
           <t>150 g</t>
         </is>
       </c>
-      <c r="D19" s="12" t="inlineStr">
+      <c r="E19" s="13" t="inlineStr">
         <is>
           <t>1x/semana</t>
         </is>
       </c>
-      <c r="E19" s="14" t="inlineStr">
+      <c r="F19" s="15" t="inlineStr">
         <is>
           <t>Moderar</t>
         </is>
       </c>
-      <c r="F19" s="11" t="inlineStr">
+      <c r="G19" s="13" t="inlineStr"/>
+      <c r="H19" s="12" t="inlineStr">
         <is>
           <t>Preferir cortes magros</t>
         </is>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1">
-      <c r="B20" s="11" t="inlineStr">
+      <c r="B20" s="12" t="inlineStr">
         <is>
           <t>Ovo</t>
         </is>
       </c>
-      <c r="C20" s="12" t="inlineStr">
+      <c r="C20" s="13" t="inlineStr"/>
+      <c r="D20" s="13" t="inlineStr">
         <is>
           <t>1 unidade</t>
         </is>
       </c>
-      <c r="D20" s="12" t="inlineStr">
+      <c r="E20" s="13" t="inlineStr">
         <is>
           <t>até 5x/semana</t>
         </is>
       </c>
-      <c r="E20" s="13" t="inlineStr">
+      <c r="F20" s="14" t="inlineStr">
         <is>
           <t>Liberado</t>
         </is>
       </c>
-      <c r="F20" s="11" t="inlineStr"/>
+      <c r="G20" s="13" t="inlineStr"/>
+      <c r="H20" s="12" t="inlineStr"/>
     </row>
     <row r="21" ht="30" customHeight="1">
-      <c r="B21" s="11" t="inlineStr">
+      <c r="B21" s="12" t="inlineStr">
         <is>
           <t>Feijão / leguminosas</t>
         </is>
       </c>
-      <c r="C21" s="12" t="inlineStr">
+      <c r="C21" s="13" t="inlineStr"/>
+      <c r="D21" s="13" t="inlineStr">
         <is>
           <t>1 concha</t>
         </is>
       </c>
-      <c r="D21" s="12" t="inlineStr">
+      <c r="E21" s="13" t="inlineStr">
         <is>
           <t>1x/dia</t>
         </is>
       </c>
-      <c r="E21" s="13" t="inlineStr">
+      <c r="F21" s="14" t="inlineStr">
         <is>
           <t>Liberado</t>
         </is>
       </c>
-      <c r="F21" s="11" t="inlineStr"/>
+      <c r="G21" s="13" t="inlineStr"/>
+      <c r="H21" s="12" t="inlineStr"/>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="9" t="inlineStr">
+      <c r="A22" s="10" t="inlineStr">
         <is>
           <t>Laticínios</t>
         </is>
       </c>
-      <c r="B22" s="10" t="n"/>
-      <c r="C22" s="10" t="n"/>
-      <c r="D22" s="10" t="n"/>
-      <c r="E22" s="10" t="n"/>
-      <c r="F22" s="10" t="n"/>
+      <c r="B22" s="11" t="n"/>
+      <c r="C22" s="11" t="n"/>
+      <c r="D22" s="11" t="n"/>
+      <c r="E22" s="11" t="n"/>
+      <c r="F22" s="11" t="n"/>
+      <c r="G22" s="11" t="n"/>
+      <c r="H22" s="11" t="n"/>
     </row>
     <row r="23" ht="30" customHeight="1">
-      <c r="B23" s="11" t="inlineStr">
+      <c r="B23" s="12" t="inlineStr">
         <is>
           <t>Leite desnatado</t>
         </is>
       </c>
-      <c r="C23" s="12" t="inlineStr">
+      <c r="C23" s="13" t="inlineStr"/>
+      <c r="D23" s="13" t="inlineStr">
         <is>
           <t>200 ml</t>
         </is>
       </c>
-      <c r="D23" s="12" t="inlineStr">
+      <c r="E23" s="13" t="inlineStr">
         <is>
           <t>1x/dia</t>
         </is>
       </c>
-      <c r="E23" s="13" t="inlineStr">
+      <c r="F23" s="14" t="inlineStr">
         <is>
           <t>Liberado</t>
         </is>
       </c>
-      <c r="F23" s="11" t="inlineStr"/>
+      <c r="G23" s="13" t="inlineStr"/>
+      <c r="H23" s="12" t="inlineStr"/>
     </row>
     <row r="24" ht="30" customHeight="1">
-      <c r="B24" s="11" t="inlineStr">
+      <c r="B24" s="12" t="inlineStr">
         <is>
           <t>Queijo branco frescal</t>
         </is>
       </c>
-      <c r="C24" s="12" t="inlineStr">
+      <c r="C24" s="13" t="inlineStr"/>
+      <c r="D24" s="13" t="inlineStr">
         <is>
           <t>30 g</t>
         </is>
       </c>
-      <c r="D24" s="12" t="inlineStr">
+      <c r="E24" s="13" t="inlineStr">
         <is>
           <t>3x/semana</t>
         </is>
       </c>
-      <c r="E24" s="13" t="inlineStr">
+      <c r="F24" s="14" t="inlineStr">
         <is>
           <t>Liberado</t>
         </is>
       </c>
-      <c r="F24" s="11" t="inlineStr">
+      <c r="G24" s="13" t="inlineStr"/>
+      <c r="H24" s="12" t="inlineStr">
         <is>
           <t>Tipo fresco (ex.: Minas frescal), sem cura/salga pesada — bem menos sódio e gordura que queijos curados. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="30" customHeight="1">
-      <c r="B25" s="11" t="inlineStr">
+      <c r="B25" s="12" t="inlineStr">
+        <is>
+          <t>Queijo frescal light</t>
+        </is>
+      </c>
+      <c r="C25" s="13" t="inlineStr">
+        <is>
+          <t>Polenghi</t>
+        </is>
+      </c>
+      <c r="D25" s="13" t="inlineStr">
+        <is>
+          <t>30 g (1 fatia)</t>
+        </is>
+      </c>
+      <c r="E25" s="13" t="inlineStr">
+        <is>
+          <t>3x/semana</t>
+        </is>
+      </c>
+      <c r="F25" s="14" t="inlineStr">
+        <is>
+          <t>Liberado</t>
+        </is>
+      </c>
+      <c r="G25" s="13" t="inlineStr"/>
+      <c r="H25" s="12" t="inlineStr">
+        <is>
+          <t>Rótulo real: 41 kcal e 105 mg de sódio por porção (bem abaixo de queijos comuns), 1,5 g de gordura saturada, sem açúcar adicionado. Contém lactose; sem glúten; pode conter soja.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="B26" s="12" t="inlineStr">
         <is>
           <t>Mussarela</t>
         </is>
       </c>
-      <c r="C25" s="12" t="inlineStr">
+      <c r="C26" s="13" t="inlineStr"/>
+      <c r="D26" s="13" t="inlineStr">
         <is>
           <t>30 g</t>
         </is>
       </c>
-      <c r="D25" s="12" t="inlineStr">
+      <c r="E26" s="13" t="inlineStr">
         <is>
           <t>2x/semana</t>
         </is>
       </c>
-      <c r="E25" s="14" t="inlineStr">
+      <c r="F26" s="15" t="inlineStr">
         <is>
           <t>Moderar</t>
         </is>
       </c>
-      <c r="F25" s="11" t="inlineStr">
+      <c r="G26" s="13" t="inlineStr"/>
+      <c r="H26" s="12" t="inlineStr">
         <is>
           <t>Mais gordura saturada e sódio que o queijo branco frescal; prefira o frescal no dia a dia. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="30" customHeight="1">
-      <c r="B26" s="11" t="inlineStr">
+    <row r="27" ht="30" customHeight="1">
+      <c r="B27" s="12" t="inlineStr">
         <is>
           <t>Iogurte natural (desnatado, sem açúcar)</t>
         </is>
       </c>
-      <c r="C26" s="12" t="inlineStr">
+      <c r="C27" s="13" t="inlineStr"/>
+      <c r="D27" s="13" t="inlineStr">
         <is>
           <t>1 unidade</t>
         </is>
       </c>
-      <c r="D26" s="12" t="inlineStr">
+      <c r="E27" s="13" t="inlineStr">
         <is>
           <t>1x/dia</t>
         </is>
       </c>
-      <c r="E26" s="13" t="inlineStr">
+      <c r="F27" s="14" t="inlineStr">
         <is>
           <t>Liberado</t>
         </is>
       </c>
-      <c r="F26" s="11" t="inlineStr">
+      <c r="G27" s="13" t="inlineStr"/>
+      <c r="H27" s="12" t="inlineStr">
         <is>
           <t>Prefira sempre a versão sem açúcar adicionado</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="30" customHeight="1">
-      <c r="B27" s="11" t="inlineStr">
+    <row r="28" ht="30" customHeight="1">
+      <c r="B28" s="12" t="inlineStr">
         <is>
           <t>Requeijão</t>
         </is>
       </c>
-      <c r="C27" s="12" t="inlineStr">
+      <c r="C28" s="13" t="inlineStr"/>
+      <c r="D28" s="13" t="inlineStr">
         <is>
           <t>1 colher de sopa (≈15 g)</t>
         </is>
       </c>
-      <c r="D27" s="12" t="inlineStr">
+      <c r="E28" s="13" t="inlineStr">
         <is>
           <t>2x/semana</t>
         </is>
       </c>
-      <c r="E27" s="14" t="inlineStr">
+      <c r="F28" s="15" t="inlineStr">
         <is>
           <t>Moderar</t>
         </is>
       </c>
-      <c r="F27" s="11" t="inlineStr">
+      <c r="G28" s="13" t="inlineStr"/>
+      <c r="H28" s="12" t="inlineStr">
         <is>
           <t>Rico em gordura saturada e sódio; prefira a versão light. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="9" t="inlineStr">
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="10" t="inlineStr">
         <is>
           <t>Bebidas</t>
         </is>
       </c>
-      <c r="B28" s="10" t="n"/>
-      <c r="C28" s="10" t="n"/>
-      <c r="D28" s="10" t="n"/>
-      <c r="E28" s="10" t="n"/>
-      <c r="F28" s="10" t="n"/>
-    </row>
-    <row r="29" ht="30" customHeight="1">
-      <c r="B29" s="11" t="inlineStr">
+      <c r="B29" s="11" t="n"/>
+      <c r="C29" s="11" t="n"/>
+      <c r="D29" s="11" t="n"/>
+      <c r="E29" s="11" t="n"/>
+      <c r="F29" s="11" t="n"/>
+      <c r="G29" s="11" t="n"/>
+      <c r="H29" s="11" t="n"/>
+    </row>
+    <row r="30" ht="30" customHeight="1">
+      <c r="B30" s="12" t="inlineStr">
         <is>
           <t>Água</t>
         </is>
       </c>
-      <c r="C29" s="12" t="inlineStr">
+      <c r="C30" s="13" t="inlineStr"/>
+      <c r="D30" s="13" t="inlineStr">
         <is>
           <t>à vontade</t>
         </is>
       </c>
-      <c r="D29" s="12" t="inlineStr">
+      <c r="E30" s="13" t="inlineStr">
         <is>
           <t>todos os dias</t>
         </is>
       </c>
-      <c r="E29" s="13" t="inlineStr">
+      <c r="F30" s="14" t="inlineStr">
         <is>
           <t>Liberado</t>
         </is>
       </c>
-      <c r="F29" s="11" t="inlineStr"/>
-    </row>
-    <row r="30" ht="30" customHeight="1">
-      <c r="B30" s="11" t="inlineStr">
+      <c r="G30" s="13" t="inlineStr"/>
+      <c r="H30" s="12" t="inlineStr"/>
+    </row>
+    <row r="31" ht="30" customHeight="1">
+      <c r="B31" s="12" t="inlineStr">
         <is>
           <t>Refrigerante zero</t>
         </is>
       </c>
-      <c r="C30" s="12" t="inlineStr">
+      <c r="C31" s="13" t="inlineStr"/>
+      <c r="D31" s="13" t="inlineStr">
         <is>
           <t>200 ml</t>
         </is>
       </c>
-      <c r="D30" s="12" t="inlineStr">
+      <c r="E31" s="13" t="inlineStr">
         <is>
           <t>1x/dia</t>
         </is>
       </c>
-      <c r="E30" s="14" t="inlineStr">
+      <c r="F31" s="15" t="inlineStr">
         <is>
           <t>Moderar</t>
         </is>
       </c>
-      <c r="F30" s="11" t="inlineStr">
+      <c r="G31" s="13" t="inlineStr"/>
+      <c r="H31" s="12" t="inlineStr">
         <is>
           <t>Sugestão gerada por IA — confirmar com nutricionista/cardiologista</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="30" customHeight="1">
-      <c r="B31" s="11" t="inlineStr">
+    <row r="32" ht="30" customHeight="1">
+      <c r="B32" s="12" t="inlineStr">
         <is>
           <t>Café sem açúcar</t>
         </is>
       </c>
-      <c r="C31" s="12" t="inlineStr">
+      <c r="C32" s="13" t="inlineStr"/>
+      <c r="D32" s="13" t="inlineStr">
         <is>
           <t>1 xícara</t>
         </is>
       </c>
-      <c r="D31" s="12" t="inlineStr">
+      <c r="E32" s="13" t="inlineStr">
         <is>
           <t>2x/dia</t>
         </is>
       </c>
-      <c r="E31" s="13" t="inlineStr">
+      <c r="F32" s="14" t="inlineStr">
         <is>
           <t>Liberado</t>
         </is>
       </c>
-      <c r="F31" s="11" t="inlineStr"/>
-    </row>
-    <row r="32" ht="30" customHeight="1">
-      <c r="B32" s="11" t="inlineStr">
+      <c r="G32" s="13" t="inlineStr"/>
+      <c r="H32" s="12" t="inlineStr"/>
+    </row>
+    <row r="33" ht="30" customHeight="1">
+      <c r="B33" s="12" t="inlineStr">
         <is>
           <t>Suco natural sem açúcar</t>
         </is>
       </c>
-      <c r="C32" s="12" t="inlineStr">
+      <c r="C33" s="13" t="inlineStr"/>
+      <c r="D33" s="13" t="inlineStr">
         <is>
           <t>200 ml</t>
         </is>
       </c>
-      <c r="D32" s="12" t="inlineStr">
+      <c r="E33" s="13" t="inlineStr">
         <is>
           <t>3x/semana</t>
         </is>
       </c>
-      <c r="E32" s="14" t="inlineStr">
+      <c r="F33" s="15" t="inlineStr">
         <is>
           <t>Moderar</t>
         </is>
       </c>
-      <c r="F32" s="11" t="inlineStr">
+      <c r="G33" s="13" t="inlineStr"/>
+      <c r="H33" s="12" t="inlineStr">
         <is>
           <t>Preferir a fruta inteira, que tem mais fibra</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="30" customHeight="1">
-      <c r="B33" s="11" t="inlineStr">
+    <row r="34" ht="30" customHeight="1">
+      <c r="B34" s="12" t="inlineStr">
         <is>
           <t>Suco de toranja / grapefruit</t>
         </is>
       </c>
-      <c r="C33" s="12" t="inlineStr">
+      <c r="C34" s="13" t="inlineStr"/>
+      <c r="D34" s="13" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D33" s="12" t="inlineStr">
+      <c r="E34" s="13" t="inlineStr">
         <is>
           <t>evitar</t>
         </is>
       </c>
-      <c r="E33" s="15" t="inlineStr">
+      <c r="F34" s="16" t="inlineStr">
         <is>
           <t>Evitar</t>
         </is>
       </c>
-      <c r="F33" s="11" t="inlineStr">
+      <c r="G34" s="13" t="inlineStr"/>
+      <c r="H34" s="12" t="inlineStr">
         <is>
           <t>Interage com o Ticagrelor (estudo mostrou quase o dobro do nível do remédio no sangue); a bula diz que não é esperado ser clinicamente relevante p/ a maioria, mas orienta evitar — mais seguro evitar, já que você toma 2 antiagregantes. Ver aba Fontes e Referências.</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="30" customHeight="1">
-      <c r="B34" s="11" t="inlineStr">
+    <row r="35" ht="30" customHeight="1">
+      <c r="B35" s="12" t="inlineStr">
         <is>
           <t>Bebida alcoólica</t>
         </is>
       </c>
-      <c r="C34" s="12" t="inlineStr">
+      <c r="C35" s="13" t="inlineStr"/>
+      <c r="D35" s="13" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D34" s="12" t="inlineStr">
+      <c r="E35" s="13" t="inlineStr">
         <is>
           <t>evitar</t>
         </is>
       </c>
-      <c r="E34" s="15" t="inlineStr">
+      <c r="F35" s="16" t="inlineStr">
         <is>
           <t>Evitar</t>
         </is>
       </c>
-      <c r="F34" s="11" t="inlineStr">
+      <c r="G35" s="13" t="inlineStr"/>
+      <c r="H35" s="12" t="inlineStr">
         <is>
           <t>Piora diretamente os triglicerídeos; soma-se ao risco de sangramento da Aspirina + Ticagrelor.</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="9" t="inlineStr">
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="10" t="inlineStr">
         <is>
           <t>Doces e Sobremesas</t>
         </is>
       </c>
-      <c r="B35" s="10" t="n"/>
-      <c r="C35" s="10" t="n"/>
-      <c r="D35" s="10" t="n"/>
-      <c r="E35" s="10" t="n"/>
-      <c r="F35" s="10" t="n"/>
-    </row>
-    <row r="36" ht="30" customHeight="1">
-      <c r="B36" s="11" t="inlineStr">
+      <c r="B36" s="11" t="n"/>
+      <c r="C36" s="11" t="n"/>
+      <c r="D36" s="11" t="n"/>
+      <c r="E36" s="11" t="n"/>
+      <c r="F36" s="11" t="n"/>
+      <c r="G36" s="11" t="n"/>
+      <c r="H36" s="11" t="n"/>
+    </row>
+    <row r="37" ht="30" customHeight="1">
+      <c r="B37" s="12" t="inlineStr">
         <is>
           <t>Açúcar refinado</t>
         </is>
       </c>
-      <c r="C36" s="12" t="inlineStr">
+      <c r="C37" s="13" t="inlineStr"/>
+      <c r="D37" s="13" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D36" s="12" t="inlineStr">
+      <c r="E37" s="13" t="inlineStr">
         <is>
           <t>evitar</t>
         </is>
       </c>
-      <c r="E36" s="15" t="inlineStr">
+      <c r="F37" s="16" t="inlineStr">
         <is>
           <t>Evitar</t>
         </is>
       </c>
-      <c r="F36" s="11" t="inlineStr">
+      <c r="G37" s="13" t="inlineStr"/>
+      <c r="H37" s="12" t="inlineStr">
         <is>
           <t>Impacto direto nos triglicerídeos</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="30" customHeight="1">
-      <c r="B37" s="11" t="inlineStr">
+    <row r="38" ht="30" customHeight="1">
+      <c r="B38" s="12" t="inlineStr">
         <is>
           <t>Doces industrializados</t>
         </is>
       </c>
-      <c r="C37" s="12" t="inlineStr">
+      <c r="C38" s="13" t="inlineStr"/>
+      <c r="D38" s="13" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D37" s="12" t="inlineStr">
+      <c r="E38" s="13" t="inlineStr">
         <is>
           <t>evitar</t>
         </is>
       </c>
-      <c r="E37" s="15" t="inlineStr">
+      <c r="F38" s="16" t="inlineStr">
         <is>
           <t>Evitar</t>
         </is>
       </c>
-      <c r="F37" s="11" t="inlineStr"/>
-    </row>
-    <row r="38" ht="30" customHeight="1">
-      <c r="B38" s="11" t="inlineStr">
+      <c r="G38" s="13" t="inlineStr"/>
+      <c r="H38" s="12" t="inlineStr"/>
+    </row>
+    <row r="39" ht="30" customHeight="1">
+      <c r="B39" s="12" t="inlineStr">
         <is>
           <t>Chocolate amargo (70%+)</t>
         </is>
       </c>
-      <c r="C38" s="12" t="inlineStr">
+      <c r="C39" s="13" t="inlineStr"/>
+      <c r="D39" s="13" t="inlineStr">
         <is>
           <t>10 g</t>
         </is>
       </c>
-      <c r="D38" s="12" t="inlineStr">
+      <c r="E39" s="13" t="inlineStr">
         <is>
           <t>2x/semana</t>
         </is>
       </c>
-      <c r="E38" s="14" t="inlineStr">
+      <c r="F39" s="15" t="inlineStr">
         <is>
           <t>Moderar</t>
         </is>
       </c>
-      <c r="F38" s="11" t="inlineStr">
+      <c r="G39" s="13" t="inlineStr"/>
+      <c r="H39" s="12" t="inlineStr">
         <is>
           <t>Sugestão gerada por IA — confirmar com nutricionista/cardiologista</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="20" customHeight="1">
-      <c r="A39" s="9" t="inlineStr">
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="10" t="inlineStr">
         <is>
           <t>Gorduras e Temperos</t>
         </is>
       </c>
-      <c r="B39" s="10" t="n"/>
-      <c r="C39" s="10" t="n"/>
-      <c r="D39" s="10" t="n"/>
-      <c r="E39" s="10" t="n"/>
-      <c r="F39" s="10" t="n"/>
-    </row>
-    <row r="40" ht="30" customHeight="1">
-      <c r="B40" s="11" t="inlineStr">
+      <c r="B40" s="11" t="n"/>
+      <c r="C40" s="11" t="n"/>
+      <c r="D40" s="11" t="n"/>
+      <c r="E40" s="11" t="n"/>
+      <c r="F40" s="11" t="n"/>
+      <c r="G40" s="11" t="n"/>
+      <c r="H40" s="11" t="n"/>
+    </row>
+    <row r="41" ht="30" customHeight="1">
+      <c r="B41" s="12" t="inlineStr">
         <is>
           <t>Azeite de oliva extra virgem</t>
         </is>
       </c>
-      <c r="C40" s="12" t="inlineStr">
+      <c r="C41" s="13" t="inlineStr"/>
+      <c r="D41" s="13" t="inlineStr">
         <is>
           <t>1-2 colheres de sopa</t>
         </is>
       </c>
-      <c r="D40" s="12" t="inlineStr">
+      <c r="E41" s="13" t="inlineStr">
         <is>
           <t>1x/dia</t>
         </is>
       </c>
-      <c r="E40" s="13" t="inlineStr">
+      <c r="F41" s="14" t="inlineStr">
         <is>
           <t>Liberado</t>
         </is>
       </c>
-      <c r="F40" s="11" t="inlineStr"/>
-    </row>
-    <row r="41" ht="30" customHeight="1">
-      <c r="B41" s="11" t="inlineStr">
+      <c r="G41" s="13" t="inlineStr"/>
+      <c r="H41" s="12" t="inlineStr"/>
+    </row>
+    <row r="42" ht="30" customHeight="1">
+      <c r="B42" s="12" t="inlineStr">
         <is>
           <t>Manteiga</t>
         </is>
       </c>
-      <c r="C41" s="12" t="inlineStr">
+      <c r="C42" s="13" t="inlineStr"/>
+      <c r="D42" s="13" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D41" s="12" t="inlineStr">
+      <c r="E42" s="13" t="inlineStr">
         <is>
           <t>evitar</t>
         </is>
       </c>
-      <c r="E41" s="15" t="inlineStr">
+      <c r="F42" s="16" t="inlineStr">
         <is>
           <t>Evitar</t>
         </is>
       </c>
-      <c r="F41" s="11" t="inlineStr">
+      <c r="G42" s="13" t="inlineStr"/>
+      <c r="H42" s="12" t="inlineStr">
         <is>
           <t>Preferir azeite</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="30" customHeight="1">
-      <c r="B42" s="11" t="inlineStr">
+    <row r="43" ht="30" customHeight="1">
+      <c r="B43" s="12" t="inlineStr">
         <is>
           <t>Sal</t>
         </is>
       </c>
-      <c r="C42" s="12" t="inlineStr">
+      <c r="C43" s="13" t="inlineStr"/>
+      <c r="D43" s="13" t="inlineStr">
         <is>
           <t>&lt; 5 g no total</t>
         </is>
       </c>
-      <c r="D42" s="12" t="inlineStr">
+      <c r="E43" s="13" t="inlineStr">
         <is>
           <t>todos os dias</t>
         </is>
       </c>
-      <c r="E42" s="14" t="inlineStr">
+      <c r="F43" s="15" t="inlineStr">
         <is>
           <t>Moderar</t>
         </is>
       </c>
-      <c r="F42" s="11" t="inlineStr">
+      <c r="G43" s="13" t="inlineStr"/>
+      <c r="H43" s="12" t="inlineStr">
         <is>
           <t>Somar sal de cozinha + industrializados</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="30" customHeight="1">
-      <c r="B43" s="11" t="inlineStr">
+    <row r="44" ht="30" customHeight="1">
+      <c r="B44" s="12" t="inlineStr">
         <is>
           <t>Sal light / substituto de sal (cloreto de potássio)</t>
         </is>
       </c>
-      <c r="C43" s="12" t="inlineStr">
+      <c r="C44" s="13" t="inlineStr"/>
+      <c r="D44" s="13" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D43" s="12" t="inlineStr">
+      <c r="E44" s="13" t="inlineStr">
         <is>
           <t>evitar</t>
         </is>
       </c>
-      <c r="E43" s="15" t="inlineStr">
+      <c r="F44" s="16" t="inlineStr">
         <is>
           <t>Evitar</t>
         </is>
       </c>
-      <c r="F43" s="11" t="inlineStr">
+      <c r="G44" s="13" t="inlineStr"/>
+      <c r="H44" s="12" t="inlineStr">
         <is>
           <t>Enalapril já tende a elevar o potássio; combinado com esse produto o risco de hipercalemia aumenta, ainda mais com a função renal pendente.</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="30" customHeight="1">
-      <c r="B44" s="11" t="inlineStr">
+    <row r="45" ht="30" customHeight="1">
+      <c r="B45" s="12" t="inlineStr">
         <is>
           <t>Ervas e temperos naturais</t>
         </is>
       </c>
-      <c r="C44" s="12" t="inlineStr">
+      <c r="C45" s="13" t="inlineStr"/>
+      <c r="D45" s="13" t="inlineStr">
         <is>
           <t>à vontade</t>
         </is>
       </c>
-      <c r="D44" s="12" t="inlineStr">
+      <c r="E45" s="13" t="inlineStr">
         <is>
           <t>todos os dias</t>
         </is>
       </c>
-      <c r="E44" s="13" t="inlineStr">
+      <c r="F45" s="14" t="inlineStr">
         <is>
           <t>Liberado</t>
         </is>
       </c>
-      <c r="F44" s="11" t="inlineStr"/>
-    </row>
-    <row r="45" ht="20" customHeight="1">
-      <c r="A45" s="9" t="inlineStr">
+      <c r="G45" s="13" t="inlineStr"/>
+      <c r="H45" s="12" t="inlineStr"/>
+    </row>
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="10" t="inlineStr">
         <is>
           <t>Vegetais e Verduras</t>
         </is>
       </c>
-      <c r="B45" s="10" t="n"/>
-      <c r="C45" s="10" t="n"/>
-      <c r="D45" s="10" t="n"/>
-      <c r="E45" s="10" t="n"/>
-      <c r="F45" s="10" t="n"/>
-    </row>
-    <row r="46" ht="30" customHeight="1">
-      <c r="B46" s="11" t="inlineStr">
+      <c r="B46" s="11" t="n"/>
+      <c r="C46" s="11" t="n"/>
+      <c r="D46" s="11" t="n"/>
+      <c r="E46" s="11" t="n"/>
+      <c r="F46" s="11" t="n"/>
+      <c r="G46" s="11" t="n"/>
+      <c r="H46" s="11" t="n"/>
+    </row>
+    <row r="47" ht="30" customHeight="1">
+      <c r="B47" s="12" t="inlineStr">
         <is>
           <t>Vegetais e verduras em geral</t>
         </is>
       </c>
-      <c r="C46" s="12" t="inlineStr">
+      <c r="C47" s="13" t="inlineStr"/>
+      <c r="D47" s="13" t="inlineStr">
         <is>
           <t>à vontade</t>
         </is>
       </c>
-      <c r="D46" s="12" t="inlineStr">
+      <c r="E47" s="13" t="inlineStr">
         <is>
           <t>todos os dias</t>
         </is>
       </c>
-      <c r="E46" s="13" t="inlineStr">
+      <c r="F47" s="14" t="inlineStr">
         <is>
           <t>Liberado</t>
         </is>
       </c>
-      <c r="F46" s="11" t="inlineStr">
+      <c r="G47" s="13" t="inlineStr"/>
+      <c r="H47" s="12" t="inlineStr">
         <is>
           <t>Se entrar anticoagulante na medicação, revisar consumo de verde-escuros ricos em vitamina K</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="30" customHeight="1">
-      <c r="A48" s="16" t="inlineStr">
-        <is>
-          <t>Lista com os alimentos acrescentados até agora — não é uma lista completa. Use a skill 'adicionar-alimento' (ex.: "adicione sucrilhos") para ir acrescentando novos itens aos poucos.</t>
+    <row r="49" ht="40" customHeight="1">
+      <c r="A49" s="17" t="inlineStr">
+        <is>
+          <t>Lista com os alimentos acrescentados até agora — não é uma lista completa. Use a skill 'adicionar-alimento' (ex.: "adicione sucrilhos") para ir acrescentando novos itens aos poucos. A coluna 'Gostoso' é sua — escolha do menu suspenso; o valor é preservado mesmo quando a planilha é regenerada por um alimento novo.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A16:F16"/>
-    <mergeCell ref="A11:F11"/>
-    <mergeCell ref="A28:F28"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A45:F45"/>
-    <mergeCell ref="A22:F22"/>
-    <mergeCell ref="A35:F35"/>
-    <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A48:F48"/>
-    <mergeCell ref="A39:F39"/>
+  <mergeCells count="11">
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A29:H29"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="A16:H16"/>
+    <mergeCell ref="A36:H36"/>
+    <mergeCell ref="A11:H11"/>
+    <mergeCell ref="A49:H49"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A46:H46"/>
+    <mergeCell ref="A22:H22"/>
+    <mergeCell ref="A40:H40"/>
   </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="G5 G6 G7 G8 G9 G10 G12 G13 G14 G15 G17 G18 G19 G20 G21 G23 G24 G25 G26 G27 G28 G30 G31 G32 G33 G34 G35 G37 G38 G39 G41 G42 G43 G44 G45 G47" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Fora da lista" error="Escolha uma opção do menu (ou deixe em branco)." type="list" errorStyle="warning">
+      <formula1>"Ruim,Normal,Bom,Muito bom"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2168,793 +2310,793 @@
       </c>
     </row>
     <row r="2" ht="48" customHeight="1">
-      <c r="A2" s="16" t="inlineStr">
+      <c r="A2" s="17" t="inlineStr">
         <is>
           <t>Escolha o alimento no menu suspenso da coluna 'Alimento' — a lista já vem filtrada por refeição (por isso não aparece arroz/feijão no café da manhã, por exemplo) e com os alimentos Liberados primeiro. Categoria, Porção sugerida e Classificação preenchem sozinhas. 'Sugestão' mostra um alimento que costuma combinar bem com o item escolhido logo acima (é uma dica, não é obrigatório escolher). Se 'Conflito' mostrar '⚠ Conflito', evite reunir esses itens na mesma refeição.</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="17" t="inlineStr">
+      <c r="A3" s="18" t="inlineStr">
         <is>
           <t>Legenda:</t>
         </is>
       </c>
-      <c r="B3" s="18" t="inlineStr">
+      <c r="B3" s="19" t="inlineStr">
         <is>
           <t>Liberado</t>
         </is>
       </c>
-      <c r="C3" s="19" t="inlineStr">
+      <c r="C3" s="20" t="inlineStr">
         <is>
           <t>Moderar</t>
         </is>
       </c>
-      <c r="D3" s="20" t="inlineStr">
+      <c r="D3" s="21" t="inlineStr">
         <is>
           <t>Evitar</t>
         </is>
       </c>
-      <c r="F3" s="21" t="inlineStr">
+      <c r="F3" s="22" t="inlineStr">
         <is>
           <t>⚠ Conflito</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="22" t="inlineStr">
+      <c r="A5" s="23" t="inlineStr">
         <is>
           <t>CAFÉ DA MANHÃ</t>
         </is>
       </c>
-      <c r="B5" s="10" t="n"/>
-      <c r="C5" s="10" t="n"/>
-      <c r="D5" s="10" t="n"/>
-      <c r="E5" s="10" t="n"/>
-      <c r="F5" s="10" t="n"/>
-      <c r="G5" s="10" t="n"/>
-      <c r="H5" s="10" t="n"/>
+      <c r="B5" s="11" t="n"/>
+      <c r="C5" s="11" t="n"/>
+      <c r="D5" s="11" t="n"/>
+      <c r="E5" s="11" t="n"/>
+      <c r="F5" s="11" t="n"/>
+      <c r="G5" s="11" t="n"/>
+      <c r="H5" s="11" t="n"/>
     </row>
     <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="23" t="inlineStr">
+      <c r="A6" s="24" t="inlineStr">
         <is>
           <t>Nº</t>
         </is>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B6" s="24" t="inlineStr">
         <is>
           <t>Alimento</t>
         </is>
       </c>
-      <c r="C6" s="23" t="inlineStr">
+      <c r="C6" s="24" t="inlineStr">
         <is>
           <t>Categoria</t>
         </is>
       </c>
-      <c r="D6" s="23" t="inlineStr">
+      <c r="D6" s="24" t="inlineStr">
         <is>
           <t>Porção sugerida</t>
         </is>
       </c>
-      <c r="E6" s="23" t="inlineStr">
+      <c r="E6" s="24" t="inlineStr">
         <is>
           <t>Quantidade a comer</t>
         </is>
       </c>
-      <c r="F6" s="23" t="inlineStr">
+      <c r="F6" s="24" t="inlineStr">
         <is>
           <t>Classificação</t>
         </is>
       </c>
-      <c r="G6" s="23" t="inlineStr">
+      <c r="G6" s="24" t="inlineStr">
         <is>
           <t>Sugestão (com base no item anterior)</t>
         </is>
       </c>
-      <c r="H6" s="23" t="inlineStr">
+      <c r="H6" s="24" t="inlineStr">
         <is>
           <t>Conflito</t>
         </is>
       </c>
     </row>
     <row r="7" ht="26" customHeight="1">
-      <c r="A7" s="24" t="n">
+      <c r="A7" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="B7" s="25" t="n"/>
-      <c r="C7" s="26">
+      <c r="B7" s="26" t="n"/>
+      <c r="C7" s="27">
         <f>IFERROR(INDEX(Ref_Alimentos!$B$2:$B$101,MATCH($B7,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="D7" s="27">
+      <c r="D7" s="28">
         <f>IFERROR(INDEX(Ref_Alimentos!$D$2:$D$101,MATCH($B7,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="E7" s="24" t="n"/>
-      <c r="F7" s="28">
+      <c r="E7" s="25" t="n"/>
+      <c r="F7" s="29">
         <f>IFERROR(INDEX(Ref_Alimentos!$C$2:$C$101,MATCH($B7,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="G7" s="29" t="inlineStr"/>
-      <c r="H7" s="30">
+      <c r="G7" s="30" t="inlineStr"/>
+      <c r="H7" s="31">
         <f>IF($B7="","",IF($F7="Evitar","⚠ Conflito",IF(AND($F7="Moderar",SUMPRODUCT(($B$7:$B$11&lt;&gt;"")*(ROW($B$7:$B$11)&lt;&gt;ROW($B7))*(($F$7:$F$11="Moderar")+($F$7:$F$11="Evitar")))&gt;0),"⚠ Conflito","")))</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="24" t="n">
+      <c r="A8" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="B8" s="25" t="n"/>
-      <c r="C8" s="26">
+      <c r="B8" s="26" t="n"/>
+      <c r="C8" s="27">
         <f>IFERROR(INDEX(Ref_Alimentos!$B$2:$B$101,MATCH($B8,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="D8" s="27">
+      <c r="D8" s="28">
         <f>IFERROR(INDEX(Ref_Alimentos!$D$2:$D$101,MATCH($B8,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="E8" s="24" t="n"/>
-      <c r="F8" s="28">
+      <c r="E8" s="25" t="n"/>
+      <c r="F8" s="29">
         <f>IFERROR(INDEX(Ref_Alimentos!$C$2:$C$101,MATCH($B8,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="G8" s="29">
+      <c r="G8" s="30">
         <f>IF($B7="","",IFERROR(INDEX(Ref_Alimentos!$R$2:$R$60,MATCH(IFERROR(INDEX(Ref_Alimentos!$U$2:$U$9,MATCH($C7,Ref_Alimentos!$T$2:$T$9,0)),"")&amp;"|"&amp;"Café da manhã",Ref_Alimentos!$Q$2:$Q$60,0)),""))</f>
         <v/>
       </c>
-      <c r="H8" s="30">
+      <c r="H8" s="31">
         <f>IF($B8="","",IF($F8="Evitar","⚠ Conflito",IF(AND($F8="Moderar",SUMPRODUCT(($B$7:$B$11&lt;&gt;"")*(ROW($B$7:$B$11)&lt;&gt;ROW($B8))*(($F$7:$F$11="Moderar")+($F$7:$F$11="Evitar")))&gt;0),"⚠ Conflito","")))</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="26" customHeight="1">
-      <c r="A9" s="24" t="n">
+      <c r="A9" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="B9" s="25" t="n"/>
-      <c r="C9" s="26">
+      <c r="B9" s="26" t="n"/>
+      <c r="C9" s="27">
         <f>IFERROR(INDEX(Ref_Alimentos!$B$2:$B$101,MATCH($B9,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="D9" s="27">
+      <c r="D9" s="28">
         <f>IFERROR(INDEX(Ref_Alimentos!$D$2:$D$101,MATCH($B9,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="E9" s="24" t="n"/>
-      <c r="F9" s="28">
+      <c r="E9" s="25" t="n"/>
+      <c r="F9" s="29">
         <f>IFERROR(INDEX(Ref_Alimentos!$C$2:$C$101,MATCH($B9,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="G9" s="29">
+      <c r="G9" s="30">
         <f>IF($B8="","",IFERROR(INDEX(Ref_Alimentos!$R$2:$R$60,MATCH(IFERROR(INDEX(Ref_Alimentos!$U$2:$U$9,MATCH($C8,Ref_Alimentos!$T$2:$T$9,0)),"")&amp;"|"&amp;"Café da manhã",Ref_Alimentos!$Q$2:$Q$60,0)),""))</f>
         <v/>
       </c>
-      <c r="H9" s="30">
+      <c r="H9" s="31">
         <f>IF($B9="","",IF($F9="Evitar","⚠ Conflito",IF(AND($F9="Moderar",SUMPRODUCT(($B$7:$B$11&lt;&gt;"")*(ROW($B$7:$B$11)&lt;&gt;ROW($B9))*(($F$7:$F$11="Moderar")+($F$7:$F$11="Evitar")))&gt;0),"⚠ Conflito","")))</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="26" customHeight="1">
-      <c r="A10" s="24" t="n">
+      <c r="A10" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="B10" s="25" t="n"/>
-      <c r="C10" s="26">
+      <c r="B10" s="26" t="n"/>
+      <c r="C10" s="27">
         <f>IFERROR(INDEX(Ref_Alimentos!$B$2:$B$101,MATCH($B10,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="D10" s="27">
+      <c r="D10" s="28">
         <f>IFERROR(INDEX(Ref_Alimentos!$D$2:$D$101,MATCH($B10,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="E10" s="24" t="n"/>
-      <c r="F10" s="28">
+      <c r="E10" s="25" t="n"/>
+      <c r="F10" s="29">
         <f>IFERROR(INDEX(Ref_Alimentos!$C$2:$C$101,MATCH($B10,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="G10" s="29">
+      <c r="G10" s="30">
         <f>IF($B9="","",IFERROR(INDEX(Ref_Alimentos!$R$2:$R$60,MATCH(IFERROR(INDEX(Ref_Alimentos!$U$2:$U$9,MATCH($C9,Ref_Alimentos!$T$2:$T$9,0)),"")&amp;"|"&amp;"Café da manhã",Ref_Alimentos!$Q$2:$Q$60,0)),""))</f>
         <v/>
       </c>
-      <c r="H10" s="30">
+      <c r="H10" s="31">
         <f>IF($B10="","",IF($F10="Evitar","⚠ Conflito",IF(AND($F10="Moderar",SUMPRODUCT(($B$7:$B$11&lt;&gt;"")*(ROW($B$7:$B$11)&lt;&gt;ROW($B10))*(($F$7:$F$11="Moderar")+($F$7:$F$11="Evitar")))&gt;0),"⚠ Conflito","")))</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="26" customHeight="1">
-      <c r="A11" s="24" t="n">
+      <c r="A11" s="25" t="n">
         <v>5</v>
       </c>
-      <c r="B11" s="25" t="n"/>
-      <c r="C11" s="26">
+      <c r="B11" s="26" t="n"/>
+      <c r="C11" s="27">
         <f>IFERROR(INDEX(Ref_Alimentos!$B$2:$B$101,MATCH($B11,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="D11" s="27">
+      <c r="D11" s="28">
         <f>IFERROR(INDEX(Ref_Alimentos!$D$2:$D$101,MATCH($B11,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="E11" s="24" t="n"/>
-      <c r="F11" s="28">
+      <c r="E11" s="25" t="n"/>
+      <c r="F11" s="29">
         <f>IFERROR(INDEX(Ref_Alimentos!$C$2:$C$101,MATCH($B11,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="G11" s="29">
+      <c r="G11" s="30">
         <f>IF($B10="","",IFERROR(INDEX(Ref_Alimentos!$R$2:$R$60,MATCH(IFERROR(INDEX(Ref_Alimentos!$U$2:$U$9,MATCH($C10,Ref_Alimentos!$T$2:$T$9,0)),"")&amp;"|"&amp;"Café da manhã",Ref_Alimentos!$Q$2:$Q$60,0)),""))</f>
         <v/>
       </c>
-      <c r="H11" s="30">
+      <c r="H11" s="31">
         <f>IF($B11="","",IF($F11="Evitar","⚠ Conflito",IF(AND($F11="Moderar",SUMPRODUCT(($B$7:$B$11&lt;&gt;"")*(ROW($B$7:$B$11)&lt;&gt;ROW($B11))*(($F$7:$F$11="Moderar")+($F$7:$F$11="Evitar")))&gt;0),"⚠ Conflito","")))</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="22" t="inlineStr">
+      <c r="A13" s="23" t="inlineStr">
         <is>
           <t>ALMOÇO</t>
         </is>
       </c>
-      <c r="B13" s="10" t="n"/>
-      <c r="C13" s="10" t="n"/>
-      <c r="D13" s="10" t="n"/>
-      <c r="E13" s="10" t="n"/>
-      <c r="F13" s="10" t="n"/>
-      <c r="G13" s="10" t="n"/>
-      <c r="H13" s="10" t="n"/>
+      <c r="B13" s="11" t="n"/>
+      <c r="C13" s="11" t="n"/>
+      <c r="D13" s="11" t="n"/>
+      <c r="E13" s="11" t="n"/>
+      <c r="F13" s="11" t="n"/>
+      <c r="G13" s="11" t="n"/>
+      <c r="H13" s="11" t="n"/>
     </row>
     <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="23" t="inlineStr">
+      <c r="A14" s="24" t="inlineStr">
         <is>
           <t>Nº</t>
         </is>
       </c>
-      <c r="B14" s="23" t="inlineStr">
+      <c r="B14" s="24" t="inlineStr">
         <is>
           <t>Alimento</t>
         </is>
       </c>
-      <c r="C14" s="23" t="inlineStr">
+      <c r="C14" s="24" t="inlineStr">
         <is>
           <t>Categoria</t>
         </is>
       </c>
-      <c r="D14" s="23" t="inlineStr">
+      <c r="D14" s="24" t="inlineStr">
         <is>
           <t>Porção sugerida</t>
         </is>
       </c>
-      <c r="E14" s="23" t="inlineStr">
+      <c r="E14" s="24" t="inlineStr">
         <is>
           <t>Quantidade a comer</t>
         </is>
       </c>
-      <c r="F14" s="23" t="inlineStr">
+      <c r="F14" s="24" t="inlineStr">
         <is>
           <t>Classificação</t>
         </is>
       </c>
-      <c r="G14" s="23" t="inlineStr">
+      <c r="G14" s="24" t="inlineStr">
         <is>
           <t>Sugestão (com base no item anterior)</t>
         </is>
       </c>
-      <c r="H14" s="23" t="inlineStr">
+      <c r="H14" s="24" t="inlineStr">
         <is>
           <t>Conflito</t>
         </is>
       </c>
     </row>
     <row r="15" ht="26" customHeight="1">
-      <c r="A15" s="24" t="n">
+      <c r="A15" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="B15" s="25" t="n"/>
-      <c r="C15" s="26">
+      <c r="B15" s="26" t="n"/>
+      <c r="C15" s="27">
         <f>IFERROR(INDEX(Ref_Alimentos!$B$2:$B$101,MATCH($B15,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="D15" s="27">
+      <c r="D15" s="28">
         <f>IFERROR(INDEX(Ref_Alimentos!$D$2:$D$101,MATCH($B15,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="E15" s="24" t="n"/>
-      <c r="F15" s="28">
+      <c r="E15" s="25" t="n"/>
+      <c r="F15" s="29">
         <f>IFERROR(INDEX(Ref_Alimentos!$C$2:$C$101,MATCH($B15,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="G15" s="29" t="inlineStr"/>
-      <c r="H15" s="30">
+      <c r="G15" s="30" t="inlineStr"/>
+      <c r="H15" s="31">
         <f>IF($B15="","",IF($F15="Evitar","⚠ Conflito",IF(AND($F15="Moderar",SUMPRODUCT(($B$15:$B$19&lt;&gt;"")*(ROW($B$15:$B$19)&lt;&gt;ROW($B15))*(($F$15:$F$19="Moderar")+($F$15:$F$19="Evitar")))&gt;0),"⚠ Conflito","")))</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="26" customHeight="1">
-      <c r="A16" s="24" t="n">
+      <c r="A16" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="B16" s="25" t="n"/>
-      <c r="C16" s="26">
+      <c r="B16" s="26" t="n"/>
+      <c r="C16" s="27">
         <f>IFERROR(INDEX(Ref_Alimentos!$B$2:$B$101,MATCH($B16,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="D16" s="27">
+      <c r="D16" s="28">
         <f>IFERROR(INDEX(Ref_Alimentos!$D$2:$D$101,MATCH($B16,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="E16" s="24" t="n"/>
-      <c r="F16" s="28">
+      <c r="E16" s="25" t="n"/>
+      <c r="F16" s="29">
         <f>IFERROR(INDEX(Ref_Alimentos!$C$2:$C$101,MATCH($B16,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="G16" s="29">
+      <c r="G16" s="30">
         <f>IF($B15="","",IFERROR(INDEX(Ref_Alimentos!$R$2:$R$60,MATCH(IFERROR(INDEX(Ref_Alimentos!$U$2:$U$9,MATCH($C15,Ref_Alimentos!$T$2:$T$9,0)),"")&amp;"|"&amp;"Almoço",Ref_Alimentos!$Q$2:$Q$60,0)),""))</f>
         <v/>
       </c>
-      <c r="H16" s="30">
+      <c r="H16" s="31">
         <f>IF($B16="","",IF($F16="Evitar","⚠ Conflito",IF(AND($F16="Moderar",SUMPRODUCT(($B$15:$B$19&lt;&gt;"")*(ROW($B$15:$B$19)&lt;&gt;ROW($B16))*(($F$15:$F$19="Moderar")+($F$15:$F$19="Evitar")))&gt;0),"⚠ Conflito","")))</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="26" customHeight="1">
-      <c r="A17" s="24" t="n">
+      <c r="A17" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="B17" s="25" t="n"/>
-      <c r="C17" s="26">
+      <c r="B17" s="26" t="n"/>
+      <c r="C17" s="27">
         <f>IFERROR(INDEX(Ref_Alimentos!$B$2:$B$101,MATCH($B17,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="D17" s="27">
+      <c r="D17" s="28">
         <f>IFERROR(INDEX(Ref_Alimentos!$D$2:$D$101,MATCH($B17,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="E17" s="24" t="n"/>
-      <c r="F17" s="28">
+      <c r="E17" s="25" t="n"/>
+      <c r="F17" s="29">
         <f>IFERROR(INDEX(Ref_Alimentos!$C$2:$C$101,MATCH($B17,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="G17" s="29">
+      <c r="G17" s="30">
         <f>IF($B16="","",IFERROR(INDEX(Ref_Alimentos!$R$2:$R$60,MATCH(IFERROR(INDEX(Ref_Alimentos!$U$2:$U$9,MATCH($C16,Ref_Alimentos!$T$2:$T$9,0)),"")&amp;"|"&amp;"Almoço",Ref_Alimentos!$Q$2:$Q$60,0)),""))</f>
         <v/>
       </c>
-      <c r="H17" s="30">
+      <c r="H17" s="31">
         <f>IF($B17="","",IF($F17="Evitar","⚠ Conflito",IF(AND($F17="Moderar",SUMPRODUCT(($B$15:$B$19&lt;&gt;"")*(ROW($B$15:$B$19)&lt;&gt;ROW($B17))*(($F$15:$F$19="Moderar")+($F$15:$F$19="Evitar")))&gt;0),"⚠ Conflito","")))</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="26" customHeight="1">
-      <c r="A18" s="24" t="n">
+      <c r="A18" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="B18" s="25" t="n"/>
-      <c r="C18" s="26">
+      <c r="B18" s="26" t="n"/>
+      <c r="C18" s="27">
         <f>IFERROR(INDEX(Ref_Alimentos!$B$2:$B$101,MATCH($B18,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="D18" s="27">
+      <c r="D18" s="28">
         <f>IFERROR(INDEX(Ref_Alimentos!$D$2:$D$101,MATCH($B18,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="E18" s="24" t="n"/>
-      <c r="F18" s="28">
+      <c r="E18" s="25" t="n"/>
+      <c r="F18" s="29">
         <f>IFERROR(INDEX(Ref_Alimentos!$C$2:$C$101,MATCH($B18,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="G18" s="29">
+      <c r="G18" s="30">
         <f>IF($B17="","",IFERROR(INDEX(Ref_Alimentos!$R$2:$R$60,MATCH(IFERROR(INDEX(Ref_Alimentos!$U$2:$U$9,MATCH($C17,Ref_Alimentos!$T$2:$T$9,0)),"")&amp;"|"&amp;"Almoço",Ref_Alimentos!$Q$2:$Q$60,0)),""))</f>
         <v/>
       </c>
-      <c r="H18" s="30">
+      <c r="H18" s="31">
         <f>IF($B18="","",IF($F18="Evitar","⚠ Conflito",IF(AND($F18="Moderar",SUMPRODUCT(($B$15:$B$19&lt;&gt;"")*(ROW($B$15:$B$19)&lt;&gt;ROW($B18))*(($F$15:$F$19="Moderar")+($F$15:$F$19="Evitar")))&gt;0),"⚠ Conflito","")))</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="26" customHeight="1">
-      <c r="A19" s="24" t="n">
+      <c r="A19" s="25" t="n">
         <v>5</v>
       </c>
-      <c r="B19" s="25" t="n"/>
-      <c r="C19" s="26">
+      <c r="B19" s="26" t="n"/>
+      <c r="C19" s="27">
         <f>IFERROR(INDEX(Ref_Alimentos!$B$2:$B$101,MATCH($B19,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="D19" s="27">
+      <c r="D19" s="28">
         <f>IFERROR(INDEX(Ref_Alimentos!$D$2:$D$101,MATCH($B19,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="E19" s="24" t="n"/>
-      <c r="F19" s="28">
+      <c r="E19" s="25" t="n"/>
+      <c r="F19" s="29">
         <f>IFERROR(INDEX(Ref_Alimentos!$C$2:$C$101,MATCH($B19,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="G19" s="29">
+      <c r="G19" s="30">
         <f>IF($B18="","",IFERROR(INDEX(Ref_Alimentos!$R$2:$R$60,MATCH(IFERROR(INDEX(Ref_Alimentos!$U$2:$U$9,MATCH($C18,Ref_Alimentos!$T$2:$T$9,0)),"")&amp;"|"&amp;"Almoço",Ref_Alimentos!$Q$2:$Q$60,0)),""))</f>
         <v/>
       </c>
-      <c r="H19" s="30">
+      <c r="H19" s="31">
         <f>IF($B19="","",IF($F19="Evitar","⚠ Conflito",IF(AND($F19="Moderar",SUMPRODUCT(($B$15:$B$19&lt;&gt;"")*(ROW($B$15:$B$19)&lt;&gt;ROW($B19))*(($F$15:$F$19="Moderar")+($F$15:$F$19="Evitar")))&gt;0),"⚠ Conflito","")))</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="22" t="inlineStr">
+      <c r="A21" s="23" t="inlineStr">
         <is>
           <t>LANCHE</t>
         </is>
       </c>
-      <c r="B21" s="10" t="n"/>
-      <c r="C21" s="10" t="n"/>
-      <c r="D21" s="10" t="n"/>
-      <c r="E21" s="10" t="n"/>
-      <c r="F21" s="10" t="n"/>
-      <c r="G21" s="10" t="n"/>
-      <c r="H21" s="10" t="n"/>
+      <c r="B21" s="11" t="n"/>
+      <c r="C21" s="11" t="n"/>
+      <c r="D21" s="11" t="n"/>
+      <c r="E21" s="11" t="n"/>
+      <c r="F21" s="11" t="n"/>
+      <c r="G21" s="11" t="n"/>
+      <c r="H21" s="11" t="n"/>
     </row>
     <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="23" t="inlineStr">
+      <c r="A22" s="24" t="inlineStr">
         <is>
           <t>Nº</t>
         </is>
       </c>
-      <c r="B22" s="23" t="inlineStr">
+      <c r="B22" s="24" t="inlineStr">
         <is>
           <t>Alimento</t>
         </is>
       </c>
-      <c r="C22" s="23" t="inlineStr">
+      <c r="C22" s="24" t="inlineStr">
         <is>
           <t>Categoria</t>
         </is>
       </c>
-      <c r="D22" s="23" t="inlineStr">
+      <c r="D22" s="24" t="inlineStr">
         <is>
           <t>Porção sugerida</t>
         </is>
       </c>
-      <c r="E22" s="23" t="inlineStr">
+      <c r="E22" s="24" t="inlineStr">
         <is>
           <t>Quantidade a comer</t>
         </is>
       </c>
-      <c r="F22" s="23" t="inlineStr">
+      <c r="F22" s="24" t="inlineStr">
         <is>
           <t>Classificação</t>
         </is>
       </c>
-      <c r="G22" s="23" t="inlineStr">
+      <c r="G22" s="24" t="inlineStr">
         <is>
           <t>Sugestão (com base no item anterior)</t>
         </is>
       </c>
-      <c r="H22" s="23" t="inlineStr">
+      <c r="H22" s="24" t="inlineStr">
         <is>
           <t>Conflito</t>
         </is>
       </c>
     </row>
     <row r="23" ht="26" customHeight="1">
-      <c r="A23" s="24" t="n">
+      <c r="A23" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="B23" s="25" t="n"/>
-      <c r="C23" s="26">
+      <c r="B23" s="26" t="n"/>
+      <c r="C23" s="27">
         <f>IFERROR(INDEX(Ref_Alimentos!$B$2:$B$101,MATCH($B23,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="D23" s="27">
+      <c r="D23" s="28">
         <f>IFERROR(INDEX(Ref_Alimentos!$D$2:$D$101,MATCH($B23,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="E23" s="24" t="n"/>
-      <c r="F23" s="28">
+      <c r="E23" s="25" t="n"/>
+      <c r="F23" s="29">
         <f>IFERROR(INDEX(Ref_Alimentos!$C$2:$C$101,MATCH($B23,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="G23" s="29" t="inlineStr"/>
-      <c r="H23" s="30">
+      <c r="G23" s="30" t="inlineStr"/>
+      <c r="H23" s="31">
         <f>IF($B23="","",IF($F23="Evitar","⚠ Conflito",IF(AND($F23="Moderar",SUMPRODUCT(($B$23:$B$27&lt;&gt;"")*(ROW($B$23:$B$27)&lt;&gt;ROW($B23))*(($F$23:$F$27="Moderar")+($F$23:$F$27="Evitar")))&gt;0),"⚠ Conflito","")))</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="26" customHeight="1">
-      <c r="A24" s="24" t="n">
+      <c r="A24" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="B24" s="25" t="n"/>
-      <c r="C24" s="26">
+      <c r="B24" s="26" t="n"/>
+      <c r="C24" s="27">
         <f>IFERROR(INDEX(Ref_Alimentos!$B$2:$B$101,MATCH($B24,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="D24" s="27">
+      <c r="D24" s="28">
         <f>IFERROR(INDEX(Ref_Alimentos!$D$2:$D$101,MATCH($B24,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="E24" s="24" t="n"/>
-      <c r="F24" s="28">
+      <c r="E24" s="25" t="n"/>
+      <c r="F24" s="29">
         <f>IFERROR(INDEX(Ref_Alimentos!$C$2:$C$101,MATCH($B24,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="G24" s="29">
+      <c r="G24" s="30">
         <f>IF($B23="","",IFERROR(INDEX(Ref_Alimentos!$R$2:$R$60,MATCH(IFERROR(INDEX(Ref_Alimentos!$U$2:$U$9,MATCH($C23,Ref_Alimentos!$T$2:$T$9,0)),"")&amp;"|"&amp;"Lanche",Ref_Alimentos!$Q$2:$Q$60,0)),""))</f>
         <v/>
       </c>
-      <c r="H24" s="30">
+      <c r="H24" s="31">
         <f>IF($B24="","",IF($F24="Evitar","⚠ Conflito",IF(AND($F24="Moderar",SUMPRODUCT(($B$23:$B$27&lt;&gt;"")*(ROW($B$23:$B$27)&lt;&gt;ROW($B24))*(($F$23:$F$27="Moderar")+($F$23:$F$27="Evitar")))&gt;0),"⚠ Conflito","")))</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="26" customHeight="1">
-      <c r="A25" s="24" t="n">
+      <c r="A25" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="B25" s="25" t="n"/>
-      <c r="C25" s="26">
+      <c r="B25" s="26" t="n"/>
+      <c r="C25" s="27">
         <f>IFERROR(INDEX(Ref_Alimentos!$B$2:$B$101,MATCH($B25,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="D25" s="27">
+      <c r="D25" s="28">
         <f>IFERROR(INDEX(Ref_Alimentos!$D$2:$D$101,MATCH($B25,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="E25" s="24" t="n"/>
-      <c r="F25" s="28">
+      <c r="E25" s="25" t="n"/>
+      <c r="F25" s="29">
         <f>IFERROR(INDEX(Ref_Alimentos!$C$2:$C$101,MATCH($B25,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="G25" s="29">
+      <c r="G25" s="30">
         <f>IF($B24="","",IFERROR(INDEX(Ref_Alimentos!$R$2:$R$60,MATCH(IFERROR(INDEX(Ref_Alimentos!$U$2:$U$9,MATCH($C24,Ref_Alimentos!$T$2:$T$9,0)),"")&amp;"|"&amp;"Lanche",Ref_Alimentos!$Q$2:$Q$60,0)),""))</f>
         <v/>
       </c>
-      <c r="H25" s="30">
+      <c r="H25" s="31">
         <f>IF($B25="","",IF($F25="Evitar","⚠ Conflito",IF(AND($F25="Moderar",SUMPRODUCT(($B$23:$B$27&lt;&gt;"")*(ROW($B$23:$B$27)&lt;&gt;ROW($B25))*(($F$23:$F$27="Moderar")+($F$23:$F$27="Evitar")))&gt;0),"⚠ Conflito","")))</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="26" customHeight="1">
-      <c r="A26" s="24" t="n">
+      <c r="A26" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="B26" s="25" t="n"/>
-      <c r="C26" s="26">
+      <c r="B26" s="26" t="n"/>
+      <c r="C26" s="27">
         <f>IFERROR(INDEX(Ref_Alimentos!$B$2:$B$101,MATCH($B26,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="D26" s="27">
+      <c r="D26" s="28">
         <f>IFERROR(INDEX(Ref_Alimentos!$D$2:$D$101,MATCH($B26,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="E26" s="24" t="n"/>
-      <c r="F26" s="28">
+      <c r="E26" s="25" t="n"/>
+      <c r="F26" s="29">
         <f>IFERROR(INDEX(Ref_Alimentos!$C$2:$C$101,MATCH($B26,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="G26" s="29">
+      <c r="G26" s="30">
         <f>IF($B25="","",IFERROR(INDEX(Ref_Alimentos!$R$2:$R$60,MATCH(IFERROR(INDEX(Ref_Alimentos!$U$2:$U$9,MATCH($C25,Ref_Alimentos!$T$2:$T$9,0)),"")&amp;"|"&amp;"Lanche",Ref_Alimentos!$Q$2:$Q$60,0)),""))</f>
         <v/>
       </c>
-      <c r="H26" s="30">
+      <c r="H26" s="31">
         <f>IF($B26="","",IF($F26="Evitar","⚠ Conflito",IF(AND($F26="Moderar",SUMPRODUCT(($B$23:$B$27&lt;&gt;"")*(ROW($B$23:$B$27)&lt;&gt;ROW($B26))*(($F$23:$F$27="Moderar")+($F$23:$F$27="Evitar")))&gt;0),"⚠ Conflito","")))</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="26" customHeight="1">
-      <c r="A27" s="24" t="n">
+      <c r="A27" s="25" t="n">
         <v>5</v>
       </c>
-      <c r="B27" s="25" t="n"/>
-      <c r="C27" s="26">
+      <c r="B27" s="26" t="n"/>
+      <c r="C27" s="27">
         <f>IFERROR(INDEX(Ref_Alimentos!$B$2:$B$101,MATCH($B27,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="D27" s="27">
+      <c r="D27" s="28">
         <f>IFERROR(INDEX(Ref_Alimentos!$D$2:$D$101,MATCH($B27,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="E27" s="24" t="n"/>
-      <c r="F27" s="28">
+      <c r="E27" s="25" t="n"/>
+      <c r="F27" s="29">
         <f>IFERROR(INDEX(Ref_Alimentos!$C$2:$C$101,MATCH($B27,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="G27" s="29">
+      <c r="G27" s="30">
         <f>IF($B26="","",IFERROR(INDEX(Ref_Alimentos!$R$2:$R$60,MATCH(IFERROR(INDEX(Ref_Alimentos!$U$2:$U$9,MATCH($C26,Ref_Alimentos!$T$2:$T$9,0)),"")&amp;"|"&amp;"Lanche",Ref_Alimentos!$Q$2:$Q$60,0)),""))</f>
         <v/>
       </c>
-      <c r="H27" s="30">
+      <c r="H27" s="31">
         <f>IF($B27="","",IF($F27="Evitar","⚠ Conflito",IF(AND($F27="Moderar",SUMPRODUCT(($B$23:$B$27&lt;&gt;"")*(ROW($B$23:$B$27)&lt;&gt;ROW($B27))*(($F$23:$F$27="Moderar")+($F$23:$F$27="Evitar")))&gt;0),"⚠ Conflito","")))</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="22" t="inlineStr">
+      <c r="A29" s="23" t="inlineStr">
         <is>
           <t>JANTAR</t>
         </is>
       </c>
-      <c r="B29" s="10" t="n"/>
-      <c r="C29" s="10" t="n"/>
-      <c r="D29" s="10" t="n"/>
-      <c r="E29" s="10" t="n"/>
-      <c r="F29" s="10" t="n"/>
-      <c r="G29" s="10" t="n"/>
-      <c r="H29" s="10" t="n"/>
+      <c r="B29" s="11" t="n"/>
+      <c r="C29" s="11" t="n"/>
+      <c r="D29" s="11" t="n"/>
+      <c r="E29" s="11" t="n"/>
+      <c r="F29" s="11" t="n"/>
+      <c r="G29" s="11" t="n"/>
+      <c r="H29" s="11" t="n"/>
     </row>
     <row r="30" ht="30" customHeight="1">
-      <c r="A30" s="23" t="inlineStr">
+      <c r="A30" s="24" t="inlineStr">
         <is>
           <t>Nº</t>
         </is>
       </c>
-      <c r="B30" s="23" t="inlineStr">
+      <c r="B30" s="24" t="inlineStr">
         <is>
           <t>Alimento</t>
         </is>
       </c>
-      <c r="C30" s="23" t="inlineStr">
+      <c r="C30" s="24" t="inlineStr">
         <is>
           <t>Categoria</t>
         </is>
       </c>
-      <c r="D30" s="23" t="inlineStr">
+      <c r="D30" s="24" t="inlineStr">
         <is>
           <t>Porção sugerida</t>
         </is>
       </c>
-      <c r="E30" s="23" t="inlineStr">
+      <c r="E30" s="24" t="inlineStr">
         <is>
           <t>Quantidade a comer</t>
         </is>
       </c>
-      <c r="F30" s="23" t="inlineStr">
+      <c r="F30" s="24" t="inlineStr">
         <is>
           <t>Classificação</t>
         </is>
       </c>
-      <c r="G30" s="23" t="inlineStr">
+      <c r="G30" s="24" t="inlineStr">
         <is>
           <t>Sugestão (com base no item anterior)</t>
         </is>
       </c>
-      <c r="H30" s="23" t="inlineStr">
+      <c r="H30" s="24" t="inlineStr">
         <is>
           <t>Conflito</t>
         </is>
       </c>
     </row>
     <row r="31" ht="26" customHeight="1">
-      <c r="A31" s="24" t="n">
+      <c r="A31" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="B31" s="25" t="n"/>
-      <c r="C31" s="26">
+      <c r="B31" s="26" t="n"/>
+      <c r="C31" s="27">
         <f>IFERROR(INDEX(Ref_Alimentos!$B$2:$B$101,MATCH($B31,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="D31" s="27">
+      <c r="D31" s="28">
         <f>IFERROR(INDEX(Ref_Alimentos!$D$2:$D$101,MATCH($B31,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="E31" s="24" t="n"/>
-      <c r="F31" s="28">
+      <c r="E31" s="25" t="n"/>
+      <c r="F31" s="29">
         <f>IFERROR(INDEX(Ref_Alimentos!$C$2:$C$101,MATCH($B31,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="G31" s="29" t="inlineStr"/>
-      <c r="H31" s="30">
+      <c r="G31" s="30" t="inlineStr"/>
+      <c r="H31" s="31">
         <f>IF($B31="","",IF($F31="Evitar","⚠ Conflito",IF(AND($F31="Moderar",SUMPRODUCT(($B$31:$B$35&lt;&gt;"")*(ROW($B$31:$B$35)&lt;&gt;ROW($B31))*(($F$31:$F$35="Moderar")+($F$31:$F$35="Evitar")))&gt;0),"⚠ Conflito","")))</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="26" customHeight="1">
-      <c r="A32" s="24" t="n">
+      <c r="A32" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="B32" s="25" t="n"/>
-      <c r="C32" s="26">
+      <c r="B32" s="26" t="n"/>
+      <c r="C32" s="27">
         <f>IFERROR(INDEX(Ref_Alimentos!$B$2:$B$101,MATCH($B32,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="D32" s="27">
+      <c r="D32" s="28">
         <f>IFERROR(INDEX(Ref_Alimentos!$D$2:$D$101,MATCH($B32,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="E32" s="24" t="n"/>
-      <c r="F32" s="28">
+      <c r="E32" s="25" t="n"/>
+      <c r="F32" s="29">
         <f>IFERROR(INDEX(Ref_Alimentos!$C$2:$C$101,MATCH($B32,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="G32" s="29">
+      <c r="G32" s="30">
         <f>IF($B31="","",IFERROR(INDEX(Ref_Alimentos!$R$2:$R$60,MATCH(IFERROR(INDEX(Ref_Alimentos!$U$2:$U$9,MATCH($C31,Ref_Alimentos!$T$2:$T$9,0)),"")&amp;"|"&amp;"Jantar",Ref_Alimentos!$Q$2:$Q$60,0)),""))</f>
         <v/>
       </c>
-      <c r="H32" s="30">
+      <c r="H32" s="31">
         <f>IF($B32="","",IF($F32="Evitar","⚠ Conflito",IF(AND($F32="Moderar",SUMPRODUCT(($B$31:$B$35&lt;&gt;"")*(ROW($B$31:$B$35)&lt;&gt;ROW($B32))*(($F$31:$F$35="Moderar")+($F$31:$F$35="Evitar")))&gt;0),"⚠ Conflito","")))</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="26" customHeight="1">
-      <c r="A33" s="24" t="n">
+      <c r="A33" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="B33" s="25" t="n"/>
-      <c r="C33" s="26">
+      <c r="B33" s="26" t="n"/>
+      <c r="C33" s="27">
         <f>IFERROR(INDEX(Ref_Alimentos!$B$2:$B$101,MATCH($B33,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="D33" s="27">
+      <c r="D33" s="28">
         <f>IFERROR(INDEX(Ref_Alimentos!$D$2:$D$101,MATCH($B33,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="E33" s="24" t="n"/>
-      <c r="F33" s="28">
+      <c r="E33" s="25" t="n"/>
+      <c r="F33" s="29">
         <f>IFERROR(INDEX(Ref_Alimentos!$C$2:$C$101,MATCH($B33,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="G33" s="29">
+      <c r="G33" s="30">
         <f>IF($B32="","",IFERROR(INDEX(Ref_Alimentos!$R$2:$R$60,MATCH(IFERROR(INDEX(Ref_Alimentos!$U$2:$U$9,MATCH($C32,Ref_Alimentos!$T$2:$T$9,0)),"")&amp;"|"&amp;"Jantar",Ref_Alimentos!$Q$2:$Q$60,0)),""))</f>
         <v/>
       </c>
-      <c r="H33" s="30">
+      <c r="H33" s="31">
         <f>IF($B33="","",IF($F33="Evitar","⚠ Conflito",IF(AND($F33="Moderar",SUMPRODUCT(($B$31:$B$35&lt;&gt;"")*(ROW($B$31:$B$35)&lt;&gt;ROW($B33))*(($F$31:$F$35="Moderar")+($F$31:$F$35="Evitar")))&gt;0),"⚠ Conflito","")))</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="26" customHeight="1">
-      <c r="A34" s="24" t="n">
+      <c r="A34" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="B34" s="25" t="n"/>
-      <c r="C34" s="26">
+      <c r="B34" s="26" t="n"/>
+      <c r="C34" s="27">
         <f>IFERROR(INDEX(Ref_Alimentos!$B$2:$B$101,MATCH($B34,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="D34" s="27">
+      <c r="D34" s="28">
         <f>IFERROR(INDEX(Ref_Alimentos!$D$2:$D$101,MATCH($B34,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="E34" s="24" t="n"/>
-      <c r="F34" s="28">
+      <c r="E34" s="25" t="n"/>
+      <c r="F34" s="29">
         <f>IFERROR(INDEX(Ref_Alimentos!$C$2:$C$101,MATCH($B34,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="G34" s="29">
+      <c r="G34" s="30">
         <f>IF($B33="","",IFERROR(INDEX(Ref_Alimentos!$R$2:$R$60,MATCH(IFERROR(INDEX(Ref_Alimentos!$U$2:$U$9,MATCH($C33,Ref_Alimentos!$T$2:$T$9,0)),"")&amp;"|"&amp;"Jantar",Ref_Alimentos!$Q$2:$Q$60,0)),""))</f>
         <v/>
       </c>
-      <c r="H34" s="30">
+      <c r="H34" s="31">
         <f>IF($B34="","",IF($F34="Evitar","⚠ Conflito",IF(AND($F34="Moderar",SUMPRODUCT(($B$31:$B$35&lt;&gt;"")*(ROW($B$31:$B$35)&lt;&gt;ROW($B34))*(($F$31:$F$35="Moderar")+($F$31:$F$35="Evitar")))&gt;0),"⚠ Conflito","")))</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="26" customHeight="1">
-      <c r="A35" s="24" t="n">
+      <c r="A35" s="25" t="n">
         <v>5</v>
       </c>
-      <c r="B35" s="25" t="n"/>
-      <c r="C35" s="26">
+      <c r="B35" s="26" t="n"/>
+      <c r="C35" s="27">
         <f>IFERROR(INDEX(Ref_Alimentos!$B$2:$B$101,MATCH($B35,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="D35" s="27">
+      <c r="D35" s="28">
         <f>IFERROR(INDEX(Ref_Alimentos!$D$2:$D$101,MATCH($B35,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="E35" s="24" t="n"/>
-      <c r="F35" s="28">
+      <c r="E35" s="25" t="n"/>
+      <c r="F35" s="29">
         <f>IFERROR(INDEX(Ref_Alimentos!$C$2:$C$101,MATCH($B35,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="G35" s="29">
+      <c r="G35" s="30">
         <f>IF($B34="","",IFERROR(INDEX(Ref_Alimentos!$R$2:$R$60,MATCH(IFERROR(INDEX(Ref_Alimentos!$U$2:$U$9,MATCH($C34,Ref_Alimentos!$T$2:$T$9,0)),"")&amp;"|"&amp;"Jantar",Ref_Alimentos!$Q$2:$Q$60,0)),""))</f>
         <v/>
       </c>
-      <c r="H35" s="30">
+      <c r="H35" s="31">
         <f>IF($B35="","",IF($F35="Evitar","⚠ Conflito",IF(AND($F35="Moderar",SUMPRODUCT(($B$31:$B$35&lt;&gt;"")*(ROW($B$31:$B$35)&lt;&gt;ROW($B35))*(($F$31:$F$35="Moderar")+($F$31:$F$35="Evitar")))&gt;0),"⚠ Conflito","")))</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="44" customHeight="1">
-      <c r="A37" s="31" t="inlineStr">
+      <c r="A37" s="9" t="inlineStr">
         <is>
           <t>Limitações conhecidas: a ordem do menu suspenso é fixa (Liberado &gt; Moderar &gt; Evitar), ela não se reordena sozinha conforme o item anterior — quem indica o que combina melhor é a coluna 'Sugestão'. A coluna 'Conflito' é uma aproximação (marca um item 'Evitar' sozinho, ou dois itens 'Moderar'/'Evitar' juntos na mesma refeição) — não é uma checagem real de interação entre os dois alimentos específicos.</t>
         </is>
@@ -3077,7 +3219,7 @@
       </c>
     </row>
     <row r="2" ht="56" customHeight="1">
-      <c r="A2" s="16" t="inlineStr">
+      <c r="A2" s="17" t="inlineStr">
         <is>
           <t>Pesquisa feita em 04/09/2026, priorizando bulas oficiais (Anvisa), estudos revisados por pares (PubMed/PMC), órgãos de saúde do governo (NIH) e diretrizes de sociedades médicas (SBC, AHA, ACC/ESC, KDIGO, ESUR, ESVS, ADA/SBD). A coluna 'Área' diz se a fonte é sobre alimentação/interação com alimento ou sobre o quadro clínico em geral. Nenhuma destas fontes substitui a avaliação do seu médico — use como ponto de partida para perguntar e confirmar na consulta. Clique no link da coluna 'Fonte' para abrir a página original.</t>
         </is>
@@ -3776,7 +3918,7 @@
       </c>
     </row>
     <row r="27" ht="24" customHeight="1">
-      <c r="A27" s="16" t="inlineStr">
+      <c r="A27" s="17" t="inlineStr">
         <is>
           <t>Lista completa com os mesmos links (mais fácil de clicar em Markdown) também em referencia/historico-tratamento.md, seção 'Referências médicas'.</t>
         </is>
@@ -3822,7 +3964,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U36"/>
+  <dimension ref="A1:U37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4464,7 +4606,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Iogurte natural (desnatado, sem açúcar)</t>
+          <t>Queijo frescal light</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -4548,7 +4690,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Água</t>
+          <t>Iogurte natural (desnatado, sem açúcar)</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -4618,7 +4760,7 @@
       <c r="J10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Iogurte natural (desnatado, sem açúcar)</t>
+          <t>Queijo frescal light</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4628,7 +4770,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Café sem açúcar</t>
+          <t>Água</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -4688,7 +4830,7 @@
       <c r="J11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Água</t>
+          <t>Iogurte natural (desnatado, sem açúcar)</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4698,7 +4840,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Vegetais e verduras em geral</t>
+          <t>Café sem açúcar</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -4762,7 +4904,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Café sem açúcar</t>
+          <t>Água</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -4772,7 +4914,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Uva</t>
+          <t>Vegetais e verduras em geral</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -4832,7 +4974,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Vegetais e verduras em geral</t>
+          <t>Café sem açúcar</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -4842,7 +4984,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Manga</t>
+          <t>Uva</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -4906,7 +5048,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Uva</t>
+          <t>Vegetais e verduras em geral</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -4916,7 +5058,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Mussarela</t>
+          <t>Manga</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -4980,7 +5122,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Manga</t>
+          <t>Uva</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -4990,7 +5132,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Requeijão</t>
+          <t>Mussarela</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -5050,7 +5192,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Mussarela</t>
+          <t>Manga</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -5060,7 +5202,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Refrigerante zero</t>
+          <t>Requeijão</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -5120,7 +5262,7 @@
       <c r="J17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Requeijão</t>
+          <t>Mussarela</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -5130,7 +5272,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Suco natural sem açúcar</t>
+          <t>Refrigerante zero</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -5194,12 +5336,12 @@
       <c r="J18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
+          <t>Requeijão</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
           <t>Suco natural sem açúcar</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>Chocolate amargo (70%+)</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -5216,7 +5358,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Mussarela</t>
+          <t>Queijo frescal light</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5226,22 +5368,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Moderar</t>
+          <t>Liberado</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>30 g</t>
+          <t>30 g (1 fatia)</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2x/semana</t>
+          <t>3x/semana</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mais gordura saturada e sódio que o queijo branco frescal; prefira o frescal no dia a dia. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
+          <t>Rótulo real: 41 kcal e 105 mg de sódio por porção (bem abaixo de queijos comuns), 1,5 g de gordura saturada, sem açúcar adicionado. Contém lactose; sem glúten; pode conter soja.</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -5258,12 +5400,12 @@
       <c r="J19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Toranja / grapefruit</t>
+          <t>Suco natural sem açúcar</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Toranja / grapefruit</t>
+          <t>Chocolate amargo (70%+)</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -5280,7 +5422,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Iogurte natural (desnatado, sem açúcar)</t>
+          <t>Mussarela</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5290,22 +5432,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Liberado</t>
+          <t>Moderar</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1 unidade</t>
+          <t>30 g</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1x/dia</t>
+          <t>2x/semana</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Prefira sempre a versão sem açúcar adicionado</t>
+          <t>Mais gordura saturada e sódio que o queijo branco frescal; prefira o frescal no dia a dia. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -5322,12 +5464,12 @@
       <c r="J20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Suco de toranja / grapefruit</t>
+          <t>Toranja / grapefruit</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Suco de toranja / grapefruit</t>
+          <t>Toranja / grapefruit</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
@@ -5344,7 +5486,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Requeijão</t>
+          <t>Iogurte natural (desnatado, sem açúcar)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5354,22 +5496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Moderar</t>
+          <t>Liberado</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1 colher de sopa (≈15 g)</t>
+          <t>1 unidade</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2x/semana</t>
+          <t>1x/dia</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rico em gordura saturada e sódio; prefira a versão light. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
+          <t>Prefira sempre a versão sem açúcar adicionado</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -5386,12 +5528,12 @@
       <c r="J21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Açúcar refinado</t>
+          <t>Suco de toranja / grapefruit</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Açúcar refinado</t>
+          <t>Suco de toranja / grapefruit</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
@@ -5408,58 +5550,54 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Água</t>
+          <t>Requeijão</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Bebidas</t>
+          <t>Laticínios</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Liberado</t>
+          <t>Moderar</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>à vontade</t>
+          <t>1 colher de sopa (≈15 g)</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>todos os dias</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr"/>
+          <t>2x/semana</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Rico em gordura saturada e sódio; prefira a versão light. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
+        </is>
+      </c>
       <c r="G22" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="J22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Manteiga</t>
+          <t>Açúcar refinado</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Doces industrializados</t>
+          <t>Açúcar refinado</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
@@ -5476,7 +5614,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Refrigerante zero</t>
+          <t>Água</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -5486,25 +5624,25 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Moderar</t>
+          <t>Liberado</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>200 ml</t>
+          <t>à vontade</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1x/dia</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Sugestão gerada por IA — confirmar com nutricionista/cardiologista</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr"/>
+          <t>todos os dias</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="H23" t="inlineStr">
         <is>
           <t>X</t>
@@ -5518,6 +5656,16 @@
       <c r="J23" t="inlineStr">
         <is>
           <t>X</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Manteiga</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Doces industrializados</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
@@ -5534,7 +5682,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Café sem açúcar</t>
+          <t>Refrigerante zero</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5544,32 +5692,40 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Liberado</t>
+          <t>Moderar</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1 xícara</t>
+          <t>200 ml</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2x/dia</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr"/>
+          <t>1x/dia</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Sugestão gerada por IA — confirmar com nutricionista/cardiologista</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="Q24" t="inlineStr">
         <is>
           <t>Bebidas|Jantar</t>
@@ -5584,7 +5740,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Suco natural sem açúcar</t>
+          <t>Café sem açúcar</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5594,24 +5750,20 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Moderar</t>
+          <t>Liberado</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>200 ml</t>
+          <t>1 xícara</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>3x/semana</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Preferir a fruta inteira, que tem mais fibra</t>
-        </is>
-      </c>
+          <t>2x/dia</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
           <t>X</t>
@@ -5638,7 +5790,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Suco de toranja / grapefruit</t>
+          <t>Suco natural sem açúcar</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5648,22 +5800,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Evitar</t>
+          <t>Moderar</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>200 ml</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>evitar</t>
+          <t>3x/semana</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Interage com o Ticagrelor (estudo mostrou quase o dobro do nível do remédio no sangue); a bula diz que não é esperado ser clinicamente relevante p/ a maioria, mas orienta evitar — mais seguro evitar, já que você toma 2 antiagregantes. Ver aba Fontes e Referências.</t>
+          <t>Preferir a fruta inteira, que tem mais fibra</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -5692,7 +5844,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Bebida alcoólica</t>
+          <t>Suco de toranja / grapefruit</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5717,21 +5869,21 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Piora diretamente os triglicerídeos; soma-se ao risco de sangramento da Aspirina + Ticagrelor.</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+          <t>Interage com o Ticagrelor (estudo mostrou quase o dobro do nível do remédio no sangue); a bula diz que não é esperado ser clinicamente relevante p/ a maioria, mas orienta evitar — mais seguro evitar, já que você toma 2 antiagregantes. Ver aba Fontes e Referências.</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
       <c r="Q27" t="inlineStr">
         <is>
           <t>Vegetais e Verduras|Jantar</t>
@@ -5746,12 +5898,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Açúcar refinado</t>
+          <t>Bebida alcoólica</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Doces e Sobremesas</t>
+          <t>Bebidas</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -5771,24 +5923,16 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Impacto direto nos triglicerídeos</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+          <t>Piora diretamente os triglicerídeos; soma-se ao risco de sangramento da Aspirina + Ticagrelor.</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
           <t>X</t>
@@ -5798,7 +5942,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Doces industrializados</t>
+          <t>Açúcar refinado</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5821,20 +5965,36 @@
           <t>evitar</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Impacto direto nos triglicerídeos</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Chocolate amargo (70%+)</t>
+          <t>Doces industrializados</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -5844,24 +6004,20 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Moderar</t>
+          <t>Evitar</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>10 g</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2x/semana</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Sugestão gerada por IA — confirmar com nutricionista/cardiologista</t>
-        </is>
-      </c>
+          <t>evitar</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
@@ -5874,47 +6030,47 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Azeite de oliva extra virgem</t>
+          <t>Chocolate amargo (70%+)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Gorduras e Temperos</t>
+          <t>Doces e Sobremesas</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Liberado</t>
+          <t>Moderar</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1-2 colheres de sopa</t>
+          <t>10 g</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1x/dia</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr"/>
+          <t>2x/semana</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Sugestão gerada por IA — confirmar com nutricionista/cardiologista</t>
+        </is>
+      </c>
       <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Manteiga</t>
+          <t>Azeite de oliva extra virgem</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -5924,37 +6080,37 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Evitar</t>
+          <t>Liberado</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1-2 colheres de sopa</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>evitar</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Preferir azeite</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr"/>
+          <t>1x/dia</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Sal</t>
+          <t>Manteiga</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -5964,41 +6120,37 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Moderar</t>
+          <t>Evitar</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>&lt; 5 g no total</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>todos os dias</t>
+          <t>evitar</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Somar sal de cozinha + industrializados</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+          <t>Preferir azeite</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="J33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sal light / substituto de sal (cloreto de potássio)</t>
+          <t>Sal</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -6008,22 +6160,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Evitar</t>
+          <t>Moderar</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>&lt; 5 g no total</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>evitar</t>
+          <t>todos os dias</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Enalapril já tende a elevar o potássio; combinado com esse produto o risco de hipercalemia aumenta, ainda mais com a função renal pendente.</t>
+          <t>Somar sal de cozinha + industrializados</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
@@ -6042,7 +6194,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Ervas e temperos naturais</t>
+          <t>Sal light / substituto de sal (cloreto de potássio)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -6052,20 +6204,24 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Liberado</t>
+          <t>Evitar</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>à vontade</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>todos os dias</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr"/>
+          <t>evitar</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Enalapril já tende a elevar o potássio; combinado com esse produto o risco de hipercalemia aumenta, ainda mais com a função renal pendente.</t>
+        </is>
+      </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
@@ -6082,50 +6238,90 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>Ervas e temperos naturais</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Gorduras e Temperos</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Liberado</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>à vontade</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>todos os dias</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
           <t>Vegetais e verduras em geral</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>Vegetais e Verduras</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>Liberado</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>à vontade</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>todos os dias</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>Se entrar anticoagulante na medicação, revisar consumo de verde-escuros ricos em vitamina K</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
         <is>
           <t>X</t>
         </is>

--- a/planilha/plano-alimentar-pos-infarto.xlsx
+++ b/planilha/plano-alimentar-pos-infarto.xlsx
@@ -1061,7 +1061,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H49"/>
+  <dimension ref="A1:H50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1447,53 +1447,57 @@
       <c r="G15" s="13" t="inlineStr"/>
       <c r="H15" s="12" t="inlineStr"/>
     </row>
-    <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="10" t="inlineStr">
+    <row r="16" ht="30" customHeight="1">
+      <c r="B16" s="12" t="inlineStr">
+        <is>
+          <t>Pão francês integral (multigrãos)</t>
+        </is>
+      </c>
+      <c r="C16" s="13" t="inlineStr">
+        <is>
+          <t>Mambo</t>
+        </is>
+      </c>
+      <c r="D16" s="13" t="inlineStr">
+        <is>
+          <t>1 unidade (~67 g)</t>
+        </is>
+      </c>
+      <c r="E16" s="13" t="inlineStr">
+        <is>
+          <t>1x/dia</t>
+        </is>
+      </c>
+      <c r="F16" s="14" t="inlineStr">
+        <is>
+          <t>Liberado</t>
+        </is>
+      </c>
+      <c r="G16" s="13" t="inlineStr"/>
+      <c r="H16" s="12" t="inlineStr">
+        <is>
+          <t>Rótulo real (porção 50 g/meia unidade): 120 kcal, 208 mg de sódio, 1,6 g de fibras, sem açúcar adicionado. Com centeio, gergelim e linhaça — boa fonte de fibra, mas sódio moderado como a maioria dos pães; contém glúten.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="10" t="inlineStr">
         <is>
           <t>Proteínas</t>
         </is>
       </c>
-      <c r="B16" s="11" t="n"/>
-      <c r="C16" s="11" t="n"/>
-      <c r="D16" s="11" t="n"/>
-      <c r="E16" s="11" t="n"/>
-      <c r="F16" s="11" t="n"/>
-      <c r="G16" s="11" t="n"/>
-      <c r="H16" s="11" t="n"/>
-    </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="B17" s="12" t="inlineStr">
-        <is>
-          <t>Peixe</t>
-        </is>
-      </c>
-      <c r="C17" s="13" t="inlineStr"/>
-      <c r="D17" s="13" t="inlineStr">
-        <is>
-          <t>150 g</t>
-        </is>
-      </c>
-      <c r="E17" s="13" t="inlineStr">
-        <is>
-          <t>3x/semana</t>
-        </is>
-      </c>
-      <c r="F17" s="14" t="inlineStr">
-        <is>
-          <t>Liberado</t>
-        </is>
-      </c>
-      <c r="G17" s="13" t="inlineStr"/>
-      <c r="H17" s="12" t="inlineStr">
-        <is>
-          <t>Fonte de ômega-3</t>
-        </is>
-      </c>
+      <c r="B17" s="11" t="n"/>
+      <c r="C17" s="11" t="n"/>
+      <c r="D17" s="11" t="n"/>
+      <c r="E17" s="11" t="n"/>
+      <c r="F17" s="11" t="n"/>
+      <c r="G17" s="11" t="n"/>
+      <c r="H17" s="11" t="n"/>
     </row>
     <row r="18" ht="30" customHeight="1">
       <c r="B18" s="12" t="inlineStr">
         <is>
-          <t>Frango sem pele</t>
+          <t>Peixe</t>
         </is>
       </c>
       <c r="C18" s="13" t="inlineStr"/>
@@ -1504,7 +1508,7 @@
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>quase todo dia</t>
+          <t>3x/semana</t>
         </is>
       </c>
       <c r="F18" s="14" t="inlineStr">
@@ -1513,12 +1517,16 @@
         </is>
       </c>
       <c r="G18" s="13" t="inlineStr"/>
-      <c r="H18" s="12" t="inlineStr"/>
+      <c r="H18" s="12" t="inlineStr">
+        <is>
+          <t>Fonte de ômega-3</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="30" customHeight="1">
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>Carne vermelha magra</t>
+          <t>Frango sem pele</t>
         </is>
       </c>
       <c r="C19" s="13" t="inlineStr"/>
@@ -1529,61 +1537,61 @@
       </c>
       <c r="E19" s="13" t="inlineStr">
         <is>
-          <t>1x/semana</t>
-        </is>
-      </c>
-      <c r="F19" s="15" t="inlineStr">
-        <is>
-          <t>Moderar</t>
+          <t>quase todo dia</t>
+        </is>
+      </c>
+      <c r="F19" s="14" t="inlineStr">
+        <is>
+          <t>Liberado</t>
         </is>
       </c>
       <c r="G19" s="13" t="inlineStr"/>
-      <c r="H19" s="12" t="inlineStr">
-        <is>
-          <t>Preferir cortes magros</t>
-        </is>
-      </c>
+      <c r="H19" s="12" t="inlineStr"/>
     </row>
     <row r="20" ht="30" customHeight="1">
       <c r="B20" s="12" t="inlineStr">
         <is>
-          <t>Ovo</t>
+          <t>Carne vermelha magra</t>
         </is>
       </c>
       <c r="C20" s="13" t="inlineStr"/>
       <c r="D20" s="13" t="inlineStr">
         <is>
-          <t>1 unidade</t>
+          <t>150 g</t>
         </is>
       </c>
       <c r="E20" s="13" t="inlineStr">
         <is>
-          <t>até 5x/semana</t>
-        </is>
-      </c>
-      <c r="F20" s="14" t="inlineStr">
-        <is>
-          <t>Liberado</t>
+          <t>1x/semana</t>
+        </is>
+      </c>
+      <c r="F20" s="15" t="inlineStr">
+        <is>
+          <t>Moderar</t>
         </is>
       </c>
       <c r="G20" s="13" t="inlineStr"/>
-      <c r="H20" s="12" t="inlineStr"/>
+      <c r="H20" s="12" t="inlineStr">
+        <is>
+          <t>Preferir cortes magros</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="30" customHeight="1">
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>Feijão / leguminosas</t>
+          <t>Ovo</t>
         </is>
       </c>
       <c r="C21" s="13" t="inlineStr"/>
       <c r="D21" s="13" t="inlineStr">
         <is>
-          <t>1 concha</t>
+          <t>1 unidade</t>
         </is>
       </c>
       <c r="E21" s="13" t="inlineStr">
         <is>
-          <t>1x/dia</t>
+          <t>até 5x/semana</t>
         </is>
       </c>
       <c r="F21" s="14" t="inlineStr">
@@ -1594,60 +1602,60 @@
       <c r="G21" s="13" t="inlineStr"/>
       <c r="H21" s="12" t="inlineStr"/>
     </row>
-    <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="10" t="inlineStr">
+    <row r="22" ht="30" customHeight="1">
+      <c r="B22" s="12" t="inlineStr">
+        <is>
+          <t>Feijão / leguminosas</t>
+        </is>
+      </c>
+      <c r="C22" s="13" t="inlineStr"/>
+      <c r="D22" s="13" t="inlineStr">
+        <is>
+          <t>1 concha</t>
+        </is>
+      </c>
+      <c r="E22" s="13" t="inlineStr">
+        <is>
+          <t>1x/dia</t>
+        </is>
+      </c>
+      <c r="F22" s="14" t="inlineStr">
+        <is>
+          <t>Liberado</t>
+        </is>
+      </c>
+      <c r="G22" s="13" t="inlineStr"/>
+      <c r="H22" s="12" t="inlineStr"/>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="10" t="inlineStr">
         <is>
           <t>Laticínios</t>
         </is>
       </c>
-      <c r="B22" s="11" t="n"/>
-      <c r="C22" s="11" t="n"/>
-      <c r="D22" s="11" t="n"/>
-      <c r="E22" s="11" t="n"/>
-      <c r="F22" s="11" t="n"/>
-      <c r="G22" s="11" t="n"/>
-      <c r="H22" s="11" t="n"/>
-    </row>
-    <row r="23" ht="30" customHeight="1">
-      <c r="B23" s="12" t="inlineStr">
-        <is>
-          <t>Leite desnatado</t>
-        </is>
-      </c>
-      <c r="C23" s="13" t="inlineStr"/>
-      <c r="D23" s="13" t="inlineStr">
-        <is>
-          <t>200 ml</t>
-        </is>
-      </c>
-      <c r="E23" s="13" t="inlineStr">
-        <is>
-          <t>1x/dia</t>
-        </is>
-      </c>
-      <c r="F23" s="14" t="inlineStr">
-        <is>
-          <t>Liberado</t>
-        </is>
-      </c>
-      <c r="G23" s="13" t="inlineStr"/>
-      <c r="H23" s="12" t="inlineStr"/>
+      <c r="B23" s="11" t="n"/>
+      <c r="C23" s="11" t="n"/>
+      <c r="D23" s="11" t="n"/>
+      <c r="E23" s="11" t="n"/>
+      <c r="F23" s="11" t="n"/>
+      <c r="G23" s="11" t="n"/>
+      <c r="H23" s="11" t="n"/>
     </row>
     <row r="24" ht="30" customHeight="1">
       <c r="B24" s="12" t="inlineStr">
         <is>
-          <t>Queijo branco frescal</t>
+          <t>Leite desnatado</t>
         </is>
       </c>
       <c r="C24" s="13" t="inlineStr"/>
       <c r="D24" s="13" t="inlineStr">
         <is>
-          <t>30 g</t>
+          <t>200 ml</t>
         </is>
       </c>
       <c r="E24" s="13" t="inlineStr">
         <is>
-          <t>3x/semana</t>
+          <t>1x/dia</t>
         </is>
       </c>
       <c r="F24" s="14" t="inlineStr">
@@ -1656,26 +1664,18 @@
         </is>
       </c>
       <c r="G24" s="13" t="inlineStr"/>
-      <c r="H24" s="12" t="inlineStr">
-        <is>
-          <t>Tipo fresco (ex.: Minas frescal), sem cura/salga pesada — bem menos sódio e gordura que queijos curados. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
-        </is>
-      </c>
+      <c r="H24" s="12" t="inlineStr"/>
     </row>
     <row r="25" ht="30" customHeight="1">
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>Queijo frescal light</t>
-        </is>
-      </c>
-      <c r="C25" s="13" t="inlineStr">
-        <is>
-          <t>Polenghi</t>
-        </is>
-      </c>
+          <t>Queijo branco frescal</t>
+        </is>
+      </c>
+      <c r="C25" s="13" t="inlineStr"/>
       <c r="D25" s="13" t="inlineStr">
         <is>
-          <t>30 g (1 fatia)</t>
+          <t>30 g</t>
         </is>
       </c>
       <c r="E25" s="13" t="inlineStr">
@@ -1691,252 +1691,256 @@
       <c r="G25" s="13" t="inlineStr"/>
       <c r="H25" s="12" t="inlineStr">
         <is>
-          <t>Rótulo real: 41 kcal e 105 mg de sódio por porção (bem abaixo de queijos comuns), 1,5 g de gordura saturada, sem açúcar adicionado. Contém lactose; sem glúten; pode conter soja.</t>
+          <t>Tipo fresco (ex.: Minas frescal), sem cura/salga pesada — bem menos sódio e gordura que queijos curados. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="30" customHeight="1">
       <c r="B26" s="12" t="inlineStr">
         <is>
-          <t>Mussarela</t>
-        </is>
-      </c>
-      <c r="C26" s="13" t="inlineStr"/>
+          <t>Queijo frescal light</t>
+        </is>
+      </c>
+      <c r="C26" s="13" t="inlineStr">
+        <is>
+          <t>Polenghi</t>
+        </is>
+      </c>
       <c r="D26" s="13" t="inlineStr">
         <is>
-          <t>30 g</t>
+          <t>30 g (1 fatia)</t>
         </is>
       </c>
       <c r="E26" s="13" t="inlineStr">
         <is>
-          <t>2x/semana</t>
-        </is>
-      </c>
-      <c r="F26" s="15" t="inlineStr">
-        <is>
-          <t>Moderar</t>
+          <t>3x/semana</t>
+        </is>
+      </c>
+      <c r="F26" s="14" t="inlineStr">
+        <is>
+          <t>Liberado</t>
         </is>
       </c>
       <c r="G26" s="13" t="inlineStr"/>
       <c r="H26" s="12" t="inlineStr">
         <is>
-          <t>Mais gordura saturada e sódio que o queijo branco frescal; prefira o frescal no dia a dia. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
+          <t>Rótulo real: 41 kcal e 105 mg de sódio por porção (bem abaixo de queijos comuns), 1,5 g de gordura saturada, sem açúcar adicionado. Contém lactose; sem glúten; pode conter soja.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="30" customHeight="1">
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>Iogurte natural (desnatado, sem açúcar)</t>
+          <t>Mussarela</t>
         </is>
       </c>
       <c r="C27" s="13" t="inlineStr"/>
       <c r="D27" s="13" t="inlineStr">
         <is>
-          <t>1 unidade</t>
+          <t>30 g</t>
         </is>
       </c>
       <c r="E27" s="13" t="inlineStr">
         <is>
-          <t>1x/dia</t>
-        </is>
-      </c>
-      <c r="F27" s="14" t="inlineStr">
-        <is>
-          <t>Liberado</t>
+          <t>2x/semana</t>
+        </is>
+      </c>
+      <c r="F27" s="15" t="inlineStr">
+        <is>
+          <t>Moderar</t>
         </is>
       </c>
       <c r="G27" s="13" t="inlineStr"/>
       <c r="H27" s="12" t="inlineStr">
         <is>
-          <t>Prefira sempre a versão sem açúcar adicionado</t>
+          <t>Mais gordura saturada e sódio que o queijo branco frescal; prefira o frescal no dia a dia. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="30" customHeight="1">
       <c r="B28" s="12" t="inlineStr">
         <is>
-          <t>Requeijão</t>
+          <t>Iogurte natural (desnatado, sem açúcar)</t>
         </is>
       </c>
       <c r="C28" s="13" t="inlineStr"/>
       <c r="D28" s="13" t="inlineStr">
         <is>
-          <t>1 colher de sopa (≈15 g)</t>
+          <t>1 unidade</t>
         </is>
       </c>
       <c r="E28" s="13" t="inlineStr">
         <is>
-          <t>2x/semana</t>
-        </is>
-      </c>
-      <c r="F28" s="15" t="inlineStr">
-        <is>
-          <t>Moderar</t>
+          <t>1x/dia</t>
+        </is>
+      </c>
+      <c r="F28" s="14" t="inlineStr">
+        <is>
+          <t>Liberado</t>
         </is>
       </c>
       <c r="G28" s="13" t="inlineStr"/>
       <c r="H28" s="12" t="inlineStr">
         <is>
+          <t>Prefira sempre a versão sem açúcar adicionado</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="30" customHeight="1">
+      <c r="B29" s="12" t="inlineStr">
+        <is>
+          <t>Requeijão</t>
+        </is>
+      </c>
+      <c r="C29" s="13" t="inlineStr"/>
+      <c r="D29" s="13" t="inlineStr">
+        <is>
+          <t>1 colher de sopa (≈15 g)</t>
+        </is>
+      </c>
+      <c r="E29" s="13" t="inlineStr">
+        <is>
+          <t>2x/semana</t>
+        </is>
+      </c>
+      <c r="F29" s="15" t="inlineStr">
+        <is>
+          <t>Moderar</t>
+        </is>
+      </c>
+      <c r="G29" s="13" t="inlineStr"/>
+      <c r="H29" s="12" t="inlineStr">
+        <is>
           <t>Rico em gordura saturada e sódio; prefira a versão light. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="10" t="inlineStr">
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="10" t="inlineStr">
         <is>
           <t>Bebidas</t>
         </is>
       </c>
-      <c r="B29" s="11" t="n"/>
-      <c r="C29" s="11" t="n"/>
-      <c r="D29" s="11" t="n"/>
-      <c r="E29" s="11" t="n"/>
-      <c r="F29" s="11" t="n"/>
-      <c r="G29" s="11" t="n"/>
-      <c r="H29" s="11" t="n"/>
-    </row>
-    <row r="30" ht="30" customHeight="1">
-      <c r="B30" s="12" t="inlineStr">
-        <is>
-          <t>Água</t>
-        </is>
-      </c>
-      <c r="C30" s="13" t="inlineStr"/>
-      <c r="D30" s="13" t="inlineStr">
-        <is>
-          <t>à vontade</t>
-        </is>
-      </c>
-      <c r="E30" s="13" t="inlineStr">
-        <is>
-          <t>todos os dias</t>
-        </is>
-      </c>
-      <c r="F30" s="14" t="inlineStr">
-        <is>
-          <t>Liberado</t>
-        </is>
-      </c>
-      <c r="G30" s="13" t="inlineStr"/>
-      <c r="H30" s="12" t="inlineStr"/>
+      <c r="B30" s="11" t="n"/>
+      <c r="C30" s="11" t="n"/>
+      <c r="D30" s="11" t="n"/>
+      <c r="E30" s="11" t="n"/>
+      <c r="F30" s="11" t="n"/>
+      <c r="G30" s="11" t="n"/>
+      <c r="H30" s="11" t="n"/>
     </row>
     <row r="31" ht="30" customHeight="1">
       <c r="B31" s="12" t="inlineStr">
         <is>
-          <t>Refrigerante zero</t>
+          <t>Água</t>
         </is>
       </c>
       <c r="C31" s="13" t="inlineStr"/>
       <c r="D31" s="13" t="inlineStr">
         <is>
-          <t>200 ml</t>
+          <t>à vontade</t>
         </is>
       </c>
       <c r="E31" s="13" t="inlineStr">
         <is>
-          <t>1x/dia</t>
-        </is>
-      </c>
-      <c r="F31" s="15" t="inlineStr">
-        <is>
-          <t>Moderar</t>
+          <t>todos os dias</t>
+        </is>
+      </c>
+      <c r="F31" s="14" t="inlineStr">
+        <is>
+          <t>Liberado</t>
         </is>
       </c>
       <c r="G31" s="13" t="inlineStr"/>
-      <c r="H31" s="12" t="inlineStr">
-        <is>
-          <t>Sugestão gerada por IA — confirmar com nutricionista/cardiologista</t>
-        </is>
-      </c>
+      <c r="H31" s="12" t="inlineStr"/>
     </row>
     <row r="32" ht="30" customHeight="1">
       <c r="B32" s="12" t="inlineStr">
         <is>
-          <t>Café sem açúcar</t>
+          <t>Refrigerante zero</t>
         </is>
       </c>
       <c r="C32" s="13" t="inlineStr"/>
       <c r="D32" s="13" t="inlineStr">
         <is>
-          <t>1 xícara</t>
+          <t>200 ml</t>
         </is>
       </c>
       <c r="E32" s="13" t="inlineStr">
         <is>
-          <t>2x/dia</t>
-        </is>
-      </c>
-      <c r="F32" s="14" t="inlineStr">
-        <is>
-          <t>Liberado</t>
+          <t>1x/dia</t>
+        </is>
+      </c>
+      <c r="F32" s="15" t="inlineStr">
+        <is>
+          <t>Moderar</t>
         </is>
       </c>
       <c r="G32" s="13" t="inlineStr"/>
-      <c r="H32" s="12" t="inlineStr"/>
+      <c r="H32" s="12" t="inlineStr">
+        <is>
+          <t>Sugestão gerada por IA — confirmar com nutricionista/cardiologista</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="30" customHeight="1">
       <c r="B33" s="12" t="inlineStr">
         <is>
-          <t>Suco natural sem açúcar</t>
+          <t>Café sem açúcar</t>
         </is>
       </c>
       <c r="C33" s="13" t="inlineStr"/>
       <c r="D33" s="13" t="inlineStr">
         <is>
-          <t>200 ml</t>
+          <t>1 xícara</t>
         </is>
       </c>
       <c r="E33" s="13" t="inlineStr">
         <is>
-          <t>3x/semana</t>
-        </is>
-      </c>
-      <c r="F33" s="15" t="inlineStr">
-        <is>
-          <t>Moderar</t>
+          <t>2x/dia</t>
+        </is>
+      </c>
+      <c r="F33" s="14" t="inlineStr">
+        <is>
+          <t>Liberado</t>
         </is>
       </c>
       <c r="G33" s="13" t="inlineStr"/>
-      <c r="H33" s="12" t="inlineStr">
-        <is>
-          <t>Preferir a fruta inteira, que tem mais fibra</t>
-        </is>
-      </c>
+      <c r="H33" s="12" t="inlineStr"/>
     </row>
     <row r="34" ht="30" customHeight="1">
       <c r="B34" s="12" t="inlineStr">
         <is>
-          <t>Suco de toranja / grapefruit</t>
+          <t>Suco natural sem açúcar</t>
         </is>
       </c>
       <c r="C34" s="13" t="inlineStr"/>
       <c r="D34" s="13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>200 ml</t>
         </is>
       </c>
       <c r="E34" s="13" t="inlineStr">
         <is>
-          <t>evitar</t>
-        </is>
-      </c>
-      <c r="F34" s="16" t="inlineStr">
-        <is>
-          <t>Evitar</t>
+          <t>3x/semana</t>
+        </is>
+      </c>
+      <c r="F34" s="15" t="inlineStr">
+        <is>
+          <t>Moderar</t>
         </is>
       </c>
       <c r="G34" s="13" t="inlineStr"/>
       <c r="H34" s="12" t="inlineStr">
         <is>
-          <t>Interage com o Ticagrelor (estudo mostrou quase o dobro do nível do remédio no sangue); a bula diz que não é esperado ser clinicamente relevante p/ a maioria, mas orienta evitar — mais seguro evitar, já que você toma 2 antiagregantes. Ver aba Fontes e Referências.</t>
+          <t>Preferir a fruta inteira, que tem mais fibra</t>
         </is>
       </c>
     </row>
     <row r="35" ht="30" customHeight="1">
       <c r="B35" s="12" t="inlineStr">
         <is>
-          <t>Bebida alcoólica</t>
+          <t>Suco de toranja / grapefruit</t>
         </is>
       </c>
       <c r="C35" s="13" t="inlineStr"/>
@@ -1958,57 +1962,57 @@
       <c r="G35" s="13" t="inlineStr"/>
       <c r="H35" s="12" t="inlineStr">
         <is>
+          <t>Interage com o Ticagrelor (estudo mostrou quase o dobro do nível do remédio no sangue); a bula diz que não é esperado ser clinicamente relevante p/ a maioria, mas orienta evitar — mais seguro evitar, já que você toma 2 antiagregantes. Ver aba Fontes e Referências.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="30" customHeight="1">
+      <c r="B36" s="12" t="inlineStr">
+        <is>
+          <t>Bebida alcoólica</t>
+        </is>
+      </c>
+      <c r="C36" s="13" t="inlineStr"/>
+      <c r="D36" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E36" s="13" t="inlineStr">
+        <is>
+          <t>evitar</t>
+        </is>
+      </c>
+      <c r="F36" s="16" t="inlineStr">
+        <is>
+          <t>Evitar</t>
+        </is>
+      </c>
+      <c r="G36" s="13" t="inlineStr"/>
+      <c r="H36" s="12" t="inlineStr">
+        <is>
           <t>Piora diretamente os triglicerídeos; soma-se ao risco de sangramento da Aspirina + Ticagrelor.</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="10" t="inlineStr">
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="10" t="inlineStr">
         <is>
           <t>Doces e Sobremesas</t>
         </is>
       </c>
-      <c r="B36" s="11" t="n"/>
-      <c r="C36" s="11" t="n"/>
-      <c r="D36" s="11" t="n"/>
-      <c r="E36" s="11" t="n"/>
-      <c r="F36" s="11" t="n"/>
-      <c r="G36" s="11" t="n"/>
-      <c r="H36" s="11" t="n"/>
-    </row>
-    <row r="37" ht="30" customHeight="1">
-      <c r="B37" s="12" t="inlineStr">
-        <is>
-          <t>Açúcar refinado</t>
-        </is>
-      </c>
-      <c r="C37" s="13" t="inlineStr"/>
-      <c r="D37" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E37" s="13" t="inlineStr">
-        <is>
-          <t>evitar</t>
-        </is>
-      </c>
-      <c r="F37" s="16" t="inlineStr">
-        <is>
-          <t>Evitar</t>
-        </is>
-      </c>
-      <c r="G37" s="13" t="inlineStr"/>
-      <c r="H37" s="12" t="inlineStr">
-        <is>
-          <t>Impacto direto nos triglicerídeos</t>
-        </is>
-      </c>
+      <c r="B37" s="11" t="n"/>
+      <c r="C37" s="11" t="n"/>
+      <c r="D37" s="11" t="n"/>
+      <c r="E37" s="11" t="n"/>
+      <c r="F37" s="11" t="n"/>
+      <c r="G37" s="11" t="n"/>
+      <c r="H37" s="11" t="n"/>
     </row>
     <row r="38" ht="30" customHeight="1">
       <c r="B38" s="12" t="inlineStr">
         <is>
-          <t>Doces industrializados</t>
+          <t>Açúcar refinado</t>
         </is>
       </c>
       <c r="C38" s="13" t="inlineStr"/>
@@ -2028,233 +2032,262 @@
         </is>
       </c>
       <c r="G38" s="13" t="inlineStr"/>
-      <c r="H38" s="12" t="inlineStr"/>
+      <c r="H38" s="12" t="inlineStr">
+        <is>
+          <t>Impacto direto nos triglicerídeos</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="30" customHeight="1">
       <c r="B39" s="12" t="inlineStr">
         <is>
-          <t>Chocolate amargo (70%+)</t>
+          <t>Doces industrializados</t>
         </is>
       </c>
       <c r="C39" s="13" t="inlineStr"/>
       <c r="D39" s="13" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E39" s="13" t="inlineStr">
+        <is>
+          <t>evitar</t>
+        </is>
+      </c>
+      <c r="F39" s="16" t="inlineStr">
+        <is>
+          <t>Evitar</t>
+        </is>
+      </c>
+      <c r="G39" s="13" t="inlineStr"/>
+      <c r="H39" s="12" t="inlineStr"/>
+    </row>
+    <row r="40" ht="30" customHeight="1">
+      <c r="B40" s="12" t="inlineStr">
+        <is>
+          <t>Chocolate amargo (70%+)</t>
+        </is>
+      </c>
+      <c r="C40" s="13" t="inlineStr"/>
+      <c r="D40" s="13" t="inlineStr">
+        <is>
           <t>10 g</t>
         </is>
       </c>
-      <c r="E39" s="13" t="inlineStr">
+      <c r="E40" s="13" t="inlineStr">
         <is>
           <t>2x/semana</t>
         </is>
       </c>
-      <c r="F39" s="15" t="inlineStr">
+      <c r="F40" s="15" t="inlineStr">
         <is>
           <t>Moderar</t>
         </is>
       </c>
-      <c r="G39" s="13" t="inlineStr"/>
-      <c r="H39" s="12" t="inlineStr">
+      <c r="G40" s="13" t="inlineStr"/>
+      <c r="H40" s="12" t="inlineStr">
         <is>
           <t>Sugestão gerada por IA — confirmar com nutricionista/cardiologista</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="20" customHeight="1">
-      <c r="A40" s="10" t="inlineStr">
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="10" t="inlineStr">
         <is>
           <t>Gorduras e Temperos</t>
         </is>
       </c>
-      <c r="B40" s="11" t="n"/>
-      <c r="C40" s="11" t="n"/>
-      <c r="D40" s="11" t="n"/>
-      <c r="E40" s="11" t="n"/>
-      <c r="F40" s="11" t="n"/>
-      <c r="G40" s="11" t="n"/>
-      <c r="H40" s="11" t="n"/>
-    </row>
-    <row r="41" ht="30" customHeight="1">
-      <c r="B41" s="12" t="inlineStr">
-        <is>
-          <t>Azeite de oliva extra virgem</t>
-        </is>
-      </c>
-      <c r="C41" s="13" t="inlineStr"/>
-      <c r="D41" s="13" t="inlineStr">
-        <is>
-          <t>1-2 colheres de sopa</t>
-        </is>
-      </c>
-      <c r="E41" s="13" t="inlineStr">
-        <is>
-          <t>1x/dia</t>
-        </is>
-      </c>
-      <c r="F41" s="14" t="inlineStr">
-        <is>
-          <t>Liberado</t>
-        </is>
-      </c>
-      <c r="G41" s="13" t="inlineStr"/>
-      <c r="H41" s="12" t="inlineStr"/>
+      <c r="B41" s="11" t="n"/>
+      <c r="C41" s="11" t="n"/>
+      <c r="D41" s="11" t="n"/>
+      <c r="E41" s="11" t="n"/>
+      <c r="F41" s="11" t="n"/>
+      <c r="G41" s="11" t="n"/>
+      <c r="H41" s="11" t="n"/>
     </row>
     <row r="42" ht="30" customHeight="1">
       <c r="B42" s="12" t="inlineStr">
         <is>
-          <t>Manteiga</t>
+          <t>Azeite de oliva extra virgem</t>
         </is>
       </c>
       <c r="C42" s="13" t="inlineStr"/>
       <c r="D42" s="13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1-2 colheres de sopa</t>
         </is>
       </c>
       <c r="E42" s="13" t="inlineStr">
         <is>
-          <t>evitar</t>
-        </is>
-      </c>
-      <c r="F42" s="16" t="inlineStr">
-        <is>
-          <t>Evitar</t>
+          <t>1x/dia</t>
+        </is>
+      </c>
+      <c r="F42" s="14" t="inlineStr">
+        <is>
+          <t>Liberado</t>
         </is>
       </c>
       <c r="G42" s="13" t="inlineStr"/>
-      <c r="H42" s="12" t="inlineStr">
-        <is>
-          <t>Preferir azeite</t>
-        </is>
-      </c>
+      <c r="H42" s="12" t="inlineStr"/>
     </row>
     <row r="43" ht="30" customHeight="1">
       <c r="B43" s="12" t="inlineStr">
         <is>
-          <t>Sal</t>
+          <t>Manteiga</t>
         </is>
       </c>
       <c r="C43" s="13" t="inlineStr"/>
       <c r="D43" s="13" t="inlineStr">
         <is>
-          <t>&lt; 5 g no total</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E43" s="13" t="inlineStr">
         <is>
-          <t>todos os dias</t>
-        </is>
-      </c>
-      <c r="F43" s="15" t="inlineStr">
-        <is>
-          <t>Moderar</t>
+          <t>evitar</t>
+        </is>
+      </c>
+      <c r="F43" s="16" t="inlineStr">
+        <is>
+          <t>Evitar</t>
         </is>
       </c>
       <c r="G43" s="13" t="inlineStr"/>
       <c r="H43" s="12" t="inlineStr">
         <is>
-          <t>Somar sal de cozinha + industrializados</t>
+          <t>Preferir azeite</t>
         </is>
       </c>
     </row>
     <row r="44" ht="30" customHeight="1">
       <c r="B44" s="12" t="inlineStr">
         <is>
-          <t>Sal light / substituto de sal (cloreto de potássio)</t>
+          <t>Sal</t>
         </is>
       </c>
       <c r="C44" s="13" t="inlineStr"/>
       <c r="D44" s="13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>&lt; 5 g no total</t>
         </is>
       </c>
       <c r="E44" s="13" t="inlineStr">
         <is>
-          <t>evitar</t>
-        </is>
-      </c>
-      <c r="F44" s="16" t="inlineStr">
-        <is>
-          <t>Evitar</t>
+          <t>todos os dias</t>
+        </is>
+      </c>
+      <c r="F44" s="15" t="inlineStr">
+        <is>
+          <t>Moderar</t>
         </is>
       </c>
       <c r="G44" s="13" t="inlineStr"/>
       <c r="H44" s="12" t="inlineStr">
         <is>
-          <t>Enalapril já tende a elevar o potássio; combinado com esse produto o risco de hipercalemia aumenta, ainda mais com a função renal pendente.</t>
+          <t>Somar sal de cozinha + industrializados</t>
         </is>
       </c>
     </row>
     <row r="45" ht="30" customHeight="1">
       <c r="B45" s="12" t="inlineStr">
         <is>
-          <t>Ervas e temperos naturais</t>
+          <t>Sal light / substituto de sal (cloreto de potássio)</t>
         </is>
       </c>
       <c r="C45" s="13" t="inlineStr"/>
       <c r="D45" s="13" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E45" s="13" t="inlineStr">
+        <is>
+          <t>evitar</t>
+        </is>
+      </c>
+      <c r="F45" s="16" t="inlineStr">
+        <is>
+          <t>Evitar</t>
+        </is>
+      </c>
+      <c r="G45" s="13" t="inlineStr"/>
+      <c r="H45" s="12" t="inlineStr">
+        <is>
+          <t>Enalapril já tende a elevar o potássio; combinado com esse produto o risco de hipercalemia aumenta, ainda mais com a função renal pendente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="30" customHeight="1">
+      <c r="B46" s="12" t="inlineStr">
+        <is>
+          <t>Ervas e temperos naturais</t>
+        </is>
+      </c>
+      <c r="C46" s="13" t="inlineStr"/>
+      <c r="D46" s="13" t="inlineStr">
+        <is>
           <t>à vontade</t>
         </is>
       </c>
-      <c r="E45" s="13" t="inlineStr">
+      <c r="E46" s="13" t="inlineStr">
         <is>
           <t>todos os dias</t>
         </is>
       </c>
-      <c r="F45" s="14" t="inlineStr">
+      <c r="F46" s="14" t="inlineStr">
         <is>
           <t>Liberado</t>
         </is>
       </c>
-      <c r="G45" s="13" t="inlineStr"/>
-      <c r="H45" s="12" t="inlineStr"/>
-    </row>
-    <row r="46" ht="20" customHeight="1">
-      <c r="A46" s="10" t="inlineStr">
+      <c r="G46" s="13" t="inlineStr"/>
+      <c r="H46" s="12" t="inlineStr"/>
+    </row>
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="10" t="inlineStr">
         <is>
           <t>Vegetais e Verduras</t>
         </is>
       </c>
-      <c r="B46" s="11" t="n"/>
-      <c r="C46" s="11" t="n"/>
-      <c r="D46" s="11" t="n"/>
-      <c r="E46" s="11" t="n"/>
-      <c r="F46" s="11" t="n"/>
-      <c r="G46" s="11" t="n"/>
-      <c r="H46" s="11" t="n"/>
-    </row>
-    <row r="47" ht="30" customHeight="1">
-      <c r="B47" s="12" t="inlineStr">
+      <c r="B47" s="11" t="n"/>
+      <c r="C47" s="11" t="n"/>
+      <c r="D47" s="11" t="n"/>
+      <c r="E47" s="11" t="n"/>
+      <c r="F47" s="11" t="n"/>
+      <c r="G47" s="11" t="n"/>
+      <c r="H47" s="11" t="n"/>
+    </row>
+    <row r="48" ht="30" customHeight="1">
+      <c r="B48" s="12" t="inlineStr">
         <is>
           <t>Vegetais e verduras em geral</t>
         </is>
       </c>
-      <c r="C47" s="13" t="inlineStr"/>
-      <c r="D47" s="13" t="inlineStr">
+      <c r="C48" s="13" t="inlineStr"/>
+      <c r="D48" s="13" t="inlineStr">
         <is>
           <t>à vontade</t>
         </is>
       </c>
-      <c r="E47" s="13" t="inlineStr">
+      <c r="E48" s="13" t="inlineStr">
         <is>
           <t>todos os dias</t>
         </is>
       </c>
-      <c r="F47" s="14" t="inlineStr">
+      <c r="F48" s="14" t="inlineStr">
         <is>
           <t>Liberado</t>
         </is>
       </c>
-      <c r="G47" s="13" t="inlineStr"/>
-      <c r="H47" s="12" t="inlineStr">
+      <c r="G48" s="13" t="inlineStr"/>
+      <c r="H48" s="12" t="inlineStr">
         <is>
           <t>Se entrar anticoagulante na medicação, revisar consumo de verde-escuros ricos em vitamina K</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="40" customHeight="1">
-      <c r="A49" s="17" t="inlineStr">
+    <row r="50" ht="40" customHeight="1">
+      <c r="A50" s="17" t="inlineStr">
         <is>
           <t>Lista com os alimentos acrescentados até agora — não é uma lista completa. Use a skill 'adicionar-alimento' (ex.: "adicione sucrilhos") para ir acrescentando novos itens aos poucos. A coluna 'Gostoso' é sua — escolha do menu suspenso; o valor é preservado mesmo quando a planilha é regenerada por um alimento novo.</t>
         </is>
@@ -2262,20 +2295,20 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A50:H50"/>
     <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A29:H29"/>
+    <mergeCell ref="A30:H30"/>
     <mergeCell ref="G2:H2"/>
-    <mergeCell ref="A16:H16"/>
-    <mergeCell ref="A36:H36"/>
+    <mergeCell ref="A41:H41"/>
     <mergeCell ref="A11:H11"/>
-    <mergeCell ref="A49:H49"/>
+    <mergeCell ref="A37:H37"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A46:H46"/>
-    <mergeCell ref="A22:H22"/>
-    <mergeCell ref="A40:H40"/>
+    <mergeCell ref="A23:H23"/>
+    <mergeCell ref="A47:H47"/>
+    <mergeCell ref="A17:H17"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="G5 G6 G7 G8 G9 G10 G12 G13 G14 G15 G17 G18 G19 G20 G21 G23 G24 G25 G26 G27 G28 G30 G31 G32 G33 G34 G35 G37 G38 G39 G41 G42 G43 G44 G45 G47" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Fora da lista" error="Escolha uma opção do menu (ou deixe em branco)." type="list" errorStyle="warning">
+    <dataValidation sqref="G5 G6 G7 G8 G9 G10 G12 G13 G14 G15 G16 G18 G19 G20 G21 G22 G24 G25 G26 G27 G28 G29 G31 G32 G33 G34 G35 G36 G38 G39 G40 G42 G43 G44 G45 G46 G48" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Fora da lista" error="Escolha uma opção do menu (ou deixe em branco)." type="list" errorStyle="warning">
       <formula1>"Ruim,Normal,Bom,Muito bom"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3964,7 +3997,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U37"/>
+  <dimension ref="A1:U38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4442,7 +4475,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Leite desnatado</t>
+          <t>Pão francês integral (multigrãos)</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -4516,7 +4549,7 @@
       <c r="J7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Ovo</t>
+          <t>Pão francês integral (multigrãos)</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -4526,7 +4559,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Queijo branco frescal</t>
+          <t>Leite desnatado</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -4596,7 +4629,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Leite desnatado</t>
+          <t>Ovo</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -4606,7 +4639,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Queijo frescal light</t>
+          <t>Queijo branco frescal</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -4680,7 +4713,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Queijo branco frescal</t>
+          <t>Leite desnatado</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -4690,7 +4723,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Iogurte natural (desnatado, sem açúcar)</t>
+          <t>Queijo frescal light</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -4760,7 +4793,7 @@
       <c r="J10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Queijo frescal light</t>
+          <t>Queijo branco frescal</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4770,7 +4803,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Água</t>
+          <t>Iogurte natural (desnatado, sem açúcar)</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -4830,7 +4863,7 @@
       <c r="J11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Iogurte natural (desnatado, sem açúcar)</t>
+          <t>Queijo frescal light</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4840,7 +4873,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Café sem açúcar</t>
+          <t>Água</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -4862,12 +4895,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Peixe</t>
+          <t>Pão francês integral (multigrãos)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Proteínas</t>
+          <t>Grãos e Cereais</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -4877,34 +4910,34 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>150 g</t>
+          <t>1 unidade (~67 g)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>3x/semana</t>
+          <t>1x/dia</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fonte de ômega-3</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+          <t>Rótulo real (porção 50 g/meia unidade): 120 kcal, 208 mg de sódio, 1,6 g de fibras, sem açúcar adicionado. Com centeio, gergelim e linhaça — boa fonte de fibra, mas sódio moderado como a maioria dos pães; contém glúten.</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Água</t>
+          <t>Iogurte natural (desnatado, sem açúcar)</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -4914,7 +4947,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Vegetais e verduras em geral</t>
+          <t>Café sem açúcar</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -4936,7 +4969,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Frango sem pele</t>
+          <t>Peixe</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -4956,10 +4989,14 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>quase todo dia</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
+          <t>3x/semana</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Fonte de ômega-3</t>
+        </is>
+      </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
@@ -4974,7 +5011,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Café sem açúcar</t>
+          <t>Água</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -4984,7 +5021,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Uva</t>
+          <t>Vegetais e verduras em geral</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -5006,7 +5043,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Carne vermelha magra</t>
+          <t>Frango sem pele</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -5016,7 +5053,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Moderar</t>
+          <t>Liberado</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -5026,14 +5063,10 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1x/semana</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Preferir cortes magros</t>
-        </is>
-      </c>
+          <t>quase todo dia</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
@@ -5048,7 +5081,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Vegetais e verduras em geral</t>
+          <t>Café sem açúcar</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -5058,7 +5091,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Manga</t>
+          <t>Uva</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -5080,7 +5113,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Ovo</t>
+          <t>Carne vermelha magra</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -5090,25 +5123,25 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Liberado</t>
+          <t>Moderar</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1 unidade</t>
+          <t>150 g</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>até 5x/semana</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+          <t>1x/semana</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Preferir cortes magros</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
           <t>X</t>
@@ -5122,7 +5155,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Uva</t>
+          <t>Vegetais e verduras em geral</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -5132,7 +5165,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Mussarela</t>
+          <t>Manga</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -5154,7 +5187,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Feijão / leguminosas</t>
+          <t>Ovo</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -5169,16 +5202,20 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1 concha</t>
+          <t>1 unidade</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1x/dia</t>
+          <t>até 5x/semana</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>X</t>
@@ -5192,7 +5229,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Manga</t>
+          <t>Uva</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -5202,7 +5239,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Requeijão</t>
+          <t>Mussarela</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -5224,12 +5261,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Leite desnatado</t>
+          <t>Feijão / leguminosas</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Laticínios</t>
+          <t>Proteínas</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -5239,7 +5276,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>200 ml</t>
+          <t>1 concha</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -5248,21 +5285,21 @@
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Mussarela</t>
+          <t>Manga</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -5272,7 +5309,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Refrigerante zero</t>
+          <t>Requeijão</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -5294,7 +5331,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Queijo branco frescal</t>
+          <t>Leite desnatado</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -5309,19 +5346,15 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>30 g</t>
+          <t>200 ml</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>3x/semana</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Tipo fresco (ex.: Minas frescal), sem cura/salga pesada — bem menos sódio e gordura que queijos curados. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
-        </is>
-      </c>
+          <t>1x/dia</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
           <t>X</t>
@@ -5336,12 +5369,12 @@
       <c r="J18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Requeijão</t>
+          <t>Mussarela</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Suco natural sem açúcar</t>
+          <t>Refrigerante zero</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -5358,7 +5391,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Queijo frescal light</t>
+          <t>Queijo branco frescal</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5373,7 +5406,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>30 g (1 fatia)</t>
+          <t>30 g</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -5383,7 +5416,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rótulo real: 41 kcal e 105 mg de sódio por porção (bem abaixo de queijos comuns), 1,5 g de gordura saturada, sem açúcar adicionado. Contém lactose; sem glúten; pode conter soja.</t>
+          <t>Tipo fresco (ex.: Minas frescal), sem cura/salga pesada — bem menos sódio e gordura que queijos curados. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -5400,12 +5433,12 @@
       <c r="J19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
+          <t>Requeijão</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
           <t>Suco natural sem açúcar</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>Chocolate amargo (70%+)</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -5422,7 +5455,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Mussarela</t>
+          <t>Queijo frescal light</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5432,22 +5465,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Moderar</t>
+          <t>Liberado</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>30 g</t>
+          <t>30 g (1 fatia)</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2x/semana</t>
+          <t>3x/semana</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mais gordura saturada e sódio que o queijo branco frescal; prefira o frescal no dia a dia. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
+          <t>Rótulo real: 41 kcal e 105 mg de sódio por porção (bem abaixo de queijos comuns), 1,5 g de gordura saturada, sem açúcar adicionado. Contém lactose; sem glúten; pode conter soja.</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -5464,12 +5497,12 @@
       <c r="J20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Toranja / grapefruit</t>
+          <t>Suco natural sem açúcar</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Toranja / grapefruit</t>
+          <t>Chocolate amargo (70%+)</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
@@ -5486,7 +5519,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Iogurte natural (desnatado, sem açúcar)</t>
+          <t>Mussarela</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5496,22 +5529,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Liberado</t>
+          <t>Moderar</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1 unidade</t>
+          <t>30 g</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1x/dia</t>
+          <t>2x/semana</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Prefira sempre a versão sem açúcar adicionado</t>
+          <t>Mais gordura saturada e sódio que o queijo branco frescal; prefira o frescal no dia a dia. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -5528,12 +5561,12 @@
       <c r="J21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Suco de toranja / grapefruit</t>
+          <t>Toranja / grapefruit</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Suco de toranja / grapefruit</t>
+          <t>Toranja / grapefruit</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
@@ -5550,7 +5583,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Requeijão</t>
+          <t>Iogurte natural (desnatado, sem açúcar)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5560,22 +5593,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Moderar</t>
+          <t>Liberado</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1 colher de sopa (≈15 g)</t>
+          <t>1 unidade</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2x/semana</t>
+          <t>1x/dia</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rico em gordura saturada e sódio; prefira a versão light. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
+          <t>Prefira sempre a versão sem açúcar adicionado</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -5592,12 +5625,12 @@
       <c r="J22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Açúcar refinado</t>
+          <t>Suco de toranja / grapefruit</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Açúcar refinado</t>
+          <t>Suco de toranja / grapefruit</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
@@ -5614,58 +5647,54 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Água</t>
+          <t>Requeijão</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Bebidas</t>
+          <t>Laticínios</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Liberado</t>
+          <t>Moderar</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>à vontade</t>
+          <t>1 colher de sopa (≈15 g)</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>todos os dias</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr"/>
+          <t>2x/semana</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Rico em gordura saturada e sódio; prefira a versão light. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
+        </is>
+      </c>
       <c r="G23" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="J23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Manteiga</t>
+          <t>Açúcar refinado</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Doces industrializados</t>
+          <t>Açúcar refinado</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
@@ -5682,7 +5711,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Refrigerante zero</t>
+          <t>Água</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5692,25 +5721,25 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Moderar</t>
+          <t>Liberado</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>200 ml</t>
+          <t>à vontade</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1x/dia</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Sugestão gerada por IA — confirmar com nutricionista/cardiologista</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr"/>
+          <t>todos os dias</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="H24" t="inlineStr">
         <is>
           <t>X</t>
@@ -5724,6 +5753,16 @@
       <c r="J24" t="inlineStr">
         <is>
           <t>X</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Manteiga</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Doces industrializados</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
@@ -5740,7 +5779,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Café sem açúcar</t>
+          <t>Refrigerante zero</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5750,32 +5789,40 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Liberado</t>
+          <t>Moderar</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1 xícara</t>
+          <t>200 ml</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2x/dia</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr"/>
+          <t>1x/dia</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Sugestão gerada por IA — confirmar com nutricionista/cardiologista</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="I25" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="Q25" t="inlineStr">
         <is>
           <t>Doces e Sobremesas|Jantar</t>
@@ -5790,7 +5837,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Suco natural sem açúcar</t>
+          <t>Café sem açúcar</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5800,24 +5847,20 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Moderar</t>
+          <t>Liberado</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>200 ml</t>
+          <t>1 xícara</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>3x/semana</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Preferir a fruta inteira, que tem mais fibra</t>
-        </is>
-      </c>
+          <t>2x/dia</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
           <t>X</t>
@@ -5844,7 +5887,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Suco de toranja / grapefruit</t>
+          <t>Suco natural sem açúcar</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5854,22 +5897,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Evitar</t>
+          <t>Moderar</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>200 ml</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>evitar</t>
+          <t>3x/semana</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Interage com o Ticagrelor (estudo mostrou quase o dobro do nível do remédio no sangue); a bula diz que não é esperado ser clinicamente relevante p/ a maioria, mas orienta evitar — mais seguro evitar, já que você toma 2 antiagregantes. Ver aba Fontes e Referências.</t>
+          <t>Preferir a fruta inteira, que tem mais fibra</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -5898,7 +5941,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Bebida alcoólica</t>
+          <t>Suco de toranja / grapefruit</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5923,31 +5966,31 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Piora diretamente os triglicerídeos; soma-se ao risco de sangramento da Aspirina + Ticagrelor.</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+          <t>Interage com o Ticagrelor (estudo mostrou quase o dobro do nível do remédio no sangue); a bula diz que não é esperado ser clinicamente relevante p/ a maioria, mas orienta evitar — mais seguro evitar, já que você toma 2 antiagregantes. Ver aba Fontes e Referências.</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Açúcar refinado</t>
+          <t>Bebida alcoólica</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Doces e Sobremesas</t>
+          <t>Bebidas</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -5967,24 +6010,16 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Impacto direto nos triglicerídeos</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+          <t>Piora diretamente os triglicerídeos; soma-se ao risco de sangramento da Aspirina + Ticagrelor.</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
           <t>X</t>
@@ -5994,7 +6029,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Doces industrializados</t>
+          <t>Açúcar refinado</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -6017,20 +6052,36 @@
           <t>evitar</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Impacto direto nos triglicerídeos</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Chocolate amargo (70%+)</t>
+          <t>Doces industrializados</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -6040,24 +6091,20 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Moderar</t>
+          <t>Evitar</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>10 g</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2x/semana</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Sugestão gerada por IA — confirmar com nutricionista/cardiologista</t>
-        </is>
-      </c>
+          <t>evitar</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
@@ -6070,47 +6117,47 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Azeite de oliva extra virgem</t>
+          <t>Chocolate amargo (70%+)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Gorduras e Temperos</t>
+          <t>Doces e Sobremesas</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Liberado</t>
+          <t>Moderar</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1-2 colheres de sopa</t>
+          <t>10 g</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1x/dia</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr"/>
+          <t>2x/semana</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Sugestão gerada por IA — confirmar com nutricionista/cardiologista</t>
+        </is>
+      </c>
       <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Manteiga</t>
+          <t>Azeite de oliva extra virgem</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -6120,37 +6167,37 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Evitar</t>
+          <t>Liberado</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1-2 colheres de sopa</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>evitar</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Preferir azeite</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr"/>
+          <t>1x/dia</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sal</t>
+          <t>Manteiga</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -6160,41 +6207,37 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Moderar</t>
+          <t>Evitar</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>&lt; 5 g no total</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>todos os dias</t>
+          <t>evitar</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Somar sal de cozinha + industrializados</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+          <t>Preferir azeite</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="J34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sal light / substituto de sal (cloreto de potássio)</t>
+          <t>Sal</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -6204,22 +6247,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Evitar</t>
+          <t>Moderar</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>&lt; 5 g no total</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>evitar</t>
+          <t>todos os dias</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Enalapril já tende a elevar o potássio; combinado com esse produto o risco de hipercalemia aumenta, ainda mais com a função renal pendente.</t>
+          <t>Somar sal de cozinha + industrializados</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
@@ -6238,7 +6281,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Ervas e temperos naturais</t>
+          <t>Sal light / substituto de sal (cloreto de potássio)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -6248,20 +6291,24 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Liberado</t>
+          <t>Evitar</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>à vontade</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>todos os dias</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr"/>
+          <t>evitar</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Enalapril já tende a elevar o potássio; combinado com esse produto o risco de hipercalemia aumenta, ainda mais com a função renal pendente.</t>
+        </is>
+      </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr">
         <is>
@@ -6278,50 +6325,90 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>Ervas e temperos naturais</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Gorduras e Temperos</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Liberado</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>à vontade</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>todos os dias</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
           <t>Vegetais e verduras em geral</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>Vegetais e Verduras</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>Liberado</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>à vontade</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>todos os dias</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>Se entrar anticoagulante na medicação, revisar consumo de verde-escuros ricos em vitamina K</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
         <is>
           <t>X</t>
         </is>

--- a/planilha/plano-alimentar-pos-infarto.xlsx
+++ b/planilha/plano-alimentar-pos-infarto.xlsx
@@ -719,7 +719,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="46" customHeight="1">
+    <row r="3" ht="36" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Perfil de risco atual</t>
@@ -731,7 +731,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="46" customHeight="1">
+    <row r="4" ht="30" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Reduzir</t>
@@ -743,7 +743,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="46" customHeight="1">
+    <row r="5" ht="30" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Reduzir</t>
@@ -755,7 +755,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="46" customHeight="1">
+    <row r="6" ht="30" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
           <t>Reduzir</t>
@@ -767,7 +767,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="46" customHeight="1">
+    <row r="7" ht="30" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
           <t>Reduzir</t>
@@ -779,7 +779,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="46" customHeight="1">
+    <row r="8" ht="30" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
           <t>Priorizar</t>
@@ -791,7 +791,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="46" customHeight="1">
+    <row r="9" ht="30" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
           <t>Priorizar</t>
@@ -803,7 +803,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="46" customHeight="1">
+    <row r="10" ht="30" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
           <t>Priorizar</t>
@@ -815,7 +815,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="46" customHeight="1">
+    <row r="11" ht="36" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
           <t>Atenção especial — triglicerídeos</t>
@@ -827,7 +827,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="46" customHeight="1">
+    <row r="12" ht="64" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
           <t>Atenção especial — LDL</t>
@@ -839,7 +839,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="46" customHeight="1">
+    <row r="13" ht="78" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
           <t>Aviso pendente — função renal</t>
@@ -851,7 +851,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="46" customHeight="1">
+    <row r="14" ht="50" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
         <is>
           <t>Medicações em uso (receita 03/09/2026)</t>
@@ -863,7 +863,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="46" customHeight="1">
+    <row r="15" ht="64" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
         <is>
           <t>Interação medicamentosa — Ticagrelor</t>
@@ -875,7 +875,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="46" customHeight="1">
+    <row r="16" ht="64" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
         <is>
           <t>Interação medicamentosa — Enalapril</t>
@@ -887,7 +887,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="46" customHeight="1">
+    <row r="17" ht="36" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
         <is>
           <t>Interação medicamentosa — Aspirina + Ticagrelor</t>
@@ -899,7 +899,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="46" customHeight="1">
+    <row r="18" ht="50" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
         <is>
           <t>Interação medicamentosa — Rosucor (estatina)</t>
@@ -911,7 +911,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="46" customHeight="1">
+    <row r="19" ht="50" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
           <t>Reabilitação cardíaca</t>
@@ -923,7 +923,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="46" customHeight="1">
+    <row r="20" ht="36" customHeight="1">
       <c r="A20" s="3" t="inlineStr">
         <is>
           <t>Leitura de rótulos</t>
@@ -975,7 +975,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="60" customHeight="1">
+    <row r="3" ht="36" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Modelo de prato</t>
@@ -987,7 +987,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="60" customHeight="1">
+    <row r="4" ht="36" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>O que pedir</t>
@@ -999,7 +999,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
+    <row r="5" ht="36" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
           <t>O que evitar</t>
@@ -1011,7 +1011,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="60" customHeight="1">
+    <row r="6" ht="36" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
           <t>Perguntas úteis ao garçom</t>
@@ -1023,7 +1023,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="60" customHeight="1">
+    <row r="7" ht="36" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
           <t>Exemplos de pratos que funcionam</t>
@@ -1035,7 +1035,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="60" customHeight="1">
+    <row r="8" ht="36" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
           <t>Em festas/eventos</t>
@@ -1061,7 +1061,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H50"/>
+  <dimension ref="A1:H51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1296,7 +1296,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="30" customHeight="1">
+    <row r="10" ht="64" customHeight="1">
       <c r="B10" s="12" t="inlineStr">
         <is>
           <t>Toranja / grapefruit</t>
@@ -1447,7 +1447,7 @@
       <c r="G15" s="13" t="inlineStr"/>
       <c r="H15" s="12" t="inlineStr"/>
     </row>
-    <row r="16" ht="30" customHeight="1">
+    <row r="16" ht="64" customHeight="1">
       <c r="B16" s="12" t="inlineStr">
         <is>
           <t>Pão francês integral (multigrãos)</t>
@@ -1666,7 +1666,7 @@
       <c r="G24" s="13" t="inlineStr"/>
       <c r="H24" s="12" t="inlineStr"/>
     </row>
-    <row r="25" ht="30" customHeight="1">
+    <row r="25" ht="50" customHeight="1">
       <c r="B25" s="12" t="inlineStr">
         <is>
           <t>Queijo branco frescal</t>
@@ -1695,7 +1695,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="30" customHeight="1">
+    <row r="26" ht="50" customHeight="1">
       <c r="B26" s="12" t="inlineStr">
         <is>
           <t>Queijo frescal light</t>
@@ -1728,7 +1728,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="30" customHeight="1">
+    <row r="27" ht="50" customHeight="1">
       <c r="B27" s="12" t="inlineStr">
         <is>
           <t>Mussarela</t>
@@ -1786,190 +1786,194 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="30" customHeight="1">
+    <row r="29" ht="50" customHeight="1">
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>Requeijão</t>
-        </is>
-      </c>
-      <c r="C29" s="13" t="inlineStr"/>
+          <t>Iogurte grego zero</t>
+        </is>
+      </c>
+      <c r="C29" s="13" t="inlineStr">
+        <is>
+          <t>Vigor</t>
+        </is>
+      </c>
       <c r="D29" s="13" t="inlineStr">
         <is>
-          <t>1 colher de sopa (≈15 g)</t>
+          <t>90 g (1 pote)</t>
         </is>
       </c>
       <c r="E29" s="13" t="inlineStr">
         <is>
-          <t>2x/semana</t>
-        </is>
-      </c>
-      <c r="F29" s="15" t="inlineStr">
-        <is>
-          <t>Moderar</t>
+          <t>1x/dia</t>
+        </is>
+      </c>
+      <c r="F29" s="14" t="inlineStr">
+        <is>
+          <t>Liberado</t>
         </is>
       </c>
       <c r="G29" s="13" t="inlineStr"/>
       <c r="H29" s="12" t="inlineStr">
         <is>
+          <t>Rótulo real: 50 kcal, 6,8 g de proteína (bem mais que iogurte comum), 0,2 g de gordura, 51 mg de sódio, zero adição de açúcar/gordura, sem lactose. Contém edulcorantes (sucralose e ciclamato).</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="36" customHeight="1">
+      <c r="B30" s="12" t="inlineStr">
+        <is>
+          <t>Requeijão</t>
+        </is>
+      </c>
+      <c r="C30" s="13" t="inlineStr"/>
+      <c r="D30" s="13" t="inlineStr">
+        <is>
+          <t>1 colher de sopa (≈15 g)</t>
+        </is>
+      </c>
+      <c r="E30" s="13" t="inlineStr">
+        <is>
+          <t>2x/semana</t>
+        </is>
+      </c>
+      <c r="F30" s="15" t="inlineStr">
+        <is>
+          <t>Moderar</t>
+        </is>
+      </c>
+      <c r="G30" s="13" t="inlineStr"/>
+      <c r="H30" s="12" t="inlineStr">
+        <is>
           <t>Rico em gordura saturada e sódio; prefira a versão light. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="10" t="inlineStr">
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="10" t="inlineStr">
         <is>
           <t>Bebidas</t>
         </is>
       </c>
-      <c r="B30" s="11" t="n"/>
-      <c r="C30" s="11" t="n"/>
-      <c r="D30" s="11" t="n"/>
-      <c r="E30" s="11" t="n"/>
-      <c r="F30" s="11" t="n"/>
-      <c r="G30" s="11" t="n"/>
-      <c r="H30" s="11" t="n"/>
-    </row>
-    <row r="31" ht="30" customHeight="1">
-      <c r="B31" s="12" t="inlineStr">
-        <is>
-          <t>Água</t>
-        </is>
-      </c>
-      <c r="C31" s="13" t="inlineStr"/>
-      <c r="D31" s="13" t="inlineStr">
-        <is>
-          <t>à vontade</t>
-        </is>
-      </c>
-      <c r="E31" s="13" t="inlineStr">
-        <is>
-          <t>todos os dias</t>
-        </is>
-      </c>
-      <c r="F31" s="14" t="inlineStr">
-        <is>
-          <t>Liberado</t>
-        </is>
-      </c>
-      <c r="G31" s="13" t="inlineStr"/>
-      <c r="H31" s="12" t="inlineStr"/>
+      <c r="B31" s="11" t="n"/>
+      <c r="C31" s="11" t="n"/>
+      <c r="D31" s="11" t="n"/>
+      <c r="E31" s="11" t="n"/>
+      <c r="F31" s="11" t="n"/>
+      <c r="G31" s="11" t="n"/>
+      <c r="H31" s="11" t="n"/>
     </row>
     <row r="32" ht="30" customHeight="1">
       <c r="B32" s="12" t="inlineStr">
         <is>
-          <t>Refrigerante zero</t>
+          <t>Água</t>
         </is>
       </c>
       <c r="C32" s="13" t="inlineStr"/>
       <c r="D32" s="13" t="inlineStr">
         <is>
-          <t>200 ml</t>
+          <t>à vontade</t>
         </is>
       </c>
       <c r="E32" s="13" t="inlineStr">
         <is>
-          <t>1x/dia</t>
-        </is>
-      </c>
-      <c r="F32" s="15" t="inlineStr">
-        <is>
-          <t>Moderar</t>
+          <t>todos os dias</t>
+        </is>
+      </c>
+      <c r="F32" s="14" t="inlineStr">
+        <is>
+          <t>Liberado</t>
         </is>
       </c>
       <c r="G32" s="13" t="inlineStr"/>
-      <c r="H32" s="12" t="inlineStr">
-        <is>
-          <t>Sugestão gerada por IA — confirmar com nutricionista/cardiologista</t>
-        </is>
-      </c>
+      <c r="H32" s="12" t="inlineStr"/>
     </row>
     <row r="33" ht="30" customHeight="1">
       <c r="B33" s="12" t="inlineStr">
         <is>
-          <t>Café sem açúcar</t>
+          <t>Refrigerante zero</t>
         </is>
       </c>
       <c r="C33" s="13" t="inlineStr"/>
       <c r="D33" s="13" t="inlineStr">
         <is>
-          <t>1 xícara</t>
+          <t>200 ml</t>
         </is>
       </c>
       <c r="E33" s="13" t="inlineStr">
         <is>
-          <t>2x/dia</t>
-        </is>
-      </c>
-      <c r="F33" s="14" t="inlineStr">
-        <is>
-          <t>Liberado</t>
+          <t>1x/dia</t>
+        </is>
+      </c>
+      <c r="F33" s="15" t="inlineStr">
+        <is>
+          <t>Moderar</t>
         </is>
       </c>
       <c r="G33" s="13" t="inlineStr"/>
-      <c r="H33" s="12" t="inlineStr"/>
+      <c r="H33" s="12" t="inlineStr">
+        <is>
+          <t>Sugestão gerada por IA — confirmar com nutricionista/cardiologista</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="30" customHeight="1">
       <c r="B34" s="12" t="inlineStr">
         <is>
-          <t>Suco natural sem açúcar</t>
+          <t>Café sem açúcar</t>
         </is>
       </c>
       <c r="C34" s="13" t="inlineStr"/>
       <c r="D34" s="13" t="inlineStr">
         <is>
-          <t>200 ml</t>
+          <t>1 xícara</t>
         </is>
       </c>
       <c r="E34" s="13" t="inlineStr">
         <is>
-          <t>3x/semana</t>
-        </is>
-      </c>
-      <c r="F34" s="15" t="inlineStr">
-        <is>
-          <t>Moderar</t>
+          <t>2x/dia</t>
+        </is>
+      </c>
+      <c r="F34" s="14" t="inlineStr">
+        <is>
+          <t>Liberado</t>
         </is>
       </c>
       <c r="G34" s="13" t="inlineStr"/>
-      <c r="H34" s="12" t="inlineStr">
-        <is>
-          <t>Preferir a fruta inteira, que tem mais fibra</t>
-        </is>
-      </c>
+      <c r="H34" s="12" t="inlineStr"/>
     </row>
     <row r="35" ht="30" customHeight="1">
       <c r="B35" s="12" t="inlineStr">
         <is>
-          <t>Suco de toranja / grapefruit</t>
+          <t>Suco natural sem açúcar</t>
         </is>
       </c>
       <c r="C35" s="13" t="inlineStr"/>
       <c r="D35" s="13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>200 ml</t>
         </is>
       </c>
       <c r="E35" s="13" t="inlineStr">
         <is>
-          <t>evitar</t>
-        </is>
-      </c>
-      <c r="F35" s="16" t="inlineStr">
-        <is>
-          <t>Evitar</t>
+          <t>3x/semana</t>
+        </is>
+      </c>
+      <c r="F35" s="15" t="inlineStr">
+        <is>
+          <t>Moderar</t>
         </is>
       </c>
       <c r="G35" s="13" t="inlineStr"/>
       <c r="H35" s="12" t="inlineStr">
         <is>
-          <t>Interage com o Ticagrelor (estudo mostrou quase o dobro do nível do remédio no sangue); a bula diz que não é esperado ser clinicamente relevante p/ a maioria, mas orienta evitar — mais seguro evitar, já que você toma 2 antiagregantes. Ver aba Fontes e Referências.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="30" customHeight="1">
+          <t>Preferir a fruta inteira, que tem mais fibra</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="64" customHeight="1">
       <c r="B36" s="12" t="inlineStr">
         <is>
-          <t>Bebida alcoólica</t>
+          <t>Suco de toranja / grapefruit</t>
         </is>
       </c>
       <c r="C36" s="13" t="inlineStr"/>
@@ -1991,57 +1995,57 @@
       <c r="G36" s="13" t="inlineStr"/>
       <c r="H36" s="12" t="inlineStr">
         <is>
+          <t>Interage com o Ticagrelor (estudo mostrou quase o dobro do nível do remédio no sangue); a bula diz que não é esperado ser clinicamente relevante p/ a maioria, mas orienta evitar — mais seguro evitar, já que você toma 2 antiagregantes. Ver aba Fontes e Referências.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="36" customHeight="1">
+      <c r="B37" s="12" t="inlineStr">
+        <is>
+          <t>Bebida alcoólica</t>
+        </is>
+      </c>
+      <c r="C37" s="13" t="inlineStr"/>
+      <c r="D37" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E37" s="13" t="inlineStr">
+        <is>
+          <t>evitar</t>
+        </is>
+      </c>
+      <c r="F37" s="16" t="inlineStr">
+        <is>
+          <t>Evitar</t>
+        </is>
+      </c>
+      <c r="G37" s="13" t="inlineStr"/>
+      <c r="H37" s="12" t="inlineStr">
+        <is>
           <t>Piora diretamente os triglicerídeos; soma-se ao risco de sangramento da Aspirina + Ticagrelor.</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="20" customHeight="1">
-      <c r="A37" s="10" t="inlineStr">
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="10" t="inlineStr">
         <is>
           <t>Doces e Sobremesas</t>
         </is>
       </c>
-      <c r="B37" s="11" t="n"/>
-      <c r="C37" s="11" t="n"/>
-      <c r="D37" s="11" t="n"/>
-      <c r="E37" s="11" t="n"/>
-      <c r="F37" s="11" t="n"/>
-      <c r="G37" s="11" t="n"/>
-      <c r="H37" s="11" t="n"/>
-    </row>
-    <row r="38" ht="30" customHeight="1">
-      <c r="B38" s="12" t="inlineStr">
-        <is>
-          <t>Açúcar refinado</t>
-        </is>
-      </c>
-      <c r="C38" s="13" t="inlineStr"/>
-      <c r="D38" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E38" s="13" t="inlineStr">
-        <is>
-          <t>evitar</t>
-        </is>
-      </c>
-      <c r="F38" s="16" t="inlineStr">
-        <is>
-          <t>Evitar</t>
-        </is>
-      </c>
-      <c r="G38" s="13" t="inlineStr"/>
-      <c r="H38" s="12" t="inlineStr">
-        <is>
-          <t>Impacto direto nos triglicerídeos</t>
-        </is>
-      </c>
+      <c r="B38" s="11" t="n"/>
+      <c r="C38" s="11" t="n"/>
+      <c r="D38" s="11" t="n"/>
+      <c r="E38" s="11" t="n"/>
+      <c r="F38" s="11" t="n"/>
+      <c r="G38" s="11" t="n"/>
+      <c r="H38" s="11" t="n"/>
     </row>
     <row r="39" ht="30" customHeight="1">
       <c r="B39" s="12" t="inlineStr">
         <is>
-          <t>Doces industrializados</t>
+          <t>Açúcar refinado</t>
         </is>
       </c>
       <c r="C39" s="13" t="inlineStr"/>
@@ -2061,233 +2065,262 @@
         </is>
       </c>
       <c r="G39" s="13" t="inlineStr"/>
-      <c r="H39" s="12" t="inlineStr"/>
+      <c r="H39" s="12" t="inlineStr">
+        <is>
+          <t>Impacto direto nos triglicerídeos</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="30" customHeight="1">
       <c r="B40" s="12" t="inlineStr">
         <is>
-          <t>Chocolate amargo (70%+)</t>
+          <t>Doces industrializados</t>
         </is>
       </c>
       <c r="C40" s="13" t="inlineStr"/>
       <c r="D40" s="13" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E40" s="13" t="inlineStr">
+        <is>
+          <t>evitar</t>
+        </is>
+      </c>
+      <c r="F40" s="16" t="inlineStr">
+        <is>
+          <t>Evitar</t>
+        </is>
+      </c>
+      <c r="G40" s="13" t="inlineStr"/>
+      <c r="H40" s="12" t="inlineStr"/>
+    </row>
+    <row r="41" ht="30" customHeight="1">
+      <c r="B41" s="12" t="inlineStr">
+        <is>
+          <t>Chocolate amargo (70%+)</t>
+        </is>
+      </c>
+      <c r="C41" s="13" t="inlineStr"/>
+      <c r="D41" s="13" t="inlineStr">
+        <is>
           <t>10 g</t>
         </is>
       </c>
-      <c r="E40" s="13" t="inlineStr">
+      <c r="E41" s="13" t="inlineStr">
         <is>
           <t>2x/semana</t>
         </is>
       </c>
-      <c r="F40" s="15" t="inlineStr">
+      <c r="F41" s="15" t="inlineStr">
         <is>
           <t>Moderar</t>
         </is>
       </c>
-      <c r="G40" s="13" t="inlineStr"/>
-      <c r="H40" s="12" t="inlineStr">
+      <c r="G41" s="13" t="inlineStr"/>
+      <c r="H41" s="12" t="inlineStr">
         <is>
           <t>Sugestão gerada por IA — confirmar com nutricionista/cardiologista</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="20" customHeight="1">
-      <c r="A41" s="10" t="inlineStr">
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="10" t="inlineStr">
         <is>
           <t>Gorduras e Temperos</t>
         </is>
       </c>
-      <c r="B41" s="11" t="n"/>
-      <c r="C41" s="11" t="n"/>
-      <c r="D41" s="11" t="n"/>
-      <c r="E41" s="11" t="n"/>
-      <c r="F41" s="11" t="n"/>
-      <c r="G41" s="11" t="n"/>
-      <c r="H41" s="11" t="n"/>
-    </row>
-    <row r="42" ht="30" customHeight="1">
-      <c r="B42" s="12" t="inlineStr">
-        <is>
-          <t>Azeite de oliva extra virgem</t>
-        </is>
-      </c>
-      <c r="C42" s="13" t="inlineStr"/>
-      <c r="D42" s="13" t="inlineStr">
-        <is>
-          <t>1-2 colheres de sopa</t>
-        </is>
-      </c>
-      <c r="E42" s="13" t="inlineStr">
-        <is>
-          <t>1x/dia</t>
-        </is>
-      </c>
-      <c r="F42" s="14" t="inlineStr">
-        <is>
-          <t>Liberado</t>
-        </is>
-      </c>
-      <c r="G42" s="13" t="inlineStr"/>
-      <c r="H42" s="12" t="inlineStr"/>
+      <c r="B42" s="11" t="n"/>
+      <c r="C42" s="11" t="n"/>
+      <c r="D42" s="11" t="n"/>
+      <c r="E42" s="11" t="n"/>
+      <c r="F42" s="11" t="n"/>
+      <c r="G42" s="11" t="n"/>
+      <c r="H42" s="11" t="n"/>
     </row>
     <row r="43" ht="30" customHeight="1">
       <c r="B43" s="12" t="inlineStr">
         <is>
-          <t>Manteiga</t>
+          <t>Azeite de oliva extra virgem</t>
         </is>
       </c>
       <c r="C43" s="13" t="inlineStr"/>
       <c r="D43" s="13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1-2 colheres de sopa</t>
         </is>
       </c>
       <c r="E43" s="13" t="inlineStr">
         <is>
-          <t>evitar</t>
-        </is>
-      </c>
-      <c r="F43" s="16" t="inlineStr">
-        <is>
-          <t>Evitar</t>
+          <t>1x/dia</t>
+        </is>
+      </c>
+      <c r="F43" s="14" t="inlineStr">
+        <is>
+          <t>Liberado</t>
         </is>
       </c>
       <c r="G43" s="13" t="inlineStr"/>
-      <c r="H43" s="12" t="inlineStr">
-        <is>
-          <t>Preferir azeite</t>
-        </is>
-      </c>
+      <c r="H43" s="12" t="inlineStr"/>
     </row>
     <row r="44" ht="30" customHeight="1">
       <c r="B44" s="12" t="inlineStr">
         <is>
-          <t>Sal</t>
+          <t>Manteiga</t>
         </is>
       </c>
       <c r="C44" s="13" t="inlineStr"/>
       <c r="D44" s="13" t="inlineStr">
         <is>
-          <t>&lt; 5 g no total</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E44" s="13" t="inlineStr">
         <is>
-          <t>todos os dias</t>
-        </is>
-      </c>
-      <c r="F44" s="15" t="inlineStr">
-        <is>
-          <t>Moderar</t>
+          <t>evitar</t>
+        </is>
+      </c>
+      <c r="F44" s="16" t="inlineStr">
+        <is>
+          <t>Evitar</t>
         </is>
       </c>
       <c r="G44" s="13" t="inlineStr"/>
       <c r="H44" s="12" t="inlineStr">
         <is>
-          <t>Somar sal de cozinha + industrializados</t>
+          <t>Preferir azeite</t>
         </is>
       </c>
     </row>
     <row r="45" ht="30" customHeight="1">
       <c r="B45" s="12" t="inlineStr">
         <is>
-          <t>Sal light / substituto de sal (cloreto de potássio)</t>
+          <t>Sal</t>
         </is>
       </c>
       <c r="C45" s="13" t="inlineStr"/>
       <c r="D45" s="13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>&lt; 5 g no total</t>
         </is>
       </c>
       <c r="E45" s="13" t="inlineStr">
         <is>
-          <t>evitar</t>
-        </is>
-      </c>
-      <c r="F45" s="16" t="inlineStr">
-        <is>
-          <t>Evitar</t>
+          <t>todos os dias</t>
+        </is>
+      </c>
+      <c r="F45" s="15" t="inlineStr">
+        <is>
+          <t>Moderar</t>
         </is>
       </c>
       <c r="G45" s="13" t="inlineStr"/>
       <c r="H45" s="12" t="inlineStr">
         <is>
-          <t>Enalapril já tende a elevar o potássio; combinado com esse produto o risco de hipercalemia aumenta, ainda mais com a função renal pendente.</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="30" customHeight="1">
+          <t>Somar sal de cozinha + industrializados</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="36" customHeight="1">
       <c r="B46" s="12" t="inlineStr">
         <is>
-          <t>Ervas e temperos naturais</t>
+          <t>Sal light / substituto de sal (cloreto de potássio)</t>
         </is>
       </c>
       <c r="C46" s="13" t="inlineStr"/>
       <c r="D46" s="13" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E46" s="13" t="inlineStr">
+        <is>
+          <t>evitar</t>
+        </is>
+      </c>
+      <c r="F46" s="16" t="inlineStr">
+        <is>
+          <t>Evitar</t>
+        </is>
+      </c>
+      <c r="G46" s="13" t="inlineStr"/>
+      <c r="H46" s="12" t="inlineStr">
+        <is>
+          <t>Enalapril já tende a elevar o potássio; combinado com esse produto o risco de hipercalemia aumenta, ainda mais com a função renal pendente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="30" customHeight="1">
+      <c r="B47" s="12" t="inlineStr">
+        <is>
+          <t>Ervas e temperos naturais</t>
+        </is>
+      </c>
+      <c r="C47" s="13" t="inlineStr"/>
+      <c r="D47" s="13" t="inlineStr">
+        <is>
           <t>à vontade</t>
         </is>
       </c>
-      <c r="E46" s="13" t="inlineStr">
+      <c r="E47" s="13" t="inlineStr">
         <is>
           <t>todos os dias</t>
         </is>
       </c>
-      <c r="F46" s="14" t="inlineStr">
+      <c r="F47" s="14" t="inlineStr">
         <is>
           <t>Liberado</t>
         </is>
       </c>
-      <c r="G46" s="13" t="inlineStr"/>
-      <c r="H46" s="12" t="inlineStr"/>
-    </row>
-    <row r="47" ht="20" customHeight="1">
-      <c r="A47" s="10" t="inlineStr">
+      <c r="G47" s="13" t="inlineStr"/>
+      <c r="H47" s="12" t="inlineStr"/>
+    </row>
+    <row r="48" ht="20" customHeight="1">
+      <c r="A48" s="10" t="inlineStr">
         <is>
           <t>Vegetais e Verduras</t>
         </is>
       </c>
-      <c r="B47" s="11" t="n"/>
-      <c r="C47" s="11" t="n"/>
-      <c r="D47" s="11" t="n"/>
-      <c r="E47" s="11" t="n"/>
-      <c r="F47" s="11" t="n"/>
-      <c r="G47" s="11" t="n"/>
-      <c r="H47" s="11" t="n"/>
-    </row>
-    <row r="48" ht="30" customHeight="1">
-      <c r="B48" s="12" t="inlineStr">
+      <c r="B48" s="11" t="n"/>
+      <c r="C48" s="11" t="n"/>
+      <c r="D48" s="11" t="n"/>
+      <c r="E48" s="11" t="n"/>
+      <c r="F48" s="11" t="n"/>
+      <c r="G48" s="11" t="n"/>
+      <c r="H48" s="11" t="n"/>
+    </row>
+    <row r="49" ht="36" customHeight="1">
+      <c r="B49" s="12" t="inlineStr">
         <is>
           <t>Vegetais e verduras em geral</t>
         </is>
       </c>
-      <c r="C48" s="13" t="inlineStr"/>
-      <c r="D48" s="13" t="inlineStr">
+      <c r="C49" s="13" t="inlineStr"/>
+      <c r="D49" s="13" t="inlineStr">
         <is>
           <t>à vontade</t>
         </is>
       </c>
-      <c r="E48" s="13" t="inlineStr">
+      <c r="E49" s="13" t="inlineStr">
         <is>
           <t>todos os dias</t>
         </is>
       </c>
-      <c r="F48" s="14" t="inlineStr">
+      <c r="F49" s="14" t="inlineStr">
         <is>
           <t>Liberado</t>
         </is>
       </c>
-      <c r="G48" s="13" t="inlineStr"/>
-      <c r="H48" s="12" t="inlineStr">
+      <c r="G49" s="13" t="inlineStr"/>
+      <c r="H49" s="12" t="inlineStr">
         <is>
           <t>Se entrar anticoagulante na medicação, revisar consumo de verde-escuros ricos em vitamina K</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="40" customHeight="1">
-      <c r="A50" s="17" t="inlineStr">
+    <row r="51" ht="36" customHeight="1">
+      <c r="A51" s="17" t="inlineStr">
         <is>
           <t>Lista com os alimentos acrescentados até agora — não é uma lista completa. Use a skill 'adicionar-alimento' (ex.: "adicione sucrilhos") para ir acrescentando novos itens aos poucos. A coluna 'Gostoso' é sua — escolha do menu suspenso; o valor é preservado mesmo quando a planilha é regenerada por um alimento novo.</t>
         </is>
@@ -2295,20 +2328,20 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A50:H50"/>
     <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A30:H30"/>
+    <mergeCell ref="A48:H48"/>
     <mergeCell ref="G2:H2"/>
-    <mergeCell ref="A41:H41"/>
+    <mergeCell ref="A38:H38"/>
+    <mergeCell ref="A51:H51"/>
+    <mergeCell ref="A42:H42"/>
     <mergeCell ref="A11:H11"/>
-    <mergeCell ref="A37:H37"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A23:H23"/>
-    <mergeCell ref="A47:H47"/>
+    <mergeCell ref="A31:H31"/>
     <mergeCell ref="A17:H17"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="G5 G6 G7 G8 G9 G10 G12 G13 G14 G15 G16 G18 G19 G20 G21 G22 G24 G25 G26 G27 G28 G29 G31 G32 G33 G34 G35 G36 G38 G39 G40 G42 G43 G44 G45 G46 G48" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Fora da lista" error="Escolha uma opção do menu (ou deixe em branco)." type="list" errorStyle="warning">
+    <dataValidation sqref="G5 G6 G7 G8 G9 G10 G12 G13 G14 G15 G16 G18 G19 G20 G21 G22 G24 G25 G26 G27 G28 G29 G30 G32 G33 G34 G35 G36 G37 G39 G40 G41 G43 G44 G45 G46 G47 G49" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Fora da lista" error="Escolha uma opção do menu (ou deixe em branco)." type="list" errorStyle="warning">
       <formula1>"Ruim,Normal,Bom,Muito bom"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3290,7 +3323,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="44" customHeight="1">
+    <row r="4" ht="36" customHeight="1">
       <c r="A4" s="32" t="n">
         <v>1</v>
       </c>
@@ -3320,7 +3353,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="44" customHeight="1">
+    <row r="5" ht="36" customHeight="1">
       <c r="A5" s="32" t="n">
         <v>2</v>
       </c>
@@ -3350,7 +3383,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="44" customHeight="1">
+    <row r="6" ht="36" customHeight="1">
       <c r="A6" s="32" t="n">
         <v>3</v>
       </c>
@@ -3380,7 +3413,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="44" customHeight="1">
+    <row r="7" ht="36" customHeight="1">
       <c r="A7" s="32" t="n">
         <v>4</v>
       </c>
@@ -3410,7 +3443,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="44" customHeight="1">
+    <row r="8" ht="36" customHeight="1">
       <c r="A8" s="32" t="n">
         <v>5</v>
       </c>
@@ -3440,7 +3473,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="44" customHeight="1">
+    <row r="9" ht="36" customHeight="1">
       <c r="A9" s="32" t="n">
         <v>6</v>
       </c>
@@ -3470,7 +3503,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="44" customHeight="1">
+    <row r="10" ht="36" customHeight="1">
       <c r="A10" s="32" t="n">
         <v>7</v>
       </c>
@@ -3500,7 +3533,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="44" customHeight="1">
+    <row r="11" ht="50" customHeight="1">
       <c r="A11" s="32" t="n">
         <v>8</v>
       </c>
@@ -3530,7 +3563,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="44" customHeight="1">
+    <row r="12" ht="50" customHeight="1">
       <c r="A12" s="32" t="n">
         <v>9</v>
       </c>
@@ -3560,7 +3593,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="44" customHeight="1">
+    <row r="13" ht="36" customHeight="1">
       <c r="A13" s="32" t="n">
         <v>10</v>
       </c>
@@ -3590,7 +3623,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="44" customHeight="1">
+    <row r="14" ht="36" customHeight="1">
       <c r="A14" s="32" t="n">
         <v>11</v>
       </c>
@@ -3620,7 +3653,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="44" customHeight="1">
+    <row r="15" ht="36" customHeight="1">
       <c r="A15" s="32" t="n">
         <v>12</v>
       </c>
@@ -3650,7 +3683,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="44" customHeight="1">
+    <row r="16" ht="36" customHeight="1">
       <c r="A16" s="32" t="n">
         <v>13</v>
       </c>
@@ -3680,7 +3713,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="44" customHeight="1">
+    <row r="17" ht="36" customHeight="1">
       <c r="A17" s="32" t="n">
         <v>14</v>
       </c>
@@ -3710,7 +3743,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="44" customHeight="1">
+    <row r="18" ht="50" customHeight="1">
       <c r="A18" s="32" t="n">
         <v>15</v>
       </c>
@@ -3740,7 +3773,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="44" customHeight="1">
+    <row r="19" ht="36" customHeight="1">
       <c r="A19" s="32" t="n">
         <v>16</v>
       </c>
@@ -3770,7 +3803,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="44" customHeight="1">
+    <row r="20" ht="36" customHeight="1">
       <c r="A20" s="32" t="n">
         <v>17</v>
       </c>
@@ -3800,7 +3833,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="44" customHeight="1">
+    <row r="21" ht="36" customHeight="1">
       <c r="A21" s="32" t="n">
         <v>18</v>
       </c>
@@ -3830,7 +3863,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="44" customHeight="1">
+    <row r="22" ht="36" customHeight="1">
       <c r="A22" s="32" t="n">
         <v>19</v>
       </c>
@@ -3860,7 +3893,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="44" customHeight="1">
+    <row r="23" ht="36" customHeight="1">
       <c r="A23" s="32" t="n">
         <v>20</v>
       </c>
@@ -3890,7 +3923,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="44" customHeight="1">
+    <row r="24" ht="36" customHeight="1">
       <c r="A24" s="32" t="n">
         <v>21</v>
       </c>
@@ -3920,7 +3953,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="44" customHeight="1">
+    <row r="25" ht="36" customHeight="1">
       <c r="A25" s="32" t="n">
         <v>22</v>
       </c>
@@ -3997,7 +4030,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U38"/>
+  <dimension ref="A1:U39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4873,7 +4906,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Água</t>
+          <t>Iogurte grego zero</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -4947,7 +4980,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Café sem açúcar</t>
+          <t>Água</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -5011,7 +5044,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Água</t>
+          <t>Iogurte grego zero</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -5021,7 +5054,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Vegetais e verduras em geral</t>
+          <t>Café sem açúcar</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -5081,7 +5114,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Café sem açúcar</t>
+          <t>Água</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -5091,7 +5124,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Uva</t>
+          <t>Vegetais e verduras em geral</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -5155,7 +5188,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Vegetais e verduras em geral</t>
+          <t>Café sem açúcar</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -5165,7 +5198,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Manga</t>
+          <t>Uva</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -5229,7 +5262,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Uva</t>
+          <t>Vegetais e verduras em geral</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -5239,7 +5272,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Mussarela</t>
+          <t>Manga</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -5299,7 +5332,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Manga</t>
+          <t>Uva</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -5309,7 +5342,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Requeijão</t>
+          <t>Mussarela</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -5369,12 +5402,12 @@
       <c r="J18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Mussarela</t>
+          <t>Manga</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Refrigerante zero</t>
+          <t>Requeijão</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -5433,12 +5466,12 @@
       <c r="J19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Requeijão</t>
+          <t>Mussarela</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Suco natural sem açúcar</t>
+          <t>Refrigerante zero</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -5497,12 +5530,12 @@
       <c r="J20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
+          <t>Requeijão</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
           <t>Suco natural sem açúcar</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>Chocolate amargo (70%+)</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
@@ -5561,12 +5594,12 @@
       <c r="J21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Toranja / grapefruit</t>
+          <t>Suco natural sem açúcar</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Toranja / grapefruit</t>
+          <t>Chocolate amargo (70%+)</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
@@ -5625,12 +5658,12 @@
       <c r="J22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Suco de toranja / grapefruit</t>
+          <t>Toranja / grapefruit</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Suco de toranja / grapefruit</t>
+          <t>Toranja / grapefruit</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
@@ -5647,7 +5680,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Requeijão</t>
+          <t>Iogurte grego zero</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -5657,22 +5690,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Moderar</t>
+          <t>Liberado</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1 colher de sopa (≈15 g)</t>
+          <t>90 g (1 pote)</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2x/semana</t>
+          <t>1x/dia</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rico em gordura saturada e sódio; prefira a versão light. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
+          <t>Rótulo real: 50 kcal, 6,8 g de proteína (bem mais que iogurte comum), 0,2 g de gordura, 51 mg de sódio, zero adição de açúcar/gordura, sem lactose. Contém edulcorantes (sucralose e ciclamato).</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -5689,12 +5722,12 @@
       <c r="J23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Açúcar refinado</t>
+          <t>Suco de toranja / grapefruit</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Açúcar refinado</t>
+          <t>Suco de toranja / grapefruit</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
@@ -5711,58 +5744,54 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Água</t>
+          <t>Requeijão</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Bebidas</t>
+          <t>Laticínios</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Liberado</t>
+          <t>Moderar</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>à vontade</t>
+          <t>1 colher de sopa (≈15 g)</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>todos os dias</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr"/>
+          <t>2x/semana</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Rico em gordura saturada e sódio; prefira a versão light. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
+        </is>
+      </c>
       <c r="G24" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="J24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Manteiga</t>
+          <t>Açúcar refinado</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Doces industrializados</t>
+          <t>Açúcar refinado</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
@@ -5779,7 +5808,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Refrigerante zero</t>
+          <t>Água</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5789,25 +5818,25 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Moderar</t>
+          <t>Liberado</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>200 ml</t>
+          <t>à vontade</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1x/dia</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Sugestão gerada por IA — confirmar com nutricionista/cardiologista</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr"/>
+          <t>todos os dias</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="H25" t="inlineStr">
         <is>
           <t>X</t>
@@ -5821,6 +5850,16 @@
       <c r="J25" t="inlineStr">
         <is>
           <t>X</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Manteiga</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Doces industrializados</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
@@ -5837,7 +5876,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Café sem açúcar</t>
+          <t>Refrigerante zero</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5847,32 +5886,40 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Liberado</t>
+          <t>Moderar</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1 xícara</t>
+          <t>200 ml</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2x/dia</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr"/>
+          <t>1x/dia</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Sugestão gerada por IA — confirmar com nutricionista/cardiologista</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="I26" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="Q26" t="inlineStr">
         <is>
           <t>Gorduras e Temperos|Jantar</t>
@@ -5887,7 +5934,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Suco natural sem açúcar</t>
+          <t>Café sem açúcar</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5897,24 +5944,20 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Moderar</t>
+          <t>Liberado</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>200 ml</t>
+          <t>1 xícara</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>3x/semana</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Preferir a fruta inteira, que tem mais fibra</t>
-        </is>
-      </c>
+          <t>2x/dia</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
           <t>X</t>
@@ -5941,7 +5984,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Suco de toranja / grapefruit</t>
+          <t>Suco natural sem açúcar</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5951,22 +5994,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Evitar</t>
+          <t>Moderar</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>200 ml</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>evitar</t>
+          <t>3x/semana</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Interage com o Ticagrelor (estudo mostrou quase o dobro do nível do remédio no sangue); a bula diz que não é esperado ser clinicamente relevante p/ a maioria, mas orienta evitar — mais seguro evitar, já que você toma 2 antiagregantes. Ver aba Fontes e Referências.</t>
+          <t>Preferir a fruta inteira, que tem mais fibra</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -5985,7 +6028,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Bebida alcoólica</t>
+          <t>Suco de toranja / grapefruit</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -6010,31 +6053,31 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Piora diretamente os triglicerídeos; soma-se ao risco de sangramento da Aspirina + Ticagrelor.</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+          <t>Interage com o Ticagrelor (estudo mostrou quase o dobro do nível do remédio no sangue); a bula diz que não é esperado ser clinicamente relevante p/ a maioria, mas orienta evitar — mais seguro evitar, já que você toma 2 antiagregantes. Ver aba Fontes e Referências.</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Açúcar refinado</t>
+          <t>Bebida alcoólica</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Doces e Sobremesas</t>
+          <t>Bebidas</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -6054,24 +6097,16 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Impacto direto nos triglicerídeos</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+          <t>Piora diretamente os triglicerídeos; soma-se ao risco de sangramento da Aspirina + Ticagrelor.</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
           <t>X</t>
@@ -6081,7 +6116,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Doces industrializados</t>
+          <t>Açúcar refinado</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -6104,20 +6139,36 @@
           <t>evitar</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Impacto direto nos triglicerídeos</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="I31" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Chocolate amargo (70%+)</t>
+          <t>Doces industrializados</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -6127,24 +6178,20 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Moderar</t>
+          <t>Evitar</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>10 g</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2x/semana</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Sugestão gerada por IA — confirmar com nutricionista/cardiologista</t>
-        </is>
-      </c>
+          <t>evitar</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
@@ -6157,47 +6204,47 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Azeite de oliva extra virgem</t>
+          <t>Chocolate amargo (70%+)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Gorduras e Temperos</t>
+          <t>Doces e Sobremesas</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Liberado</t>
+          <t>Moderar</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1-2 colheres de sopa</t>
+          <t>10 g</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1x/dia</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr"/>
+          <t>2x/semana</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Sugestão gerada por IA — confirmar com nutricionista/cardiologista</t>
+        </is>
+      </c>
       <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Manteiga</t>
+          <t>Azeite de oliva extra virgem</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -6207,37 +6254,37 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Evitar</t>
+          <t>Liberado</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1-2 colheres de sopa</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>evitar</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Preferir azeite</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr"/>
+          <t>1x/dia</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sal</t>
+          <t>Manteiga</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -6247,41 +6294,37 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Moderar</t>
+          <t>Evitar</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>&lt; 5 g no total</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>todos os dias</t>
+          <t>evitar</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Somar sal de cozinha + industrializados</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+          <t>Preferir azeite</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="J35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sal light / substituto de sal (cloreto de potássio)</t>
+          <t>Sal</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -6291,22 +6334,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Evitar</t>
+          <t>Moderar</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>&lt; 5 g no total</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>evitar</t>
+          <t>todos os dias</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Enalapril já tende a elevar o potássio; combinado com esse produto o risco de hipercalemia aumenta, ainda mais com a função renal pendente.</t>
+          <t>Somar sal de cozinha + industrializados</t>
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
@@ -6325,7 +6368,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Ervas e temperos naturais</t>
+          <t>Sal light / substituto de sal (cloreto de potássio)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -6335,20 +6378,24 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Liberado</t>
+          <t>Evitar</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>à vontade</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>todos os dias</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr"/>
+          <t>evitar</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Enalapril já tende a elevar o potássio; combinado com esse produto o risco de hipercalemia aumenta, ainda mais com a função renal pendente.</t>
+        </is>
+      </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
@@ -6365,50 +6412,90 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>Ervas e temperos naturais</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Gorduras e Temperos</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Liberado</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>à vontade</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>todos os dias</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
           <t>Vegetais e verduras em geral</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>Vegetais e Verduras</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>Liberado</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>à vontade</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>todos os dias</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>Se entrar anticoagulante na medicação, revisar consumo de verde-escuros ricos em vitamina K</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
         <is>
           <t>X</t>
         </is>

--- a/planilha/plano-alimentar-pos-infarto.xlsx
+++ b/planilha/plano-alimentar-pos-infarto.xlsx
@@ -1393,16 +1393,20 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="30" customHeight="1">
+    <row r="14" ht="50" customHeight="1">
       <c r="B14" s="12" t="inlineStr">
         <is>
-          <t>Aveia</t>
-        </is>
-      </c>
-      <c r="C14" s="13" t="inlineStr"/>
+          <t>Aveia integral em flocos</t>
+        </is>
+      </c>
+      <c r="C14" s="13" t="inlineStr">
+        <is>
+          <t>Quaker</t>
+        </is>
+      </c>
       <c r="D14" s="13" t="inlineStr">
         <is>
-          <t>2 colheres de sopa</t>
+          <t>2 colheres de sopa (~30 g)</t>
         </is>
       </c>
       <c r="E14" s="13" t="inlineStr">
@@ -1418,7 +1422,7 @@
       <c r="G14" s="13" t="inlineStr"/>
       <c r="H14" s="12" t="inlineStr">
         <is>
-          <t>Ajuda a reduzir colesterol</t>
+          <t>Rótulo real: 110 kcal, 2,8 g de fibra (1,2 g de beta-glucana — a fibra solúvel que ajuda a reduzir o colesterol), sem açúcar adicionado, 0 mg de sódio.</t>
         </is>
       </c>
     </row>
@@ -4271,7 +4275,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Aveia</t>
+          <t>Aveia integral em flocos</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -4414,7 +4418,7 @@
       <c r="J5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Aveia</t>
+          <t>Aveia integral em flocos</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -4788,7 +4792,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Aveia</t>
+          <t>Aveia integral em flocos</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4803,7 +4807,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2 colheres de sopa</t>
+          <t>2 colheres de sopa (~30 g)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4813,7 +4817,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ajuda a reduzir colesterol</t>
+          <t>Rótulo real: 110 kcal, 2,8 g de fibra (1,2 g de beta-glucana — a fibra solúvel que ajuda a reduzir o colesterol), sem açúcar adicionado, 0 mg de sódio.</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
